--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="562">
   <si>
     <t>IDSocio</t>
   </si>
@@ -106,216 +106,240 @@
     <t>288404</t>
   </si>
   <si>
+    <t>301635</t>
+  </si>
+  <si>
     <t>326034</t>
   </si>
   <si>
     <t>278277</t>
   </si>
   <si>
+    <t>331503</t>
+  </si>
+  <si>
+    <t>340080</t>
+  </si>
+  <si>
     <t>278704</t>
   </si>
   <si>
-    <t>331503</t>
+    <t>340085</t>
   </si>
   <si>
     <t>316379</t>
   </si>
   <si>
+    <t>341105</t>
+  </si>
+  <si>
     <t>339397</t>
   </si>
   <si>
-    <t>340080</t>
-  </si>
-  <si>
-    <t>340085</t>
+    <t>341507</t>
+  </si>
+  <si>
+    <t>341661</t>
+  </si>
+  <si>
+    <t>341663</t>
+  </si>
+  <si>
+    <t>341100</t>
+  </si>
+  <si>
+    <t>341505</t>
   </si>
   <si>
     <t>340527</t>
   </si>
   <si>
-    <t>341100</t>
+    <t>342256</t>
+  </si>
+  <si>
+    <t>342260</t>
+  </si>
+  <si>
+    <t>342280</t>
+  </si>
+  <si>
+    <t>342298</t>
   </si>
   <si>
     <t>340868</t>
   </si>
   <si>
-    <t>341105</t>
-  </si>
-  <si>
-    <t>341505</t>
-  </si>
-  <si>
     <t>341037</t>
   </si>
   <si>
+    <t>342346</t>
+  </si>
+  <si>
+    <t>342395</t>
+  </si>
+  <si>
+    <t>342308</t>
+  </si>
+  <si>
+    <t>341568</t>
+  </si>
+  <si>
+    <t>342319</t>
+  </si>
+  <si>
+    <t>342661</t>
+  </si>
+  <si>
+    <t>342901</t>
+  </si>
+  <si>
+    <t>342175</t>
+  </si>
+  <si>
     <t>341259</t>
   </si>
   <si>
-    <t>342175</t>
-  </si>
-  <si>
-    <t>341507</t>
-  </si>
-  <si>
-    <t>341661</t>
-  </si>
-  <si>
-    <t>341663</t>
-  </si>
-  <si>
-    <t>341568</t>
-  </si>
-  <si>
-    <t>342308</t>
-  </si>
-  <si>
-    <t>342298</t>
+    <t>342761</t>
+  </si>
+  <si>
+    <t>343805</t>
+  </si>
+  <si>
+    <t>344674</t>
   </si>
   <si>
     <t>342110</t>
   </si>
   <si>
-    <t>342761</t>
-  </si>
-  <si>
-    <t>342256</t>
-  </si>
-  <si>
-    <t>342260</t>
-  </si>
-  <si>
-    <t>342280</t>
-  </si>
-  <si>
-    <t>342346</t>
-  </si>
-  <si>
-    <t>342661</t>
+    <t>344234</t>
+  </si>
+  <si>
+    <t>344677</t>
   </si>
   <si>
     <t>342364</t>
   </si>
   <si>
-    <t>342319</t>
-  </si>
-  <si>
-    <t>342395</t>
-  </si>
-  <si>
-    <t>342901</t>
-  </si>
-  <si>
-    <t>343805</t>
-  </si>
-  <si>
     <t>343806</t>
   </si>
   <si>
     <t>85902</t>
   </si>
   <si>
+    <t>99133</t>
+  </si>
+  <si>
     <t>22973</t>
   </si>
   <si>
     <t>75778</t>
   </si>
   <si>
+    <t>16557</t>
+  </si>
+  <si>
+    <t>17898</t>
+  </si>
+  <si>
     <t>76205</t>
   </si>
   <si>
-    <t>16557</t>
+    <t>17903</t>
   </si>
   <si>
     <t>13877</t>
   </si>
   <si>
+    <t>18923</t>
+  </si>
+  <si>
     <t>17215</t>
   </si>
   <si>
-    <t>17898</t>
-  </si>
-  <si>
-    <t>17903</t>
+    <t>19325</t>
+  </si>
+  <si>
+    <t>19479</t>
+  </si>
+  <si>
+    <t>19481</t>
+  </si>
+  <si>
+    <t>18918</t>
+  </si>
+  <si>
+    <t>19323</t>
   </si>
   <si>
     <t>18345</t>
   </si>
   <si>
-    <t>18918</t>
+    <t>20074</t>
+  </si>
+  <si>
+    <t>20078</t>
+  </si>
+  <si>
+    <t>20098</t>
+  </si>
+  <si>
+    <t>20116</t>
   </si>
   <si>
     <t>18686</t>
   </si>
   <si>
-    <t>18923</t>
-  </si>
-  <si>
-    <t>19323</t>
-  </si>
-  <si>
     <t>18855</t>
   </si>
   <si>
+    <t>20164</t>
+  </si>
+  <si>
+    <t>20213</t>
+  </si>
+  <si>
+    <t>20126</t>
+  </si>
+  <si>
+    <t>19386</t>
+  </si>
+  <si>
+    <t>20137</t>
+  </si>
+  <si>
+    <t>20478</t>
+  </si>
+  <si>
+    <t>20718</t>
+  </si>
+  <si>
+    <t>19993</t>
+  </si>
+  <si>
     <t>19077</t>
   </si>
   <si>
-    <t>19993</t>
-  </si>
-  <si>
-    <t>19325</t>
-  </si>
-  <si>
-    <t>19479</t>
-  </si>
-  <si>
-    <t>19481</t>
-  </si>
-  <si>
-    <t>19386</t>
-  </si>
-  <si>
-    <t>20126</t>
-  </si>
-  <si>
-    <t>20116</t>
+    <t>20578</t>
+  </si>
+  <si>
+    <t>21622</t>
+  </si>
+  <si>
+    <t>22491</t>
   </si>
   <si>
     <t>19928</t>
   </si>
   <si>
-    <t>20578</t>
-  </si>
-  <si>
-    <t>20074</t>
-  </si>
-  <si>
-    <t>20078</t>
-  </si>
-  <si>
-    <t>20098</t>
-  </si>
-  <si>
-    <t>20164</t>
-  </si>
-  <si>
-    <t>20478</t>
+    <t>22051</t>
+  </si>
+  <si>
+    <t>22494</t>
   </si>
   <si>
     <t>20182</t>
   </si>
   <si>
-    <t>20137</t>
-  </si>
-  <si>
-    <t>20213</t>
-  </si>
-  <si>
-    <t>20718</t>
-  </si>
-  <si>
-    <t>21622</t>
-  </si>
-  <si>
     <t>21623</t>
   </si>
   <si>
@@ -325,213 +349,228 @@
     <t>CRISTIAN ALAN</t>
   </si>
   <si>
+    <t xml:space="preserve">YODGAR JASIEL </t>
+  </si>
+  <si>
     <t>GILBERTO</t>
   </si>
   <si>
     <t xml:space="preserve">JAVIER OMAR </t>
   </si>
   <si>
+    <t>JOSE ALBERTO</t>
+  </si>
+  <si>
+    <t>YARELI</t>
+  </si>
+  <si>
     <t>ANIBAL</t>
   </si>
   <si>
-    <t>JOSE ALBERTO</t>
+    <t>EDNA ODALYS</t>
   </si>
   <si>
     <t>SEBASTIAN</t>
   </si>
   <si>
+    <t>ELIANA JANETH</t>
+  </si>
+  <si>
     <t>JUAN JOSE</t>
   </si>
   <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>EDNA ODALYS</t>
+    <t>KARELIA EDITH</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>NAOMI ALEJANDRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR MANUEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBARA </t>
   </si>
   <si>
     <t>JULIO CESAR</t>
   </si>
   <si>
-    <t xml:space="preserve">VICTOR MANUEL </t>
+    <t>EIMY ANAHI</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL </t>
   </si>
   <si>
     <t xml:space="preserve">LUIS ADRIAN </t>
   </si>
   <si>
-    <t>ELIANA JANETH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARBARA </t>
-  </si>
-  <si>
     <t>HEDER ARTURO</t>
   </si>
   <si>
+    <t>VICTORIA</t>
+  </si>
+  <si>
+    <t>ALISON</t>
+  </si>
+  <si>
+    <t>DANIEL ANTONIO</t>
+  </si>
+  <si>
+    <t>GRECIA</t>
+  </si>
+  <si>
+    <t>NANCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ALONSO </t>
+  </si>
+  <si>
+    <t>LETICIA</t>
+  </si>
+  <si>
+    <t>MARCO IVAN</t>
+  </si>
+  <si>
     <t xml:space="preserve">NAYELI ADAMARI </t>
   </si>
   <si>
-    <t>MARCO IVAN</t>
-  </si>
-  <si>
-    <t>KARELIA EDITH</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>NAOMI ALEJANDRA</t>
-  </si>
-  <si>
-    <t>GRECIA</t>
-  </si>
-  <si>
-    <t>DANIEL ANTONIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAFAEL </t>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSA IRENE </t>
+  </si>
+  <si>
+    <t>ABRAHM</t>
   </si>
   <si>
     <t>MARIO EDGARDO</t>
   </si>
   <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>EIMY ANAHI</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>VICTORIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSE ALONSO </t>
+    <t>JONATHA IVAN</t>
   </si>
   <si>
     <t>CLAUDIA LESLIE</t>
   </si>
   <si>
-    <t>NANCY</t>
-  </si>
-  <si>
-    <t>ALISON</t>
-  </si>
-  <si>
-    <t>LETICIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROSA IRENE </t>
-  </si>
-  <si>
     <t>JESUS RUBEN</t>
   </si>
   <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
     <t>CISNEROS</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>GAYTAN</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>CHAPARRO</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t xml:space="preserve">GAYTAN </t>
+  </si>
+  <si>
     <t>LOERA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>CHAPARRO</t>
+    <t>GANDARILLA</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>MACIAS</t>
   </si>
   <si>
-    <t>ESTRADA</t>
+    <t xml:space="preserve">TOBARA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILLALOBOS </t>
+  </si>
+  <si>
+    <t>TAMEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOERA </t>
   </si>
   <si>
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t xml:space="preserve">GAYTAN </t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MONTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERRANO </t>
+  </si>
+  <si>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIVAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDERO </t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOLINAR </t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t xml:space="preserve">MOLINAR </t>
-  </si>
-  <si>
-    <t>GANDARILLA</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>AVILA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRANO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOERA </t>
+    <t>DOZAL</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOMEZ </t>
   </si>
   <si>
     <t>SILVA</t>
   </si>
   <si>
-    <t>DOZAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOBARA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VILLALOBOS </t>
-  </si>
-  <si>
-    <t>TAMEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDERO </t>
-  </si>
-  <si>
     <t>PORTILLO</t>
   </si>
   <si>
-    <t xml:space="preserve">OLIVAS </t>
-  </si>
-  <si>
-    <t>MONTES</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
     <t>LARA</t>
   </si>
   <si>
@@ -541,180 +580,201 @@
     <t>CAMPOS</t>
   </si>
   <si>
+    <t>HERMOSILLO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>HERMOSILLO</t>
+    <t>BARREA</t>
   </si>
   <si>
     <t>LUGO</t>
   </si>
   <si>
+    <t>HOLGUIN</t>
+  </si>
+  <si>
     <t>CABALLERO</t>
   </si>
   <si>
-    <t>BARREA</t>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>SANTOYO</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
   </si>
   <si>
     <t>CARO</t>
   </si>
   <si>
-    <t>SANTOYO</t>
+    <t>ALCANTAR</t>
+  </si>
+  <si>
+    <t>SAEZ</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>HOLGUIN</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CEBALLOS</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>CANTU</t>
   </si>
   <si>
     <t>VALLES</t>
   </si>
   <si>
-    <t>CANTU</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CEBALLOS</t>
-  </si>
-  <si>
-    <t>SAEZ</t>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
   </si>
   <si>
     <t>OLIVAS</t>
   </si>
   <si>
-    <t>CHACON</t>
-  </si>
-  <si>
-    <t>ALCANTAR</t>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>MORELOS</t>
   </si>
   <si>
     <t>MILLAN</t>
   </si>
   <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
     <t>6144545766</t>
   </si>
   <si>
+    <t>6146099932</t>
+  </si>
+  <si>
     <t>6141834791</t>
   </si>
   <si>
     <t>6142791568</t>
   </si>
   <si>
+    <t>6143556958</t>
+  </si>
+  <si>
+    <t>6142757940</t>
+  </si>
+  <si>
     <t>8129739105</t>
   </si>
   <si>
-    <t>6143556958</t>
+    <t>6143185738</t>
   </si>
   <si>
     <t>6144687095</t>
   </si>
   <si>
+    <t>6146308375</t>
+  </si>
+  <si>
     <t>6143368528</t>
   </si>
   <si>
-    <t>6142757940</t>
-  </si>
-  <si>
-    <t>6143185738</t>
+    <t>6391727197</t>
+  </si>
+  <si>
+    <t>6142817080</t>
+  </si>
+  <si>
+    <t>6145973271</t>
+  </si>
+  <si>
+    <t>6142518849</t>
+  </si>
+  <si>
+    <t>6143682180</t>
   </si>
   <si>
     <t>8112983028</t>
   </si>
   <si>
-    <t>6142518849</t>
+    <t>6145118271</t>
+  </si>
+  <si>
+    <t>6144616643</t>
+  </si>
+  <si>
+    <t>6146114137</t>
+  </si>
+  <si>
+    <t>6144270811</t>
   </si>
   <si>
     <t>6142166555</t>
   </si>
   <si>
-    <t>6146308375</t>
-  </si>
-  <si>
-    <t>6143682180</t>
-  </si>
-  <si>
     <t>6145315107</t>
   </si>
   <si>
+    <t>6141631910</t>
+  </si>
+  <si>
+    <t>6142511165</t>
+  </si>
+  <si>
+    <t>6271210648</t>
+  </si>
+  <si>
+    <t>6142139312</t>
+  </si>
+  <si>
+    <t>6491107772</t>
+  </si>
+  <si>
+    <t>6143546193</t>
+  </si>
+  <si>
+    <t>6142443644</t>
+  </si>
+  <si>
+    <t>6141719602</t>
+  </si>
+  <si>
     <t>6144630791</t>
   </si>
   <si>
-    <t>6141719602</t>
-  </si>
-  <si>
-    <t>6391727197</t>
-  </si>
-  <si>
-    <t>6142817080</t>
-  </si>
-  <si>
-    <t>6145973271</t>
-  </si>
-  <si>
-    <t>6142139312</t>
-  </si>
-  <si>
-    <t>6271210648</t>
-  </si>
-  <si>
-    <t>6144270811</t>
+    <t>6563497877</t>
+  </si>
+  <si>
+    <t>6143813334</t>
+  </si>
+  <si>
+    <t>6147767384</t>
   </si>
   <si>
     <t>6144714471</t>
   </si>
   <si>
-    <t>6563497877</t>
-  </si>
-  <si>
-    <t>6145118271</t>
-  </si>
-  <si>
-    <t>6144616643</t>
-  </si>
-  <si>
-    <t>6146114137</t>
-  </si>
-  <si>
-    <t>6141631910</t>
-  </si>
-  <si>
-    <t>6143546193</t>
+    <t>6141324957</t>
+  </si>
+  <si>
+    <t>6144072330</t>
   </si>
   <si>
     <t>6143534589</t>
   </si>
   <si>
-    <t>6491107772</t>
-  </si>
-  <si>
-    <t>6142511165</t>
-  </si>
-  <si>
-    <t>6142443644</t>
-  </si>
-  <si>
-    <t>6143813334</t>
-  </si>
-  <si>
     <t>6141109571</t>
   </si>
   <si>
@@ -724,75 +784,78 @@
     <t>GARCILAZO DE LA VEGA 15300</t>
   </si>
   <si>
+    <t>MINA LOS REYES 3722</t>
+  </si>
+  <si>
+    <t>C RUBEN JARAMILLO 214</t>
+  </si>
+  <si>
     <t>CALLE FRANCISCO PIMENTEL 5115</t>
   </si>
   <si>
-    <t>MINA LOS REYES 3722</t>
+    <t>C SALVADOR DIAZ CASAS 57</t>
+  </si>
+  <si>
+    <t>CALLE DELICIAS</t>
   </si>
   <si>
     <t>CALLE DE METER 5510</t>
   </si>
   <si>
-    <t>C RUBEN JARAMILLO 214</t>
-  </si>
-  <si>
-    <t>C SALVADOR DIAZ CASAS 57</t>
+    <t>SAN JORGE 2600</t>
   </si>
   <si>
     <t>CALLE DELCIAS</t>
   </si>
   <si>
+    <t>ALAMEDAS 311</t>
+  </si>
+  <si>
+    <t>PROLETARIOS 19</t>
+  </si>
+  <si>
     <t>CTO TERRANOVA 2803</t>
   </si>
   <si>
-    <t>CALLE DELICIAS</t>
-  </si>
-  <si>
-    <t>SAN JORGE 2600</t>
-  </si>
-  <si>
     <t xml:space="preserve">PASEOS DE JUAREZ </t>
   </si>
   <si>
+    <t>CAFETALES</t>
+  </si>
+  <si>
+    <t>MARK TWAIN 500</t>
+  </si>
+  <si>
+    <t>REPUBLICA DOMINICANA 20</t>
+  </si>
+  <si>
+    <t>ERNESTO ESPINOZA 269</t>
+  </si>
+  <si>
+    <t>REPUBLICA DOMINICANA</t>
+  </si>
+  <si>
+    <t>MONTE ALTAI 4323</t>
+  </si>
+  <si>
+    <t>PRIV DE GONZALEZ COSSIO 6734</t>
+  </si>
+  <si>
     <t>MIGUEL ANGEL SAENZ 14123</t>
   </si>
   <si>
-    <t>ERNESTO ESPINOZA 269</t>
-  </si>
-  <si>
-    <t>REPUBLICA DOMINICANA 20</t>
+    <t>RIO META 1803</t>
+  </si>
+  <si>
+    <t>CALLE DOLORES PIMENTEL</t>
   </si>
   <si>
     <t>CDA PUERTA DE GRANADA 2821</t>
   </si>
   <si>
-    <t>ALAMEDAS 311</t>
-  </si>
-  <si>
-    <t>PROLETARIOS 19</t>
-  </si>
-  <si>
-    <t>CAFETALES</t>
-  </si>
-  <si>
-    <t>MONTE ALTAI 4323</t>
-  </si>
-  <si>
     <t>CIUDAD DURANGO 31125</t>
   </si>
   <si>
-    <t>REPUBLICA DOMINICANA</t>
-  </si>
-  <si>
-    <t>MARK TWAIN 500</t>
-  </si>
-  <si>
-    <t>PRIV DE GONZALEZ COSSIO 6734</t>
-  </si>
-  <si>
-    <t>RIO META 1803</t>
-  </si>
-  <si>
     <t>DESIERTO DEL SAHARA 3706</t>
   </si>
   <si>
@@ -805,331 +868,370 @@
     <t>08-05-2008</t>
   </si>
   <si>
+    <t>18-06-2008</t>
+  </si>
+  <si>
     <t>05-06-1997</t>
   </si>
   <si>
     <t>28-01-1994</t>
   </si>
   <si>
+    <t>29-01-1999</t>
+  </si>
+  <si>
+    <t>05-01-1996</t>
+  </si>
+  <si>
     <t>08-12-1998</t>
   </si>
   <si>
-    <t>29-01-1999</t>
+    <t>18-05-1999</t>
   </si>
   <si>
     <t>12-04-2007</t>
   </si>
   <si>
+    <t>12-04-1992</t>
+  </si>
+  <si>
     <t>07-12-1998</t>
   </si>
   <si>
-    <t>05-01-1996</t>
-  </si>
-  <si>
-    <t>18-05-1999</t>
+    <t>02-04-2006</t>
+  </si>
+  <si>
+    <t>24-11-1998</t>
+  </si>
+  <si>
+    <t>15-05-1998</t>
+  </si>
+  <si>
+    <t>25-10-1989</t>
+  </si>
+  <si>
+    <t>15-09-2006</t>
   </si>
   <si>
     <t>29-10-1984</t>
   </si>
   <si>
-    <t>25-10-1989</t>
+    <t>30-09-1990</t>
+  </si>
+  <si>
+    <t>28-02-1992</t>
+  </si>
+  <si>
+    <t>07-12-1999</t>
+  </si>
+  <si>
+    <t>22-08-1977</t>
   </si>
   <si>
     <t>03-11-1986</t>
   </si>
   <si>
-    <t>12-04-1992</t>
-  </si>
-  <si>
-    <t>15-09-2006</t>
-  </si>
-  <si>
     <t>24-07-1983</t>
   </si>
   <si>
+    <t>03-01-2007</t>
+  </si>
+  <si>
+    <t>08-10-2000</t>
+  </si>
+  <si>
+    <t>27-03-1999</t>
+  </si>
+  <si>
+    <t>01-04-1992</t>
+  </si>
+  <si>
+    <t>19-11-1998</t>
+  </si>
+  <si>
+    <t>20-04-1982</t>
+  </si>
+  <si>
+    <t>08-03-1963</t>
+  </si>
+  <si>
+    <t>16-04-1996</t>
+  </si>
+  <si>
     <t>20-07-2001</t>
   </si>
   <si>
-    <t>16-04-1996</t>
-  </si>
-  <si>
-    <t>02-04-2006</t>
-  </si>
-  <si>
-    <t>24-11-1998</t>
-  </si>
-  <si>
-    <t>15-05-1998</t>
-  </si>
-  <si>
-    <t>01-04-1992</t>
-  </si>
-  <si>
-    <t>27-03-1999</t>
-  </si>
-  <si>
-    <t>22-08-1977</t>
+    <t>30-01-2003</t>
+  </si>
+  <si>
+    <t>24-06-1984</t>
+  </si>
+  <si>
+    <t>22-03-1999</t>
   </si>
   <si>
     <t>20-02-1987</t>
   </si>
   <si>
-    <t>30-01-2003</t>
-  </si>
-  <si>
-    <t>30-09-1990</t>
-  </si>
-  <si>
-    <t>28-02-1992</t>
-  </si>
-  <si>
-    <t>07-12-1999</t>
-  </si>
-  <si>
-    <t>03-01-2007</t>
-  </si>
-  <si>
-    <t>20-04-1982</t>
+    <t>06-08-2002</t>
+  </si>
+  <si>
+    <t>15-02-2004</t>
   </si>
   <si>
     <t>19-01-2000</t>
   </si>
   <si>
-    <t>19-11-1998</t>
-  </si>
-  <si>
-    <t>08-10-2000</t>
-  </si>
-  <si>
-    <t>08-03-1963</t>
-  </si>
-  <si>
-    <t>24-06-1984</t>
-  </si>
-  <si>
     <t>20-06-1989</t>
   </si>
   <si>
     <t>CRISALANCASTA_1985@GMAIL.COM</t>
   </si>
   <si>
+    <t>CG569407@GMAIL.COM</t>
+  </si>
+  <si>
     <t>GILGUTIERREZV013@GMAIL.COM</t>
   </si>
   <si>
     <t>JOSS0194@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>X61@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>YARELI.H9628@GMAIL.COM</t>
+  </si>
+  <si>
     <t>GAYTAN.ANIBAL@GMAIL.COM</t>
   </si>
   <si>
-    <t>X61@GMAIL.COM</t>
+    <t>ODALYSCHAPARRO40@GMAIL.COM</t>
   </si>
   <si>
     <t>RIVERA.LUGO.SE07@GMAIL.COM</t>
   </si>
   <si>
+    <t>ELI.GAYTTAN@GMAIL.COM</t>
+  </si>
+  <si>
     <t>TBRBEANS98@GMAIL.COM</t>
   </si>
   <si>
-    <t>YARELI.H9628@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ODALYSCHAPARRO40@GMAIL.COM</t>
+    <t>KAREEGD@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CARLOSBEL395@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NAOMI998@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MANUEL654@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VALERIAR150906@GMAIL.COM</t>
   </si>
   <si>
     <t>JULIO565@GMAIL.COM</t>
   </si>
   <si>
-    <t>MANUEL654@GMAIL.COM</t>
+    <t>EIMI09@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JOSEEDUA98@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALANEDU09@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VLOERASAEZ@GMAIL.COM</t>
   </si>
   <si>
     <t>LUIS_ADRIAN@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>GAYTAN023@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>VALERIAR150906@GMAIL.COM</t>
-  </si>
-  <si>
     <t>HEDER1930@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALISONMONTES00@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>THEHRHH@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AVILAGRECIA8@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>OLIVASNANCY086@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
+  </si>
+  <si>
+    <t>LEOTO056@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MARCO.MOLINAR3.@GMAIL.COM</t>
+  </si>
+  <si>
     <t>NAYELIHDZ2001@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>MARCO.MOLINAR3.@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>KAREEGD@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CARLOSBEL395@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>NAOMI998@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>AVILAGRECIA8@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>THEHRHH@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>VLOERASAEZ@GMAIL.COM</t>
+    <t>05.DOZAL.ANDREA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ROSYSOTO24@ICLOUD.COM</t>
+  </si>
+  <si>
+    <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
   </si>
   <si>
     <t>SILVAOLIVASM@GMAIL.COM</t>
   </si>
   <si>
-    <t>05.DOZAL.ANDREA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>EIMI09@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JOSEEDUA98@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ALANEDU09@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
+    <t>JONATHANGOMEZ4446@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CG8165424@GMAIL.COM</t>
   </si>
   <si>
     <t>LESLIEMILLA09@GMAIL.COM</t>
   </si>
   <si>
-    <t>OLIVASNANCY086@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ALISONMONTES00@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>LEOTO056@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ROSYSOTO34@ICLOUD.COM</t>
-  </si>
-  <si>
     <t>JESUSRUBEN201989@ICLOUD.COM</t>
   </si>
   <si>
     <t>16-04-2025 13:38:48</t>
   </si>
   <si>
+    <t>01-07-2025 19:06:32</t>
+  </si>
+  <si>
     <t>30-11-2025 11:31:22</t>
   </si>
   <si>
     <t>10-02-2025 17:19:45</t>
   </si>
   <si>
+    <t>02-01-2026 11:17:55</t>
+  </si>
+  <si>
+    <t>02-02-2026 12:19:55</t>
+  </si>
+  <si>
     <t>12-02-2025 19:17:51</t>
   </si>
   <si>
-    <t>02-01-2026 11:17:55</t>
+    <t>02-02-2026 12:27:34</t>
   </si>
   <si>
     <t>29-09-2025 19:06:54</t>
   </si>
   <si>
+    <t>04-02-2026 17:21:04</t>
+  </si>
+  <si>
     <t>30-01-2026 16:37:06</t>
   </si>
   <si>
-    <t>02-02-2026 12:19:55</t>
-  </si>
-  <si>
-    <t>02-02-2026 12:27:34</t>
+    <t>06-02-2026 10:13:27</t>
+  </si>
+  <si>
+    <t>06-02-2026 18:16:57</t>
+  </si>
+  <si>
+    <t>06-02-2026 18:20:37</t>
+  </si>
+  <si>
+    <t>04-02-2026 17:15:41</t>
+  </si>
+  <si>
+    <t>06-02-2026 10:10:46</t>
   </si>
   <si>
     <t>03-02-2026 11:45:26</t>
   </si>
   <si>
-    <t>04-02-2026 17:15:41</t>
+    <t>09-02-2026 16:30:52</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:34:00</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:46:37</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:05:24</t>
   </si>
   <si>
     <t>04-02-2026 06:30:38</t>
   </si>
   <si>
-    <t>04-02-2026 17:21:04</t>
-  </si>
-  <si>
-    <t>06-02-2026 10:10:46</t>
-  </si>
-  <si>
     <t>04-02-2026 15:22:46</t>
   </si>
   <si>
+    <t>09-02-2026 17:42:44</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:32:20</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:12:49</t>
+  </si>
+  <si>
+    <t>06-02-2026 14:00:17</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:21:10</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:13:05</t>
+  </si>
+  <si>
+    <t>11-02-2026 08:12:54</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:21:30</t>
+  </si>
+  <si>
     <t>05-02-2026 10:04:55</t>
   </si>
   <si>
-    <t>09-02-2026 14:21:30</t>
-  </si>
-  <si>
-    <t>06-02-2026 10:13:27</t>
-  </si>
-  <si>
-    <t>06-02-2026 18:16:57</t>
-  </si>
-  <si>
-    <t>06-02-2026 18:20:37</t>
-  </si>
-  <si>
-    <t>06-02-2026 14:00:17</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:12:49</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:05:24</t>
+    <t>10-02-2026 17:45:06</t>
+  </si>
+  <si>
+    <t>15-02-2026 10:57:33</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:04:34</t>
   </si>
   <si>
     <t>09-02-2026 11:22:59</t>
   </si>
   <si>
-    <t>10-02-2026 17:45:06</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:30:52</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:34:00</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:46:37</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:42:44</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:13:05</t>
+    <t>16-02-2026 17:44:53</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:12:24</t>
   </si>
   <si>
     <t>09-02-2026 18:00:59</t>
   </si>
   <si>
-    <t>09-02-2026 17:21:10</t>
-  </si>
-  <si>
-    <t>09-02-2026 18:32:20</t>
-  </si>
-  <si>
-    <t>11-02-2026 08:12:54</t>
-  </si>
-  <si>
-    <t>15-02-2026 10:57:33</t>
-  </si>
-  <si>
     <t>15-02-2026 11:10:14</t>
   </si>
   <si>
+    <t>Tarifas 2026 LE</t>
+  </si>
+  <si>
     <t>anualidad LE 300</t>
   </si>
   <si>
-    <t>Tarifas 2026 LE</t>
+    <t>inscripcion promo 199</t>
   </si>
   <si>
     <t>Forzoso</t>
@@ -1144,165 +1246,186 @@
     <t>PROMO FEBRERO 12 MESES</t>
   </si>
   <si>
+    <t>1 MES $899</t>
+  </si>
+  <si>
     <t>ANUALIDAD + MES REGALO $5,999</t>
   </si>
   <si>
+    <t>RECURRENTE $649 LE</t>
+  </si>
+  <si>
     <t>CONVENIOS $549</t>
   </si>
   <si>
-    <t>RECURRENTE $649 LE</t>
-  </si>
-  <si>
     <t>PLAN FAMILIA / AMIGOS X $499</t>
   </si>
   <si>
+    <t>3 MESES $1,899</t>
+  </si>
+  <si>
     <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
   </si>
   <si>
-    <t>3 MESES $1,899</t>
-  </si>
-  <si>
     <t>499</t>
   </si>
   <si>
+    <t>899</t>
+  </si>
+  <si>
     <t>461.46</t>
   </si>
   <si>
+    <t>649</t>
+  </si>
+  <si>
     <t>549</t>
   </si>
   <si>
-    <t>649</t>
+    <t>633</t>
   </si>
   <si>
     <t>1449</t>
   </si>
   <si>
-    <t>633</t>
-  </si>
-  <si>
     <t>02-02-2026 12:44:05</t>
   </si>
   <si>
+    <t>17-02-2026 19:16:14</t>
+  </si>
+  <si>
     <t>10-02-2026 19:16:06</t>
   </si>
   <si>
     <t>03-02-2026 07:23:51</t>
   </si>
   <si>
+    <t>09-02-2026 11:20:21</t>
+  </si>
+  <si>
+    <t>02-02-2026 12:24:36</t>
+  </si>
+  <si>
     <t>14-02-2026 09:21:50</t>
   </si>
   <si>
-    <t>09-02-2026 11:20:21</t>
+    <t>02-02-2026 12:31:44</t>
   </si>
   <si>
     <t>09-02-2026 17:45:36</t>
   </si>
   <si>
+    <t>04-02-2026 17:24:25</t>
+  </si>
+  <si>
     <t>02-02-2026 17:39:05</t>
   </si>
   <si>
-    <t>02-02-2026 12:24:36</t>
-  </si>
-  <si>
-    <t>02-02-2026 12:31:44</t>
+    <t>10-02-2026 05:11:01</t>
+  </si>
+  <si>
+    <t>11-02-2026 19:03:53</t>
+  </si>
+  <si>
+    <t>11-02-2026 19:04:57</t>
+  </si>
+  <si>
+    <t>04-02-2026 17:19:37</t>
+  </si>
+  <si>
+    <t>10-02-2026 05:14:42</t>
   </si>
   <si>
     <t>03-02-2026 11:51:04</t>
   </si>
   <si>
-    <t>04-02-2026 17:19:37</t>
+    <t>11-02-2026 16:42:43</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:44:25</t>
+  </si>
+  <si>
+    <t>09-02-2026 16:47:42</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:07:07</t>
   </si>
   <si>
     <t>04-02-2026 06:34:33</t>
   </si>
   <si>
-    <t>04-02-2026 17:24:25</t>
-  </si>
-  <si>
-    <t>10-02-2026 05:14:42</t>
-  </si>
-  <si>
     <t>04-02-2026 15:26:49</t>
   </si>
   <si>
+    <t>09-02-2026 17:47:57</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:40:18</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:19:08</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:29:47</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:23:56</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:19:33</t>
+  </si>
+  <si>
+    <t>11-02-2026 08:29:30</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:25:15</t>
+  </si>
+  <si>
     <t>09-02-2026 18:35:53</t>
   </si>
   <si>
-    <t>09-02-2026 14:25:15</t>
-  </si>
-  <si>
-    <t>10-02-2026 05:11:01</t>
-  </si>
-  <si>
-    <t>11-02-2026 19:03:53</t>
-  </si>
-  <si>
-    <t>11-02-2026 19:04:57</t>
-  </si>
-  <si>
-    <t>09-02-2026 14:29:47</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:19:08</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:07:07</t>
+    <t>10-02-2026 17:46:42</t>
+  </si>
+  <si>
+    <t>15-02-2026 11:04:14</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:10:12</t>
   </si>
   <si>
     <t>09-02-2026 11:26:28</t>
   </si>
   <si>
-    <t>10-02-2026 17:46:42</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:42:43</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:44:25</t>
-  </si>
-  <si>
-    <t>09-02-2026 16:47:42</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:47:57</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:19:33</t>
+    <t>16-02-2026 17:46:24</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:13:46</t>
   </si>
   <si>
     <t>09-02-2026 18:08:11</t>
   </si>
   <si>
-    <t>09-02-2026 17:23:56</t>
-  </si>
-  <si>
-    <t>09-02-2026 18:40:18</t>
-  </si>
-  <si>
-    <t>11-02-2026 08:29:30</t>
-  </si>
-  <si>
-    <t>15-02-2026 11:04:14</t>
-  </si>
-  <si>
     <t>15-02-2026 11:12:58</t>
   </si>
   <si>
     <t>02-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>17-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>10-03-2027 23:59:59</t>
   </si>
   <si>
     <t>03-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>09-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>14-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>09-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>04-03-2026 23:59:59</t>
   </si>
   <si>
@@ -1318,87 +1441,93 @@
     <t>15-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>02-02-2026 12:41:04</t>
   </si>
   <si>
     <t>03-02-2026 07:22:24</t>
   </si>
   <si>
+    <t>09-02-2026 11:19:32</t>
+  </si>
+  <si>
+    <t>02-02-2026 12:24:04</t>
+  </si>
+  <si>
     <t>14-02-2026 09:16:25</t>
   </si>
   <si>
-    <t>09-02-2026 11:19:32</t>
+    <t>02-02-2026 12:30:57</t>
+  </si>
+  <si>
+    <t>04-02-2026 17:23:58</t>
   </si>
   <si>
     <t>02-02-2026 17:37:49</t>
   </si>
   <si>
-    <t>02-02-2026 12:24:04</t>
-  </si>
-  <si>
-    <t>02-02-2026 12:30:57</t>
+    <t>10-02-2026 05:10:28</t>
   </si>
   <si>
     <t>04-02-2026 17:19:05</t>
   </si>
   <si>
+    <t>10-02-2026 05:13:41</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:42:01</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:43:52</t>
+  </si>
+  <si>
     <t>04-02-2026 06:33:26</t>
   </si>
   <si>
-    <t>04-02-2026 17:23:58</t>
-  </si>
-  <si>
-    <t>10-02-2026 05:13:41</t>
-  </si>
-  <si>
     <t>04-02-2026 15:26:11</t>
   </si>
   <si>
+    <t>09-02-2026 17:47:26</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:39:43</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:16:19</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:29:29</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:23:32</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:16:36</t>
+  </si>
+  <si>
+    <t>11-02-2026 08:28:18</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:23:33</t>
+  </si>
+  <si>
     <t>09-02-2026 18:34:57</t>
   </si>
   <si>
-    <t>09-02-2026 14:23:33</t>
-  </si>
-  <si>
-    <t>10-02-2026 05:10:28</t>
-  </si>
-  <si>
-    <t>09-02-2026 14:29:29</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:16:19</t>
+    <t>15-02-2026 11:01:26</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:08:30</t>
   </si>
   <si>
     <t>09-02-2026 11:25:37</t>
   </si>
   <si>
-    <t>11-02-2026 16:42:01</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:43:52</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:47:26</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:16:36</t>
-  </si>
-  <si>
     <t>09-02-2026 18:07:44</t>
   </si>
   <si>
-    <t>09-02-2026 17:23:32</t>
-  </si>
-  <si>
-    <t>09-02-2026 18:39:43</t>
-  </si>
-  <si>
-    <t>11-02-2026 08:28:18</t>
-  </si>
-  <si>
-    <t>15-02-2026 11:01:26</t>
-  </si>
-  <si>
     <t>15-02-2026 11:11:57</t>
   </si>
   <si>
@@ -1411,108 +1540,120 @@
     <t>26200522009480001296</t>
   </si>
   <si>
+    <t>26200522443750002097</t>
+  </si>
+  <si>
     <t>26200522246270001744</t>
   </si>
   <si>
     <t>26200522031990001330</t>
   </si>
   <si>
+    <t>26200522188810001604</t>
+  </si>
+  <si>
+    <t>26200522008710001292</t>
+  </si>
+  <si>
     <t>26200522344660001916</t>
   </si>
   <si>
-    <t>26200522188810001604</t>
+    <t>26200522008980001294</t>
   </si>
   <si>
     <t>26200522203750001652</t>
   </si>
   <si>
+    <t>26200522082280001431</t>
+  </si>
+  <si>
     <t>26200522019070001314</t>
   </si>
   <si>
-    <t>26200522008710001292</t>
-  </si>
-  <si>
-    <t>26200522008980001294</t>
+    <t>26200522216950001671</t>
+  </si>
+  <si>
+    <t>26200522275860001803</t>
+  </si>
+  <si>
+    <t>26200522275940001804</t>
+  </si>
+  <si>
+    <t>26200522081990001429</t>
+  </si>
+  <si>
+    <t>26200522217020001672</t>
   </si>
   <si>
     <t>26200522037480001340</t>
   </si>
   <si>
-    <t>26200522081990001429</t>
+    <t>26200522269260001777</t>
+  </si>
+  <si>
+    <t>26200522269350001778</t>
+  </si>
+  <si>
+    <t>26200522199520001636</t>
+  </si>
+  <si>
+    <t>26200522200740001643</t>
   </si>
   <si>
     <t>26200522067340001402</t>
   </si>
   <si>
-    <t>26200522082280001431</t>
-  </si>
-  <si>
-    <t>26200522217020001672</t>
-  </si>
-  <si>
     <t>26200522077360001418</t>
   </si>
   <si>
+    <t>26200522203900001653</t>
+  </si>
+  <si>
+    <t>26200522207950001662</t>
+  </si>
+  <si>
+    <t>26200522201590001646</t>
+  </si>
+  <si>
+    <t>26200522193120001614</t>
+  </si>
+  <si>
+    <t>26200522202050001649</t>
+  </si>
+  <si>
+    <t>26200522234120001697</t>
+  </si>
+  <si>
+    <t>26200522259660001758</t>
+  </si>
+  <si>
+    <t>26200522193020001613</t>
+  </si>
+  <si>
     <t>26200522207710001661</t>
   </si>
   <si>
-    <t>26200522193020001613</t>
-  </si>
-  <si>
-    <t>26200522216950001671</t>
-  </si>
-  <si>
-    <t>26200522275860001803</t>
-  </si>
-  <si>
-    <t>26200522275940001804</t>
-  </si>
-  <si>
-    <t>26200522193120001614</t>
-  </si>
-  <si>
-    <t>26200522201590001646</t>
-  </si>
-  <si>
-    <t>26200522200740001643</t>
+    <t>26200522241060001732</t>
+  </si>
+  <si>
+    <t>26200522364020001931</t>
+  </si>
+  <si>
+    <t>26200522443540002095</t>
   </si>
   <si>
     <t>26200522188970001605</t>
   </si>
   <si>
-    <t>26200522241060001732</t>
-  </si>
-  <si>
-    <t>26200522269260001777</t>
-  </si>
-  <si>
-    <t>26200522269350001778</t>
-  </si>
-  <si>
-    <t>26200522199520001636</t>
-  </si>
-  <si>
-    <t>26200522203900001653</t>
-  </si>
-  <si>
-    <t>26200522234120001697</t>
+    <t>26200522400880002009</t>
+  </si>
+  <si>
+    <t>26200522443700002096</t>
   </si>
   <si>
     <t>26200522205660001656</t>
   </si>
   <si>
-    <t>26200522202050001649</t>
-  </si>
-  <si>
-    <t>26200522207950001662</t>
-  </si>
-  <si>
-    <t>26200522259660001758</t>
-  </si>
-  <si>
-    <t>26200522364020001931</t>
-  </si>
-  <si>
     <t>26200522364120001933</t>
   </si>
   <si>
@@ -1543,16 +1684,16 @@
     <t>N/D</t>
   </si>
   <si>
+    <t>Ivonne Hernandez Rivera</t>
+  </si>
+  <si>
+    <t>Jesus Antonio Flores Torres</t>
+  </si>
+  <si>
     <t>Luis Alberto Pulido Teran</t>
   </si>
   <si>
     <t>Edgar Eduardo Perez Pillado</t>
-  </si>
-  <si>
-    <t>Ivonne Hernandez Rivera</t>
-  </si>
-  <si>
-    <t>Jesus Antonio Flores Torres</t>
   </si>
   <si>
     <t>sin rutina</t>
@@ -1916,7 +2057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -2013,82 +2154,82 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="G2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H2" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="I2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="J2" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K2" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="L2" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="M2" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="O2" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P2" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q2" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R2" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="S2" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="T2" t="s">
-        <v>434</v>
+        <v>476</v>
       </c>
       <c r="U2" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V2" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>464</v>
+        <v>507</v>
       </c>
       <c r="Y2" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="AA2" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB2" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC2" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -2096,73 +2237,73 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H3" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="J3" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K3" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="L3" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="M3" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="N3" t="s">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="O3" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="P3" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="Q3" t="s">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="R3" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="S3" t="s">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="U3" t="s">
-        <v>462</v>
+        <v>506</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>465</v>
+        <v>508</v>
       </c>
       <c r="AA3" t="s">
-        <v>506</v>
+        <v>418</v>
       </c>
       <c r="AB3" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC3" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -2170,82 +2311,73 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F4" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="G4" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H4" t="s">
-        <v>200</v>
-      </c>
-      <c r="I4" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="J4" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K4" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="L4" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="M4" t="s">
-        <v>336</v>
+        <v>365</v>
+      </c>
+      <c r="N4" t="s">
+        <v>404</v>
       </c>
       <c r="O4" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="P4" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="Q4" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="R4" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="S4" t="s">
-        <v>426</v>
-      </c>
-      <c r="T4" t="s">
-        <v>435</v>
+        <v>466</v>
       </c>
       <c r="U4" t="s">
-        <v>462</v>
-      </c>
-      <c r="V4" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>466</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="AA4" t="s">
-        <v>382</v>
+        <v>553</v>
       </c>
       <c r="AB4" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC4" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -2253,82 +2385,82 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F5" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G5" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="I5" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="J5" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K5" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="L5" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="M5" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="O5" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P5" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q5" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R5" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="S5" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
       <c r="T5" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="U5" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V5" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>467</v>
+        <v>510</v>
       </c>
       <c r="Y5" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
       <c r="AA5" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB5" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC5" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2336,85 +2468,85 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F6" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="G6" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H6" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="I6" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="J6" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K6" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="L6" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="M6" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="O6" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P6" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q6" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R6" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="S6" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="T6" t="s">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="U6" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V6" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>468</v>
+        <v>511</v>
       </c>
       <c r="Y6" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
       <c r="Z6" t="s">
-        <v>503</v>
+        <v>550</v>
       </c>
       <c r="AA6" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB6" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC6" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -2422,79 +2554,82 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G7" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H7" t="s">
-        <v>203</v>
+        <v>219</v>
+      </c>
+      <c r="I7" t="s">
+        <v>257</v>
       </c>
       <c r="J7" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="K7" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="L7" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="M7" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="N7" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="O7" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="P7" t="s">
-        <v>377</v>
+        <v>412</v>
       </c>
       <c r="Q7" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="R7" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="S7" t="s">
-        <v>428</v>
+        <v>464</v>
+      </c>
+      <c r="T7" t="s">
+        <v>479</v>
       </c>
       <c r="U7" t="s">
-        <v>462</v>
+        <v>505</v>
+      </c>
+      <c r="V7" t="s">
+        <v>505</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>469</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>501</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="AA7" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="AB7" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC7" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -2502,85 +2637,82 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F8" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="G8" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H8" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="I8" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="J8" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K8" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="L8" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="M8" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="O8" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P8" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q8" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R8" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="S8" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
       <c r="T8" t="s">
-        <v>438</v>
+        <v>480</v>
       </c>
       <c r="U8" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V8" t="s">
-        <v>462</v>
+        <v>506</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>470</v>
+        <v>513</v>
       </c>
       <c r="Y8" t="s">
-        <v>501</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>503</v>
+        <v>548</v>
       </c>
       <c r="AA8" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB8" t="s">
-        <v>509</v>
+        <v>555</v>
       </c>
       <c r="AC8" t="s">
-        <v>514</v>
+        <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -2588,82 +2720,82 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F9" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="G9" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H9" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="I9" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="J9" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K9" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="L9" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="M9" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="N9" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="O9" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="P9" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="Q9" t="s">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="R9" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="S9" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="T9" t="s">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="U9" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V9" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>471</v>
+        <v>514</v>
       </c>
       <c r="AA9" t="s">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="AB9" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="AC9" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -2671,82 +2803,79 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="F10" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="G10" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I10" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="J10" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K10" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="L10" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="M10" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="N10" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="O10" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="P10" t="s">
-        <v>378</v>
+        <v>413</v>
       </c>
       <c r="Q10" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="R10" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="S10" t="s">
-        <v>424</v>
-      </c>
-      <c r="T10" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="U10" t="s">
-        <v>462</v>
-      </c>
-      <c r="V10" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>472</v>
+        <v>515</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>548</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>551</v>
       </c>
       <c r="AA10" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="AB10" t="s">
-        <v>509</v>
+        <v>555</v>
       </c>
       <c r="AC10" t="s">
-        <v>514</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -2754,73 +2883,79 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F11" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G11" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H11" t="s">
-        <v>207</v>
+        <v>223</v>
+      </c>
+      <c r="I11" t="s">
+        <v>260</v>
       </c>
       <c r="J11" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="K11" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="L11" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="M11" t="s">
-        <v>343</v>
-      </c>
-      <c r="N11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O11" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="P11" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="Q11" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="R11" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="S11" t="s">
-        <v>426</v>
+        <v>470</v>
+      </c>
+      <c r="T11" t="s">
+        <v>482</v>
       </c>
       <c r="U11" t="s">
-        <v>462</v>
+        <v>505</v>
+      </c>
+      <c r="V11" t="s">
+        <v>506</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>473</v>
+        <v>516</v>
       </c>
       <c r="AA11" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="AB11" t="s">
-        <v>508</v>
+        <v>557</v>
       </c>
       <c r="AC11" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -2828,79 +2963,85 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="F12" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H12" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="I12" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="J12" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K12" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="L12" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="M12" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="O12" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P12" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="Q12" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R12" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="S12" t="s">
-        <v>429</v>
+        <v>464</v>
       </c>
       <c r="T12" t="s">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="U12" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V12" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>474</v>
+        <v>517</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>548</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>550</v>
       </c>
       <c r="AA12" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB12" t="s">
-        <v>508</v>
+        <v>558</v>
       </c>
       <c r="AC12" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -2908,82 +3049,85 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F13" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="G13" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H13" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="I13" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="J13" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="K13" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="L13" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="M13" t="s">
-        <v>345</v>
-      </c>
-      <c r="N13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="O13" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P13" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="Q13" t="s">
-        <v>386</v>
+        <v>417</v>
       </c>
       <c r="R13" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="S13" t="s">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="T13" t="s">
-        <v>442</v>
+        <v>484</v>
       </c>
       <c r="U13" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V13" t="s">
-        <v>462</v>
+        <v>506</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>475</v>
+        <v>518</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>548</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>552</v>
       </c>
       <c r="AA13" t="s">
-        <v>386</v>
+        <v>417</v>
       </c>
       <c r="AB13" t="s">
-        <v>508</v>
+        <v>559</v>
       </c>
       <c r="AC13" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -2991,79 +3135,79 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F14" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="G14" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H14" t="s">
-        <v>210</v>
-      </c>
-      <c r="I14" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="J14" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K14" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="L14" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="M14" t="s">
-        <v>346</v>
+        <v>375</v>
+      </c>
+      <c r="N14" t="s">
+        <v>403</v>
       </c>
       <c r="O14" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="P14" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="Q14" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="R14" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="S14" t="s">
-        <v>429</v>
-      </c>
-      <c r="T14" t="s">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="U14" t="s">
-        <v>462</v>
-      </c>
-      <c r="V14" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>476</v>
+        <v>519</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>548</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>550</v>
       </c>
       <c r="AA14" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="AB14" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC14" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -3071,85 +3215,79 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F15" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="G15" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H15" t="s">
-        <v>211</v>
-      </c>
-      <c r="I15" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="J15" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K15" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="L15" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="M15" t="s">
-        <v>347</v>
+        <v>376</v>
+      </c>
+      <c r="N15" t="s">
+        <v>403</v>
       </c>
       <c r="O15" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="P15" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="Q15" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="R15" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="S15" t="s">
-        <v>430</v>
-      </c>
-      <c r="T15" t="s">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="U15" t="s">
-        <v>462</v>
-      </c>
-      <c r="V15" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>477</v>
+        <v>520</v>
       </c>
       <c r="Y15" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
       <c r="Z15" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="AA15" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="AB15" t="s">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="AC15" t="s">
-        <v>514</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -3157,82 +3295,79 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F16" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="G16" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H16" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="I16" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="J16" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K16" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="L16" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="M16" t="s">
-        <v>348</v>
-      </c>
-      <c r="N16" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="O16" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="P16" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="Q16" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="R16" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="S16" t="s">
-        <v>429</v>
+        <v>470</v>
       </c>
       <c r="T16" t="s">
-        <v>445</v>
+        <v>485</v>
       </c>
       <c r="U16" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V16" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>478</v>
+        <v>521</v>
       </c>
       <c r="AA16" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="AB16" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC16" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -3240,82 +3375,85 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F17" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="G17" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H17" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="I17" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="J17" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K17" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="L17" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="M17" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="O17" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P17" t="s">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="Q17" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R17" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="S17" t="s">
-        <v>428</v>
+        <v>471</v>
       </c>
       <c r="T17" t="s">
-        <v>446</v>
+        <v>486</v>
       </c>
       <c r="U17" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V17" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
       <c r="Y17" t="s">
-        <v>502</v>
+        <v>548</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>552</v>
       </c>
       <c r="AA17" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB17" t="s">
-        <v>508</v>
+        <v>559</v>
       </c>
       <c r="AC17" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -3323,79 +3461,73 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F18" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="G18" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H18" t="s">
-        <v>214</v>
-      </c>
-      <c r="I18" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="J18" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K18" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="L18" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="M18" t="s">
-        <v>350</v>
+        <v>379</v>
+      </c>
+      <c r="N18" t="s">
+        <v>403</v>
       </c>
       <c r="O18" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="P18" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="Q18" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="R18" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="S18" t="s">
-        <v>428</v>
-      </c>
-      <c r="T18" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="U18" t="s">
-        <v>462</v>
-      </c>
-      <c r="V18" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="AA18" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="AB18" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="AC18" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -3403,85 +3535,85 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="G19" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H19" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="I19" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="J19" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K19" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="L19" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="M19" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="O19" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P19" t="s">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="Q19" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R19" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="S19" t="s">
-        <v>430</v>
+        <v>472</v>
       </c>
       <c r="T19" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
       <c r="U19" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V19" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="Y19" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
       <c r="Z19" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="AA19" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB19" t="s">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="AC19" t="s">
-        <v>514</v>
+        <v>560</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -3489,79 +3621,85 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F20" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G20" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H20" t="s">
-        <v>216</v>
+        <v>232</v>
+      </c>
+      <c r="I20" t="s">
+        <v>265</v>
       </c>
       <c r="J20" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K20" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="L20" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="M20" t="s">
-        <v>352</v>
-      </c>
-      <c r="N20" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="O20" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="P20" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="Q20" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="R20" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="S20" t="s">
-        <v>431</v>
+        <v>472</v>
+      </c>
+      <c r="T20" t="s">
+        <v>488</v>
       </c>
       <c r="U20" t="s">
-        <v>462</v>
+        <v>505</v>
+      </c>
+      <c r="V20" t="s">
+        <v>506</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>482</v>
+        <v>525</v>
       </c>
       <c r="Y20" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
       <c r="Z20" t="s">
-        <v>503</v>
+        <v>550</v>
       </c>
       <c r="AA20" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="AB20" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC20" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -3569,79 +3707,73 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="F21" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="G21" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H21" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="J21" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K21" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="L21" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="M21" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="N21" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="O21" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="P21" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="Q21" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="R21" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="S21" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="U21" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>483</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>501</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AA21" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="AB21" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC21" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -3649,82 +3781,73 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="F22" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="G22" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H22" t="s">
-        <v>218</v>
-      </c>
-      <c r="I22" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="J22" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K22" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="L22" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="M22" t="s">
-        <v>354</v>
+        <v>383</v>
+      </c>
+      <c r="N22" t="s">
+        <v>403</v>
       </c>
       <c r="O22" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="P22" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="Q22" t="s">
-        <v>382</v>
+        <v>422</v>
       </c>
       <c r="R22" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="S22" t="s">
-        <v>428</v>
-      </c>
-      <c r="T22" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="U22" t="s">
-        <v>462</v>
-      </c>
-      <c r="V22" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>484</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="AA22" t="s">
-        <v>382</v>
+        <v>554</v>
       </c>
       <c r="AB22" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC22" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -3732,79 +3855,82 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="F23" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="G23" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H23" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="I23" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="J23" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K23" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="L23" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="M23" t="s">
-        <v>355</v>
+        <v>384</v>
+      </c>
+      <c r="N23" t="s">
+        <v>403</v>
       </c>
       <c r="O23" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P23" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="Q23" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="R23" t="s">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="S23" t="s">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="T23" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="U23" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V23" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="W23" t="s">
         <v>2</v>
       </c>
       <c r="X23" t="s">
-        <v>485</v>
+        <v>528</v>
       </c>
       <c r="AA23" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="AB23" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC23" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -3812,73 +3938,82 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E24" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="F24" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="G24" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H24" t="s">
-        <v>220</v>
+        <v>236</v>
+      </c>
+      <c r="I24" t="s">
+        <v>267</v>
       </c>
       <c r="J24" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K24" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="L24" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="M24" t="s">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="N24" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="O24" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="P24" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="Q24" t="s">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="R24" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="S24" t="s">
-        <v>432</v>
+        <v>470</v>
+      </c>
+      <c r="T24" t="s">
+        <v>490</v>
       </c>
       <c r="U24" t="s">
-        <v>462</v>
+        <v>505</v>
+      </c>
+      <c r="V24" t="s">
+        <v>506</v>
       </c>
       <c r="W24" t="s">
         <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="AA24" t="s">
-        <v>507</v>
+        <v>420</v>
       </c>
       <c r="AB24" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC24" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -3886,79 +4021,79 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F25" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="G25" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H25" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="I25" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="J25" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="K25" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="L25" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="M25" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="O25" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P25" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q25" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R25" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="S25" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="T25" t="s">
-        <v>451</v>
+        <v>491</v>
       </c>
       <c r="U25" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V25" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W25" t="s">
         <v>2</v>
       </c>
       <c r="X25" t="s">
-        <v>487</v>
+        <v>530</v>
       </c>
       <c r="AA25" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB25" t="s">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="AC25" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -3966,73 +4101,79 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F26" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G26" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H26" t="s">
-        <v>222</v>
+        <v>238</v>
+      </c>
+      <c r="I26" t="s">
+        <v>269</v>
       </c>
       <c r="J26" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K26" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="L26" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="M26" t="s">
-        <v>358</v>
-      </c>
-      <c r="N26" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="O26" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="P26" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="Q26" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="R26" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="S26" t="s">
-        <v>430</v>
+        <v>468</v>
+      </c>
+      <c r="T26" t="s">
+        <v>492</v>
       </c>
       <c r="U26" t="s">
-        <v>462</v>
+        <v>505</v>
+      </c>
+      <c r="V26" t="s">
+        <v>505</v>
       </c>
       <c r="W26" t="s">
         <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="AA26" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="AB26" t="s">
-        <v>511</v>
+        <v>556</v>
       </c>
       <c r="AC26" t="s">
-        <v>514</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -4040,85 +4181,79 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E27" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="F27" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="G27" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H27" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="I27" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="J27" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K27" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="L27" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="M27" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="O27" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P27" t="s">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="Q27" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R27" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="S27" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="T27" t="s">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="U27" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V27" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W27" t="s">
         <v>2</v>
       </c>
       <c r="X27" t="s">
-        <v>489</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>501</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>503</v>
+        <v>532</v>
       </c>
       <c r="AA27" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB27" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC27" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -4126,85 +4261,82 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E28" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="G28" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H28" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="I28" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="J28" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="K28" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="L28" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="M28" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="O28" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P28" t="s">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="Q28" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R28" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="S28" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="T28" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="U28" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V28" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="W28" t="s">
         <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>490</v>
+        <v>533</v>
       </c>
       <c r="Y28" t="s">
-        <v>501</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>503</v>
+        <v>549</v>
       </c>
       <c r="AA28" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB28" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC28" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -4212,73 +4344,79 @@
         <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F29" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="G29" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H29" t="s">
-        <v>225</v>
+        <v>241</v>
+      </c>
+      <c r="I29" t="s">
+        <v>272</v>
       </c>
       <c r="J29" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="K29" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="L29" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="M29" t="s">
-        <v>361</v>
-      </c>
-      <c r="N29" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="O29" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="P29" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="Q29" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="R29" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="S29" t="s">
-        <v>428</v>
+        <v>468</v>
+      </c>
+      <c r="T29" t="s">
+        <v>495</v>
       </c>
       <c r="U29" t="s">
-        <v>462</v>
+        <v>505</v>
+      </c>
+      <c r="V29" t="s">
+        <v>506</v>
       </c>
       <c r="W29" t="s">
         <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="AA29" t="s">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="AB29" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC29" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -4286,79 +4424,79 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F30" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="G30" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H30" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="I30" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="J30" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K30" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="L30" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="M30" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="O30" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P30" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q30" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R30" t="s">
-        <v>416</v>
+        <v>452</v>
       </c>
       <c r="S30" t="s">
-        <v>428</v>
+        <v>471</v>
       </c>
       <c r="T30" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c r="U30" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V30" t="s">
-        <v>462</v>
+        <v>506</v>
       </c>
       <c r="W30" t="s">
         <v>2</v>
       </c>
       <c r="X30" t="s">
-        <v>492</v>
+        <v>535</v>
       </c>
       <c r="AA30" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB30" t="s">
-        <v>511</v>
+        <v>555</v>
       </c>
       <c r="AC30" t="s">
-        <v>514</v>
+        <v>560</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -4366,79 +4504,82 @@
         <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F31" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="G31" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H31" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="I31" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="J31" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="K31" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="L31" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="M31" t="s">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="O31" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P31" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q31" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R31" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="S31" t="s">
-        <v>430</v>
+        <v>472</v>
       </c>
       <c r="T31" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="U31" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V31" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W31" t="s">
         <v>2</v>
       </c>
       <c r="X31" t="s">
-        <v>493</v>
+        <v>536</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>549</v>
       </c>
       <c r="AA31" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB31" t="s">
-        <v>508</v>
+        <v>557</v>
       </c>
       <c r="AC31" t="s">
-        <v>513</v>
+        <v>561</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -4446,82 +4587,79 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F32" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="G32" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H32" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="I32" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="J32" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K32" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="L32" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="M32" t="s">
-        <v>364</v>
-      </c>
-      <c r="N32" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="O32" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="P32" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="Q32" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="R32" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="S32" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="T32" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="U32" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V32" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W32" t="s">
         <v>2</v>
       </c>
       <c r="X32" t="s">
-        <v>494</v>
+        <v>537</v>
       </c>
       <c r="AA32" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="AB32" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC32" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -4529,79 +4667,82 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F33" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G33" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H33" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="I33" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="J33" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K33" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="L33" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="M33" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
       <c r="O33" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P33" t="s">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="Q33" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R33" t="s">
-        <v>419</v>
+        <v>455</v>
       </c>
       <c r="S33" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="T33" t="s">
-        <v>457</v>
+        <v>499</v>
       </c>
       <c r="U33" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V33" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W33" t="s">
         <v>2</v>
       </c>
       <c r="X33" t="s">
-        <v>495</v>
+        <v>538</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>549</v>
       </c>
       <c r="AA33" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB33" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC33" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -4609,79 +4750,73 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F34" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G34" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H34" t="s">
-        <v>230</v>
-      </c>
-      <c r="I34" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="J34" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K34" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="L34" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="M34" t="s">
-        <v>366</v>
+        <v>395</v>
+      </c>
+      <c r="N34" t="s">
+        <v>403</v>
       </c>
       <c r="O34" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="P34" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="Q34" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="R34" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="S34" t="s">
-        <v>428</v>
-      </c>
-      <c r="T34" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="U34" t="s">
-        <v>462</v>
-      </c>
-      <c r="V34" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="W34" t="s">
         <v>2</v>
       </c>
       <c r="X34" t="s">
-        <v>496</v>
+        <v>539</v>
       </c>
       <c r="AA34" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="AB34" t="s">
-        <v>511</v>
+        <v>556</v>
       </c>
       <c r="AC34" t="s">
-        <v>514</v>
+        <v>561</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -4689,82 +4824,79 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E35" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F35" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="G35" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H35" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="I35" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="J35" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K35" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="L35" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="M35" t="s">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="O35" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P35" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q35" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R35" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="S35" t="s">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="T35" t="s">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="U35" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V35" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W35" t="s">
         <v>2</v>
       </c>
       <c r="X35" t="s">
-        <v>497</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="AA35" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB35" t="s">
-        <v>512</v>
+        <v>555</v>
       </c>
       <c r="AC35" t="s">
-        <v>514</v>
+        <v>560</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -4772,79 +4904,82 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E36" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F36" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="G36" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H36" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="I36" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="J36" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="K36" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="M36" t="s">
-        <v>368</v>
+        <v>397</v>
+      </c>
+      <c r="N36" t="s">
+        <v>405</v>
       </c>
       <c r="O36" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P36" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q36" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R36" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="S36" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="T36" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="U36" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V36" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="W36" t="s">
         <v>2</v>
       </c>
       <c r="X36" t="s">
-        <v>498</v>
+        <v>541</v>
       </c>
       <c r="AA36" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB36" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC36" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -4852,79 +4987,390 @@
         <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E37" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F37" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="G37" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="H37" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="I37" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="J37" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="K37" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="L37" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="O37" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="P37" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="Q37" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="R37" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="S37" t="s">
-        <v>433</v>
+        <v>468</v>
       </c>
       <c r="T37" t="s">
-        <v>461</v>
+        <v>502</v>
       </c>
       <c r="U37" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="V37" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="W37" t="s">
         <v>2</v>
       </c>
       <c r="X37" t="s">
-        <v>499</v>
+        <v>542</v>
       </c>
       <c r="AA37" t="s">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="AB37" t="s">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="AC37" t="s">
-        <v>513</v>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" t="s">
+        <v>182</v>
+      </c>
+      <c r="F38" t="s">
+        <v>210</v>
+      </c>
+      <c r="G38" t="s">
+        <v>213</v>
+      </c>
+      <c r="H38" t="s">
+        <v>250</v>
+      </c>
+      <c r="J38" t="s">
+        <v>281</v>
+      </c>
+      <c r="K38" t="s">
+        <v>319</v>
+      </c>
+      <c r="L38" t="s">
+        <v>359</v>
+      </c>
+      <c r="M38" t="s">
+        <v>399</v>
+      </c>
+      <c r="N38" t="s">
+        <v>403</v>
+      </c>
+      <c r="O38" t="s">
+        <v>407</v>
+      </c>
+      <c r="P38" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>421</v>
+      </c>
+      <c r="R38" t="s">
+        <v>460</v>
+      </c>
+      <c r="S38" t="s">
+        <v>475</v>
+      </c>
+      <c r="U38" t="s">
+        <v>505</v>
+      </c>
+      <c r="W38" t="s">
+        <v>2</v>
+      </c>
+      <c r="X38" t="s">
+        <v>543</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>421</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>558</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" t="s">
+        <v>153</v>
+      </c>
+      <c r="F39" t="s">
+        <v>211</v>
+      </c>
+      <c r="G39" t="s">
+        <v>213</v>
+      </c>
+      <c r="H39" t="s">
+        <v>251</v>
+      </c>
+      <c r="J39" t="s">
+        <v>281</v>
+      </c>
+      <c r="K39" t="s">
+        <v>320</v>
+      </c>
+      <c r="L39" t="s">
+        <v>360</v>
+      </c>
+      <c r="M39" t="s">
+        <v>400</v>
+      </c>
+      <c r="N39" t="s">
+        <v>403</v>
+      </c>
+      <c r="O39" t="s">
+        <v>407</v>
+      </c>
+      <c r="P39" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>418</v>
+      </c>
+      <c r="R39" t="s">
+        <v>461</v>
+      </c>
+      <c r="S39" t="s">
+        <v>465</v>
+      </c>
+      <c r="U39" t="s">
+        <v>506</v>
+      </c>
+      <c r="W39" t="s">
+        <v>2</v>
+      </c>
+      <c r="X39" t="s">
+        <v>544</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>418</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>555</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29">
+      <c r="A40" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" t="s">
+        <v>184</v>
+      </c>
+      <c r="F40" t="s">
+        <v>212</v>
+      </c>
+      <c r="G40" t="s">
+        <v>213</v>
+      </c>
+      <c r="H40" t="s">
+        <v>252</v>
+      </c>
+      <c r="I40" t="s">
+        <v>279</v>
+      </c>
+      <c r="J40" t="s">
+        <v>282</v>
+      </c>
+      <c r="K40" t="s">
+        <v>321</v>
+      </c>
+      <c r="L40" t="s">
+        <v>361</v>
+      </c>
+      <c r="M40" t="s">
+        <v>401</v>
+      </c>
+      <c r="N40" t="s">
+        <v>403</v>
+      </c>
+      <c r="O40" t="s">
+        <v>408</v>
+      </c>
+      <c r="P40" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>420</v>
+      </c>
+      <c r="R40" t="s">
+        <v>462</v>
+      </c>
+      <c r="S40" t="s">
+        <v>468</v>
+      </c>
+      <c r="T40" t="s">
+        <v>503</v>
+      </c>
+      <c r="U40" t="s">
+        <v>505</v>
+      </c>
+      <c r="V40" t="s">
+        <v>505</v>
+      </c>
+      <c r="W40" t="s">
+        <v>2</v>
+      </c>
+      <c r="X40" t="s">
+        <v>545</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>420</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>555</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
+      <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" t="s">
+        <v>148</v>
+      </c>
+      <c r="E41" t="s">
+        <v>181</v>
+      </c>
+      <c r="F41" t="s">
+        <v>207</v>
+      </c>
+      <c r="G41" t="s">
+        <v>213</v>
+      </c>
+      <c r="H41" t="s">
+        <v>253</v>
+      </c>
+      <c r="I41" t="s">
+        <v>280</v>
+      </c>
+      <c r="J41" t="s">
+        <v>281</v>
+      </c>
+      <c r="K41" t="s">
+        <v>322</v>
+      </c>
+      <c r="L41" t="s">
+        <v>362</v>
+      </c>
+      <c r="M41" t="s">
+        <v>402</v>
+      </c>
+      <c r="O41" t="s">
+        <v>406</v>
+      </c>
+      <c r="P41" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>417</v>
+      </c>
+      <c r="R41" t="s">
+        <v>463</v>
+      </c>
+      <c r="S41" t="s">
+        <v>474</v>
+      </c>
+      <c r="T41" t="s">
+        <v>504</v>
+      </c>
+      <c r="U41" t="s">
+        <v>505</v>
+      </c>
+      <c r="V41" t="s">
+        <v>506</v>
+      </c>
+      <c r="W41" t="s">
+        <v>2</v>
+      </c>
+      <c r="X41" t="s">
+        <v>546</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>417</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>555</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>326034</t>
+          <t>299297</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>96795</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GILBERTO</t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>DE LA ROSA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,67 +1435,79 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6141834791</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6143701479</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CENTAURO DEL NORTE</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>05-06-1997</t>
+          <t>26-08-2005</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GILGUTIERREZV013@GMAIL.COM</t>
+          <t>XIMENADELAROSA42@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30-11-2025 11:31:22</t>
+          <t>19-06-2025 09:42:01</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>anualidad LE 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:06</t>
+          <t>19-02-2026 12:14:40</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10-03-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>19-02-2026 11:40:58</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1503,14 +1515,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26200522246270001744</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26200522492700002183</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1662,12 +1682,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340085</t>
+          <t>340527</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EDNA ODALYS</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BARREA</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,32 +1717,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6143185738</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>C SALVADOR DIAZ CASAS 57</t>
-        </is>
-      </c>
+          <t>8112983028</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>18-05-1999</t>
+          <t>29-10-1984</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
+          <t>JULIO565@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-02-2026 12:27:34</t>
+          <t>03-02-2026 11:45:26</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1732,44 +1748,36 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-02-2026 12:31:44</t>
+          <t>03-02-2026 11:51:04</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-02-2026 12:30:57</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1777,14 +1785,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26200522008980001294</t>
+          <t>26200522037480001340</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1801,12 +1809,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>341105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1816,17 +1824,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAYELI ADAMARI </t>
+          <t>ELIANA JANETH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">GAYTAN </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1836,12 +1844,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6144630791</t>
+          <t>6146308375</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL SAENZ 14123</t>
+          <t>CALLE DELICIAS</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1851,17 +1859,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>20-07-2001</t>
+          <t>12-04-1992</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
+          <t>ELI.GAYTTAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>05-02-2026 10:04:55</t>
+          <t>04-02-2026 17:21:04</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1882,17 +1890,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-02-2026 18:35:53</t>
+          <t>04-02-2026 17:24:25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:57</t>
+          <t>04-02-2026 17:23:58</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1912,14 +1920,10 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26200522207710001661</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26200522082280001431</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1928,24 +1932,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341105</t>
+          <t>341259</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ELIANA JANETH</t>
+          <t xml:space="preserve">NAYELI ADAMARI </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAYTAN </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,12 +1979,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6146308375</t>
+          <t>6144630791</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CALLE DELICIAS</t>
+          <t>MIGUEL ANGEL SAENZ 14123</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1990,17 +1994,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12-04-1992</t>
+          <t>20-07-2001</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ELI.GAYTTAN@GMAIL.COM</t>
+          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>04-02-2026 17:21:04</t>
+          <t>05-02-2026 10:04:55</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2021,17 +2025,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-02-2026 17:24:25</t>
+          <t>09-02-2026 18:35:53</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>04-02-2026 17:23:58</t>
+          <t>09-02-2026 18:34:57</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2051,10 +2055,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26200522082280001431</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26200522207710001661</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2063,24 +2071,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340527</t>
+          <t>341037</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>HEDER ARTURO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,10 +2118,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8112983028</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6145315107</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASEOS DE JUAREZ </t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2121,17 +2133,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29-10-1984</t>
+          <t>24-07-1983</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JULIO565@GMAIL.COM</t>
+          <t>HEDER1930@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-02-2026 11:45:26</t>
+          <t>04-02-2026 15:22:46</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2141,36 +2153,44 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 11:51:04</t>
+          <t>04-02-2026 15:26:49</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>04-02-2026 15:26:11</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2178,36 +2198,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26200522037480001340</t>
+          <t>26200522077360001418</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341507</t>
+          <t>326034</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2217,17 +2237,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KARELIA EDITH</t>
+          <t>GILBERTO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GANDARILLA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2237,75 +2257,67 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6391727197</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>SAN JORGE 2600</t>
-        </is>
-      </c>
+          <t>6141834791</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>02-04-2006</t>
+          <t>05-06-1997</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>KAREEGD@GMAIL.COM</t>
+          <t>GILGUTIERREZV013@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>06-02-2026 10:13:27</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>30-11-2025 11:31:22</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>anualidad LE 300</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>10-02-2026 05:11:01</t>
+          <t>10-02-2026 19:16:06</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:10:28</t>
-        </is>
-      </c>
+          <t>10-03-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2313,44 +2325,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26200522216950001671</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522246270001744</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341037</t>
+          <t>340868</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2360,17 +2364,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HEDER ARTURO</t>
+          <t xml:space="preserve">LUIS ADRIAN </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2380,12 +2384,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6145315107</t>
+          <t>6142166555</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASEOS DE JUAREZ </t>
+          <t>CTO TERRANOVA 2803</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2395,17 +2399,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-07-1983</t>
+          <t>03-11-1986</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>HEDER1930@HOTMAIL.COM</t>
+          <t>LUIS_ADRIAN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>04-02-2026 15:22:46</t>
+          <t>04-02-2026 06:30:38</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2415,22 +2419,22 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>04-02-2026 15:26:49</t>
+          <t>04-02-2026 06:34:33</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2440,7 +2444,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>04-02-2026 15:26:11</t>
+          <t>04-02-2026 06:33:26</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2460,14 +2464,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26200522077360001418</t>
+          <t>26200522067340001402</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2484,12 +2488,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342110</t>
+          <t>341507</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2499,17 +2503,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MARIO EDGARDO</t>
+          <t>KARELIA EDITH</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>GANDARILLA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2519,32 +2523,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6144714471</t>
+          <t>6391727197</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CDA PUERTA DE GRANADA 2821</t>
+          <t>SAN JORGE 2600</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20-02-1987</t>
+          <t>02-04-2006</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>SILVAOLIVASM@GMAIL.COM</t>
+          <t>KAREEGD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 11:22:59</t>
+          <t>06-02-2026 10:13:27</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2555,7 +2559,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2565,17 +2569,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 11:26:28</t>
+          <t>10-02-2026 05:11:01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>09-02-2026 11:25:37</t>
+          <t>10-02-2026 05:10:28</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2585,7 +2589,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2595,11 +2599,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26200522188970001605</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26200522216950001671</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>499</t>
@@ -2607,24 +2619,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341661</t>
+          <t>341568</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2634,17 +2646,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>GRECIA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>CEBALLOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2654,67 +2666,75 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6142817080</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6142139312</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ERNESTO ESPINOZA 269</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>24-11-1998</t>
+          <t>01-04-1992</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CARLOSBEL395@GMAIL.COM</t>
+          <t>AVILAGRECIA8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>06-02-2026 18:16:57</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 14:00:17</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>11-02-2026 19:03:53</t>
+          <t>09-02-2026 14:29:47</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>09-02-2026 14:29:29</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2722,22 +2742,18 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26200522275860001803</t>
+          <t>26200522193120001614</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2754,12 +2770,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341663</t>
+          <t>341100</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2769,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NAOMI ALEJANDRA</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2789,67 +2805,75 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6145973271</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6142518849</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CALLE DELCIAS</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15-05-1998</t>
+          <t>25-10-1989</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NAOMI998@GMAIL.COM</t>
+          <t>MANUEL654@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>06-02-2026 18:20:37</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 17:15:41</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>11-02-2026 19:04:57</t>
+          <t>04-02-2026 17:19:37</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>04-02-2026 17:19:05</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2857,22 +2881,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26200522275940001804</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522081990001429</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2889,12 +2905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342298</t>
+          <t>278277</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>75778</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2904,17 +2920,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL </t>
+          <t xml:space="preserve">JAVIER OMAR </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOERA </t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2924,10 +2940,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6144270811</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6142791568</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>GARCILAZO DE LA VEGA 15300</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2935,56 +2955,60 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-08-1977</t>
+          <t>28-01-1994</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>VLOERASAEZ@GMAIL.COM</t>
+          <t>JOSS0194@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-02-2026 17:05:24</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2025 17:19:45</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-02-2026 17:07:07</t>
+          <t>03-02-2026 07:23:51</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>03-02-2026 07:22:24</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2992,14 +3016,18 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26200522200740001643</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>26200522031990001330</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3016,12 +3044,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341568</t>
+          <t>341661</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3031,17 +3059,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GRECIA</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CEBALLOS</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3051,75 +3079,67 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6142139312</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>ERNESTO ESPINOZA 269</t>
-        </is>
-      </c>
+          <t>6142817080</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>01-04-1992</t>
+          <t>24-11-1998</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>AVILAGRECIA8@GMAIL.COM</t>
+          <t>CARLOSBEL395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>06-02-2026 14:00:17</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>06-02-2026 18:16:57</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 14:29:47</t>
+          <t>11-02-2026 19:03:53</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>09-02-2026 14:29:29</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3127,18 +3147,22 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26200522193120001614</t>
+          <t>26200522275860001803</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3155,12 +3179,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340868</t>
+          <t>341663</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3170,17 +3194,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ADRIAN </t>
+          <t>NAOMI ALEJANDRA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3190,32 +3214,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6142166555</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>CTO TERRANOVA 2803</t>
-        </is>
-      </c>
+          <t>6145973271</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>03-11-1986</t>
+          <t>15-05-1998</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>LUIS_ADRIAN@HOTMAIL.COM</t>
+          <t>NAOMI998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-02-2026 06:30:38</t>
+          <t>06-02-2026 18:20:37</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3225,44 +3245,36 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-02-2026 06:34:33</t>
+          <t>11-02-2026 19:04:57</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>04-02-2026 06:33:26</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3270,14 +3282,22 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26200522067340001402</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26200522275940001804</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3294,12 +3314,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341100</t>
+          <t>342110</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3309,17 +3329,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t>MARIO EDGARDO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SANTOYO</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3329,12 +3349,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6142518849</t>
+          <t>6144714471</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CALLE DELCIAS</t>
+          <t>CDA PUERTA DE GRANADA 2821</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3344,17 +3364,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25-10-1989</t>
+          <t>20-02-1987</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MANUEL654@GMAIL.COM</t>
+          <t>SILVAOLIVASM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:41</t>
+          <t>09-02-2026 11:22:59</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3365,7 +3385,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3375,17 +3395,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>04-02-2026 17:19:37</t>
+          <t>09-02-2026 11:26:28</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>04-02-2026 17:19:05</t>
+          <t>09-02-2026 11:25:37</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3395,7 +3415,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3405,7 +3425,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26200522081990001429</t>
+          <t>26200522188970001605</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3429,12 +3449,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342364</t>
+          <t>340085</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3444,17 +3464,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CLAUDIA LESLIE</t>
+          <t>EDNA ODALYS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>BARREA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3464,12 +3484,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6143534589</t>
+          <t>6143185738</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CIUDAD DURANGO 31125</t>
+          <t>C SALVADOR DIAZ CASAS 57</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3479,17 +3499,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19-01-2000</t>
+          <t>18-05-1999</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>LESLIEMILLA09@GMAIL.COM</t>
+          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 18:00:59</t>
+          <t>02-02-2026 12:27:34</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3514,17 +3534,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-02-2026 18:08:11</t>
+          <t>02-02-2026 12:31:44</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>09-02-2026 18:07:44</t>
+          <t>02-02-2026 12:30:57</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3544,7 +3564,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26200522205660001656</t>
+          <t>26200522008980001294</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3556,12 +3576,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3731,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342260</t>
+          <t>342364</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3726,17 +3746,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t>CLAUDIA LESLIE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLALOBOS </t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3746,63 +3766,67 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6144616643</t>
+          <t>6143534589</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PROLETARIOS 19</t>
+          <t>CIUDAD DURANGO 31125</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>28-02-1992</t>
+          <t>19-01-2000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>JOSEEDUA98@GMAIL.COM</t>
+          <t>LESLIEMILLA09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>09-02-2026 18:00:59</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>11-02-2026 16:44:25</t>
+          <t>09-02-2026 18:08:11</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>11-02-2026 16:43:52</t>
+          <t>09-02-2026 18:07:44</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3812,7 +3836,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3822,22 +3846,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26200522269350001778</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522205660001656</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3854,12 +3870,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342280</t>
+          <t>342175</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3869,17 +3885,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ALAN EDUARDO</t>
+          <t>MARCO IVAN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TAMEZ</t>
+          <t xml:space="preserve">MOLINAR </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CANTU</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3889,10 +3905,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6146114137</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6141719602</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ERNESTO ESPINOZA 269</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3900,42 +3920,38 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>07-12-1999</t>
+          <t>16-04-1996</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ALANEDU09@GMAIL.COM</t>
+          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 16:46:37</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:21:30</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 16:47:42</t>
+          <t>09-02-2026 14:25:15</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3943,13 +3959,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>09-02-2026 14:23:33</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3957,14 +3981,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26200522199520001636</t>
+          <t>26200522193020001613</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3981,12 +4005,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342346</t>
+          <t>331503</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3996,17 +4020,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SOFIA VICTORIA</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>HERMOSILLO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4016,32 +4040,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6141631910</t>
+          <t>6143556958</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CAFETALES</t>
+          <t>MINA LOS REYES 3722</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>03-01-2007</t>
+          <t>29-01-1999</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
+          <t>X61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 17:42:44</t>
+          <t>02-01-2026 11:17:55</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4062,7 +4086,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:57</t>
+          <t>09-02-2026 11:20:21</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4072,7 +4096,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:26</t>
+          <t>09-02-2026 11:19:32</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4092,11 +4116,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26200522203900001653</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>26200522188810001604</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>499</t>
@@ -4104,24 +4136,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342395</t>
+          <t>342260</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4131,17 +4163,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ALISON</t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t xml:space="preserve">VILLALOBOS </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4151,32 +4183,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6142511165</t>
+          <t>6144616643</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MARK TWAIN 500</t>
+          <t>PROLETARIOS 19</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>08-10-2000</t>
+          <t>28-02-1992</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ALISONMONTES00@GMAIL.COM</t>
+          <t>JOSEEDUA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 18:32:20</t>
+          <t>09-02-2026 16:34:00</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4197,17 +4229,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 18:40:18</t>
+          <t>11-02-2026 16:44:25</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>09-02-2026 18:39:43</t>
+          <t>11-02-2026 16:43:52</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4217,7 +4249,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4227,11 +4259,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26200522207950001662</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26200522269350001778</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>499</t>
@@ -4239,24 +4279,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>342280</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>75778</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4266,17 +4306,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAVIER OMAR </t>
+          <t>ALAN EDUARDO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>TAMEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4286,14 +4326,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6142791568</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>GARCILAZO DE LA VEGA 15300</t>
-        </is>
-      </c>
+          <t>6146114137</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4301,60 +4337,56 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>28-01-1994</t>
+          <t>07-12-1999</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JOSS0194@HOTMAIL.COM</t>
+          <t>ALANEDU09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-02-2025 17:19:45</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>09-02-2026 16:46:37</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>03-02-2026 07:23:51</t>
+          <t>09-02-2026 16:47:42</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>03-02-2026 07:22:24</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4362,18 +4394,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26200522031990001330</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522199520001636</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4390,12 +4418,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>331503</t>
+          <t>342346</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4405,17 +4433,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>SOFIA VICTORIA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HERMOSILLO</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4425,32 +4453,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6143556958</t>
+          <t>6141631910</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MINA LOS REYES 3722</t>
+          <t>CAFETALES</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>29-01-1999</t>
+          <t>03-01-2007</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X61@GMAIL.COM</t>
+          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-01-2026 11:17:55</t>
+          <t>09-02-2026 17:42:44</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4471,7 +4499,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:20:21</t>
+          <t>09-02-2026 17:47:57</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4481,7 +4509,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:32</t>
+          <t>09-02-2026 17:47:26</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4501,19 +4529,11 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26200522188810001604</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522203900001653</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
           <t>499</t>
@@ -4521,24 +4541,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>341505</t>
+          <t>342395</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4548,17 +4568,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARBARA </t>
+          <t>ALISON</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4568,12 +4588,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6143682180</t>
+          <t>6142511165</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SAN JORGE 2600</t>
+          <t>MARK TWAIN 500</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4583,17 +4603,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15-09-2006</t>
+          <t>08-10-2000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>VALERIAR150906@GMAIL.COM</t>
+          <t>ALISONMONTES00@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>06-02-2026 10:10:46</t>
+          <t>09-02-2026 18:32:20</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4614,17 +4634,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 05:14:42</t>
+          <t>09-02-2026 18:40:18</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10-02-2026 05:13:41</t>
+          <t>09-02-2026 18:39:43</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4634,7 +4654,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4644,19 +4664,11 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26200522217020001672</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522207950001662</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
           <t>499</t>
@@ -4664,7 +4676,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4676,12 +4688,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342175</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4691,17 +4703,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MARCO IVAN</t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLINAR </t>
+          <t>DOZAL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CANTU</t>
+          <t>CHACON</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4711,75 +4723,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6141719602</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>ERNESTO ESPINOZA 269</t>
-        </is>
-      </c>
+          <t>6563497877</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>16-04-1996</t>
+          <t>30-01-2003</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
+          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 14:21:30</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>10-02-2026 17:45:06</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 14:25:15</t>
+          <t>10-02-2026 17:46:42</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>09-02-2026 14:23:33</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4787,36 +4791,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26200522193020001613</t>
+          <t>26200522241060001732</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>344209</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4826,17 +4830,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ELBA</t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4846,10 +4850,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6141057797</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6143682180</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SAN JORGE 2600</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4857,56 +4865,60 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>01-06-1967</t>
+          <t>15-09-2006</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MARIAHDZ67000@HOTMAIL.COM</t>
+          <t>VALERIAR150906@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:53</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 10:10:46</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:06</t>
+          <t>10-02-2026 05:14:42</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:13:41</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4914,7 +4926,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26200522467120002145</t>
+          <t>26200522217020001672</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4924,17 +4936,17 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
+          <t>DIANA EDITH BARRAZA DURAN</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4946,12 +4958,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342308</t>
+          <t>343806</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4961,17 +4973,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DANIEL ANTONIO</t>
+          <t>JESUS RUBEN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERRANO </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4981,12 +4993,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6271210648</t>
+          <t>6141109571</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>REPUBLICA DOMINICANA 20</t>
+          <t>DESIERTO DEL SAHARA 3706</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4996,17 +5008,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>27-03-1999</t>
+          <t>20-06-1989</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>THEHRHH@GMAIL.COM</t>
+          <t>JESUSRUBEN201989@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 17:12:49</t>
+          <t>15-02-2026 11:10:14</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5017,7 +5029,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5027,17 +5039,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 17:19:08</t>
+          <t>15-02-2026 11:12:58</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>09-02-2026 17:16:19</t>
+          <t>15-02-2026 11:11:57</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5057,7 +5069,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26200522201590001646</t>
+          <t>26200522364120001933</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5081,12 +5093,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342761</t>
+          <t>342308</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5096,17 +5108,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>DANIEL ANTONIO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DOZAL</t>
+          <t xml:space="preserve">SERRANO </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CHACON</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5116,67 +5128,75 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6563497877</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6271210648</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>REPUBLICA DOMINICANA 20</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>30-01-2003</t>
+          <t>27-03-1999</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
+          <t>THEHRHH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10-02-2026 17:45:06</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:12:49</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10-02-2026 17:46:42</t>
+          <t>09-02-2026 17:19:08</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:16:19</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5184,36 +5204,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26200522241060001732</t>
+          <t>26200522201590001646</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342661</t>
+          <t>344200</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5223,17 +5243,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ALONSO </t>
+          <t>MAGDALENA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORDERO </t>
+          <t>BALDERRAMA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>AVELAR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5243,63 +5263,67 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6143546193</t>
+          <t>6391115826</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MONTE ALTAI 4323</t>
+          <t>COL SANTO NIÑO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>20-04-1982</t>
+          <t>10-01-1971</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
+          <t>MAGDAURIBE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-02-2026 15:13:05</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>16-02-2026 17:13:45</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-02-2026 15:19:33</t>
+          <t>18-02-2026 18:02:37</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>10-02-2026 15:16:36</t>
+          <t>18-02-2026 18:01:54</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5309,7 +5333,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5319,14 +5343,22 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26200522234120001697</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26200522471160002153</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5343,12 +5375,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343806</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5358,17 +5390,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JESUS RUBEN</t>
+          <t xml:space="preserve">RAFAEL </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">LOERA </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>SAEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5378,14 +5410,10 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6141109571</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>DESIERTO DEL SAHARA 3706</t>
-        </is>
-      </c>
+          <t>6144270811</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5393,60 +5421,56 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>20-06-1989</t>
+          <t>22-08-1977</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JESUSRUBEN201989@ICLOUD.COM</t>
+          <t>VLOERASAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>15-02-2026 11:10:14</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>09-02-2026 17:05:24</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>15-02-2026 11:12:58</t>
+          <t>09-02-2026 17:07:07</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>15-02-2026 11:11:57</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5454,14 +5478,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26200522364120001933</t>
+          <t>26200522200740001643</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5478,12 +5502,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344200</t>
+          <t>342661</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5493,17 +5517,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MAGDALENA</t>
+          <t xml:space="preserve">JOSE ALONSO </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BALDERRAMA</t>
+          <t xml:space="preserve">CORDERO </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AVELAR</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5513,67 +5537,63 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6391115826</t>
+          <t>6143546193</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COL SANTO NIÑO</t>
+          <t>MONTE ALTAI 4323</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>10-01-1971</t>
+          <t>20-04-1982</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MAGDAURIBE10@HOTMAIL.COM</t>
+          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16-02-2026 17:13:45</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:13:05</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>18-02-2026 18:02:37</t>
+          <t>10-02-2026 15:19:33</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>18-02-2026 18:01:54</t>
+          <t>10-02-2026 15:16:36</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5583,7 +5603,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5593,22 +5613,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26200522471160002153</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522234120001697</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5625,12 +5637,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344234</t>
+          <t>344674</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5640,7 +5652,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>JONATHA IVAN</t>
+          <t>ABRAHM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5650,7 +5662,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5660,10 +5672,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6141324957</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6147767384</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CALLE DOLORES PIMENTEL</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5671,56 +5687,64 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>22-03-1999</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
+          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 17:44:53</t>
+          <t>17-02-2026 19:04:34</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>16-02-2026 17:46:24</t>
+          <t>17-02-2026 19:10:12</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:08:30</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5728,36 +5752,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26200522400880002009</t>
+          <t>26200522443540002095</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344677</t>
+          <t>342319</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5767,17 +5791,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">OLIVAS </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5787,67 +5811,75 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6144072330</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6491107772</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>REPUBLICA DOMINICANA</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15-02-2004</t>
+          <t>19-11-1998</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CG8165424@GMAIL.COM</t>
+          <t>OLIVASNANCY086@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>17-02-2026 19:12:24</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:21:10</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-02-2026 19:13:46</t>
+          <t>09-02-2026 17:23:56</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:23:32</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5855,36 +5887,36 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26200522443700002096</t>
+          <t>26200522202050001649</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344674</t>
+          <t>342901</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>20718</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5894,17 +5926,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ABRAHM</t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5914,39 +5946,35 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6147767384</t>
+          <t>6142443644</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CALLE DOLORES PIMENTEL</t>
+          <t>PRIV DE GONZALEZ COSSIO 6734</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22-03-1999</t>
+          <t>08-03-1963</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
+          <t>LEOTO056@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>17-02-2026 19:04:34</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 08:12:54</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5964,17 +5992,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>17-02-2026 19:10:12</t>
+          <t>11-02-2026 08:29:30</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>17-02-2026 19:08:30</t>
+          <t>11-02-2026 08:28:18</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5994,10 +6022,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26200522443540002095</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>26200522259660001758</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6006,24 +6038,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342319</t>
+          <t>344209</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6033,17 +6065,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>ELBA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVAS </t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6053,14 +6085,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6491107772</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>REPUBLICA DOMINICANA</t>
-        </is>
-      </c>
+          <t>6141057797</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6068,60 +6096,56 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>19-11-1998</t>
+          <t>01-06-1967</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>OLIVASNANCY086@GMAIL.COM</t>
+          <t>MARIAHDZ67000@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:10</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>16-02-2026 17:19:53</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:56</t>
+          <t>18-02-2026 16:45:06</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:23:32</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6129,36 +6153,44 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26200522202050001649</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+          <t>26200522467120002145</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>344234</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6168,17 +6200,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t>JONATHA IVAN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6188,75 +6220,67 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6142443644</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>PRIV DE GONZALEZ COSSIO 6734</t>
-        </is>
-      </c>
+          <t>6141324957</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>08-03-1963</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>LEOTO056@GMAIL.COM</t>
+          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>11-02-2026 08:12:54</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>16-02-2026 17:44:53</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>11-02-2026 08:29:30</t>
+          <t>16-02-2026 17:46:24</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>11-02-2026 08:28:18</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6264,23 +6288,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26200522259660001758</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26200522400880002009</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6427,12 +6447,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344116</t>
+          <t>344677</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6442,17 +6462,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LOZOYA</t>
+          <t>MORELOS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6462,28 +6482,28 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6143978047</t>
+          <t>6144072330</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21-10-1996</t>
+          <t>15-02-2004</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>SUGEYPONLOZ@GMAIL.COM</t>
+          <t>CG8165424@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-02-2026 15:12:06</t>
+          <t>17-02-2026 19:12:24</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6498,28 +6518,28 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>18-02-2026 15:52:54</t>
+          <t>17-02-2026 19:13:46</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -6530,30 +6550,157 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
+          <t>26200522443700002096</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>344116</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21933</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PONCE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>LOZOYA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6143978047</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>21-10-1996</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>SUGEYPONLOZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>16-02-2026 15:12:06</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>18-02-2026 15:52:54</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
           <t>26200522464950002139</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>Rubi Esmeralda  Martinez Alcala</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>279168</t>
+          <t>133116</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t>LUIS DAVID</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">URIBE </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>BALDERRAMA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,33 +613,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6142760908</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6391894082</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>43 1/2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16-11-1992</t>
+          <t>23-02-2005</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ARACELYTRUJILLO26@GMAIL.COM</t>
+          <t>LILLUCHO10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>17-02-2025 15:57:01</t>
+          <t>05-11-2022 09:19:53</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -649,28 +653,28 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18-02-2026 07:29:15</t>
+          <t>23-02-2026 06:06:52</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -681,32 +685,24 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26200522456240002117</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522566540002297</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1114,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>288404</t>
+          <t>303219</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>85902</t>
+          <t>718</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRISTIAN ALAN</t>
+          <t>ADAN ENRIQUE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>LOYA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6144545766</t>
+          <t>6141522107</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ALCATIFA 15115</t>
+          <t>CUENCA DEL CONCHOS 6805</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1168,20 +1164,24 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>08-05-2008</t>
+          <t>31-01-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CRISALANCASTA_1985@GMAIL.COM</t>
+          <t>ADAN.RAMIREZ1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16-04-2025 13:38:48</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>10-07-2025 09:58:09</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 12:44:05</t>
+          <t>23-02-2026 11:23:51</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-02-2026 12:41:04</t>
+          <t>23-02-2026 11:22:05</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200522009480001296</t>
+          <t>26200522576970002310</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
@@ -1682,12 +1682,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340527</t>
+          <t>288404</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>85902</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>CRISTIAN ALAN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1717,10 +1717,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8112983028</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6144545766</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ALCATIFA 15115</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1728,56 +1732,60 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>29-10-1984</t>
+          <t>08-05-2008</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JULIO565@GMAIL.COM</t>
+          <t>CRISALANCASTA_1985@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-02-2026 11:45:26</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>16-04-2025 13:38:48</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-02-2026 11:51:04</t>
+          <t>02-02-2026 12:44:05</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-02-2026 12:41:04</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1785,24 +1793,28 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26200522037480001340</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
+          <t>26200522009480001296</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1956,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>279168</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>76669</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,7 +1971,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAYELI ADAMARI </t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1969,7 +1981,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,14 +1991,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6144630791</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MIGUEL ANGEL SAENZ 14123</t>
-        </is>
-      </c>
+          <t>6142760908</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1994,60 +2002,56 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20-07-2001</t>
+          <t>16-11-1992</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
+          <t>ARACELYTRUJILLO26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>05-02-2026 10:04:55</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>17-02-2025 15:57:01</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>09-02-2026 18:35:53</t>
+          <t>18-02-2026 07:29:15</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:34:57</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2055,40 +2059,44 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26200522207710001661</t>
+          <t>26200522456240002117</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341037</t>
+          <t>340527</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2106,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HEDER ARTURO</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,14 +2126,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6145315107</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PASEOS DE JUAREZ </t>
-        </is>
-      </c>
+          <t>8112983028</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2133,17 +2137,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24-07-1983</t>
+          <t>29-10-1984</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>HEDER1930@HOTMAIL.COM</t>
+          <t>JULIO565@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>04-02-2026 15:22:46</t>
+          <t>03-02-2026 11:45:26</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2153,44 +2157,36 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-02-2026 15:26:49</t>
+          <t>03-02-2026 11:51:04</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>04-02-2026 15:26:11</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2198,36 +2194,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26200522077360001418</t>
+          <t>26200522037480001340</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>326034</t>
+          <t>341507</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2237,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GILBERTO</t>
+          <t>KARELIA EDITH</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GANDARILLA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2257,67 +2253,75 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6141834791</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6391727197</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SAN JORGE 2600</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>05-06-1997</t>
+          <t>02-04-2006</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>GILGUTIERREZV013@GMAIL.COM</t>
+          <t>KAREEGD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>30-11-2025 11:31:22</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>anualidad LE 300</t>
-        </is>
-      </c>
+          <t>06-02-2026 10:13:27</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:06</t>
+          <t>10-02-2026 05:11:01</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>10-03-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:10:28</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2325,36 +2329,44 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26200522246270001744</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26200522216950001671</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340868</t>
+          <t>341661</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,17 +2376,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ADRIAN </t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2384,14 +2396,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6142166555</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CTO TERRANOVA 2803</t>
-        </is>
-      </c>
+          <t>6142817080</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2399,17 +2407,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>03-11-1986</t>
+          <t>24-11-1998</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>LUIS_ADRIAN@HOTMAIL.COM</t>
+          <t>CARLOSBEL395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>04-02-2026 06:30:38</t>
+          <t>06-02-2026 18:16:57</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2419,44 +2427,36 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>04-02-2026 06:34:33</t>
+          <t>11-02-2026 19:03:53</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>04-02-2026 06:33:26</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2464,14 +2464,22 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26200522067340001402</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26200522275860001803</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2488,12 +2496,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341507</t>
+          <t>341663</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2503,17 +2511,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KARELIA EDITH</t>
+          <t>NAOMI ALEJANDRA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GANDARILLA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2523,14 +2531,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6391727197</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>SAN JORGE 2600</t>
-        </is>
-      </c>
+          <t>6145973271</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2538,60 +2542,56 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>02-04-2006</t>
+          <t>15-05-1998</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>KAREEGD@GMAIL.COM</t>
+          <t>NAOMI998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>06-02-2026 10:13:27</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>06-02-2026 18:20:37</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>10-02-2026 05:11:01</t>
+          <t>11-02-2026 19:04:57</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:10:28</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26200522216950001671</t>
+          <t>26200522275940001804</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2609,34 +2609,34 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341568</t>
+          <t>340868</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GRECIA</t>
+          <t xml:space="preserve">LUIS ADRIAN </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CEBALLOS</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2666,35 +2666,39 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6142139312</t>
+          <t>6142166555</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ERNESTO ESPINOZA 269</t>
+          <t>CTO TERRANOVA 2803</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>01-04-1992</t>
+          <t>03-11-1986</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>AVILAGRECIA8@GMAIL.COM</t>
+          <t>LUIS_ADRIAN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>06-02-2026 14:00:17</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>04-02-2026 06:30:38</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2702,27 +2706,27 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 14:29:47</t>
+          <t>04-02-2026 06:34:33</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>09-02-2026 14:29:29</t>
+          <t>04-02-2026 06:33:26</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2742,18 +2746,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26200522193120001614</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26200522067340001402</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2770,12 +2770,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341100</t>
+          <t>341037</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t>HEDER ARTURO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTOYO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6142518849</t>
+          <t>6145315107</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CALLE DELCIAS</t>
+          <t xml:space="preserve">PASEOS DE JUAREZ </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2820,38 +2820,42 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25-10-1989</t>
+          <t>24-07-1983</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MANUEL654@GMAIL.COM</t>
+          <t>HEDER1930@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:41</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>04-02-2026 15:22:46</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-02-2026 17:19:37</t>
+          <t>04-02-2026 15:26:49</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2861,7 +2865,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>04-02-2026 17:19:05</t>
+          <t>04-02-2026 15:26:11</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2881,14 +2885,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26200522081990001429</t>
+          <t>26200522077360001418</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2905,12 +2909,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>341259</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>75778</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2920,17 +2924,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAVIER OMAR </t>
+          <t xml:space="preserve">NAYELI ADAMARI </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2940,32 +2944,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6142791568</t>
+          <t>6144630791</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GARCILAZO DE LA VEGA 15300</t>
+          <t>MIGUEL ANGEL SAENZ 14123</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>28-01-1994</t>
+          <t>20-07-2001</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JOSS0194@HOTMAIL.COM</t>
+          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10-02-2025 17:19:45</t>
+          <t>05-02-2026 10:04:55</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2976,7 +2980,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2986,17 +2990,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-02-2026 07:23:51</t>
+          <t>09-02-2026 18:35:53</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>03-02-2026 07:22:24</t>
+          <t>09-02-2026 18:34:57</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3016,12 +3020,12 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26200522031990001330</t>
+          <t>26200522207710001661</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE RECORRIDO</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr"/>
@@ -3044,12 +3048,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341661</t>
+          <t>342256</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3059,17 +3063,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>EIMY ANAHI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t xml:space="preserve">TOBARA </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>ALCANTAR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3079,53 +3083,53 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6142817080</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6145118271</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ALAMEDAS 311</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>24-11-1998</t>
+          <t>30-09-1990</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CARLOSBEL395@GMAIL.COM</t>
+          <t>EIMI09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>06-02-2026 18:16:57</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:30:52</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>11-02-2026 19:03:53</t>
+          <t>11-02-2026 16:42:43</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3133,13 +3137,21 @@
           <t>11-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>11-02-2026 16:42:01</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3147,7 +3159,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26200522275860001803</t>
+          <t>26200522269260001777</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3162,7 +3174,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3179,12 +3191,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341663</t>
+          <t>341568</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3194,17 +3206,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NAOMI ALEJANDRA</t>
+          <t>GRECIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>CEBALLOS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3214,10 +3226,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6145973271</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6142139312</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ERNESTO ESPINOZA 269</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3225,56 +3241,60 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>15-05-1998</t>
+          <t>01-04-1992</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>NAOMI998@GMAIL.COM</t>
+          <t>AVILAGRECIA8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>06-02-2026 18:20:37</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 14:00:17</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>11-02-2026 19:04:57</t>
+          <t>09-02-2026 14:29:47</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>09-02-2026 14:29:29</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3282,22 +3302,18 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26200522275940001804</t>
+          <t>26200522193120001614</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3314,12 +3330,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342110</t>
+          <t>341100</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3329,17 +3345,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARIO EDGARDO</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3349,12 +3365,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6144714471</t>
+          <t>6142518849</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CDA PUERTA DE GRANADA 2821</t>
+          <t>CALLE DELCIAS</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3364,17 +3380,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20-02-1987</t>
+          <t>25-10-1989</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SILVAOLIVASM@GMAIL.COM</t>
+          <t>MANUEL654@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 11:22:59</t>
+          <t>04-02-2026 17:15:41</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3385,7 +3401,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3395,17 +3411,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-02-2026 11:26:28</t>
+          <t>04-02-2026 17:19:37</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>09-02-2026 11:25:37</t>
+          <t>04-02-2026 17:19:05</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3415,7 +3431,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3425,7 +3441,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26200522188970001605</t>
+          <t>26200522081990001429</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3449,12 +3465,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340085</t>
+          <t>342260</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3464,17 +3480,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EDNA ODALYS</t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t xml:space="preserve">VILLALOBOS </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BARREA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3484,67 +3500,63 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6143185738</t>
+          <t>6144616643</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C SALVADOR DIAZ CASAS 57</t>
+          <t>PROLETARIOS 19</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18-05-1999</t>
+          <t>28-02-1992</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
+          <t>JOSEEDUA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-02-2026 12:27:34</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:34:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-02-2026 12:31:44</t>
+          <t>11-02-2026 16:44:25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-02-2026 12:30:57</t>
+          <t>11-02-2026 16:43:52</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3554,7 +3566,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3564,36 +3576,44 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26200522008980001294</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26200522269350001778</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342256</t>
+          <t>342280</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3603,17 +3623,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EIMY ANAHI</t>
+          <t>ALAN EDUARDO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOBARA </t>
+          <t>TAMEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALCANTAR</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3623,75 +3643,67 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6145118271</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>ALAMEDAS 311</t>
-        </is>
-      </c>
+          <t>6146114137</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>30-09-1990</t>
+          <t>07-12-1999</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>EIMI09@GMAIL.COM</t>
+          <t>ALANEDU09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 16:30:52</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>09-02-2026 16:46:37</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>11-02-2026 16:42:43</t>
+          <t>09-02-2026 16:47:42</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>11-02-2026 16:42:01</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3699,22 +3711,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26200522269260001777</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522199520001636</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3731,12 +3735,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342364</t>
+          <t>342346</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3746,17 +3750,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CLAUDIA LESLIE</t>
+          <t>SOFIA VICTORIA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3766,12 +3770,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6143534589</t>
+          <t>6141631910</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CIUDAD DURANGO 31125</t>
+          <t>CAFETALES</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3781,42 +3785,38 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19-01-2000</t>
+          <t>03-01-2007</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>LESLIEMILLA09@GMAIL.COM</t>
+          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 18:00:59</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:42:44</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>09-02-2026 18:08:11</t>
+          <t>09-02-2026 17:47:57</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>09-02-2026 18:07:44</t>
+          <t>09-02-2026 17:47:26</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3846,36 +3846,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26200522205660001656</t>
+          <t>26200522203900001653</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342175</t>
+          <t>342395</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARCO IVAN</t>
+          <t>ALISON</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLINAR </t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CANTU</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6141719602</t>
+          <t>6142511165</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ERNESTO ESPINOZA 269</t>
+          <t>MARK TWAIN 500</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>16-04-1996</t>
+          <t>08-10-2000</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
+          <t>ALISONMONTES00@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 14:21:30</t>
+          <t>09-02-2026 18:32:20</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 14:25:15</t>
+          <t>09-02-2026 18:40:18</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>09-02-2026 14:23:33</t>
+          <t>09-02-2026 18:39:43</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26200522193020001613</t>
+          <t>26200522207950001662</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3993,24 +3993,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>331503</t>
+          <t>278277</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>75778</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4020,17 +4020,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t xml:space="preserve">JAVIER OMAR </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HERMOSILLO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6143556958</t>
+          <t>6142791568</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MINA LOS REYES 3722</t>
+          <t>GARCILAZO DE LA VEGA 15300</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4055,17 +4055,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>29-01-1999</t>
+          <t>28-01-1994</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>X61@GMAIL.COM</t>
+          <t>JOSS0194@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-01-2026 11:17:55</t>
+          <t>10-02-2025 17:19:45</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4086,17 +4086,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-02-2026 11:20:21</t>
+          <t>03-02-2026 07:23:51</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:32</t>
+          <t>03-02-2026 07:22:24</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26200522188810001604</t>
+          <t>26200522031990001330</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4124,11 +4124,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>499</t>
@@ -4148,12 +4144,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342260</t>
+          <t>326034</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4163,17 +4159,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t>GILBERTO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLALOBOS </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4183,14 +4179,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6144616643</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>PROLETARIOS 19</t>
-        </is>
-      </c>
+          <t>6141834791</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4198,60 +4190,56 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>28-02-1992</t>
+          <t>05-06-1997</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>JOSEEDUA98@GMAIL.COM</t>
+          <t>GILGUTIERREZV013@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>30-11-2025 11:31:22</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>anualidad LE 300</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>11-02-2026 16:44:25</t>
+          <t>10-02-2026 19:16:06</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>11-02-2026 16:43:52</t>
-        </is>
-      </c>
+          <t>10-03-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4259,22 +4247,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26200522269350001778</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522246270001744</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4291,12 +4271,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342280</t>
+          <t>342110</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4306,17 +4286,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ALAN EDUARDO</t>
+          <t>MARIO EDGARDO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TAMEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4326,10 +4306,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6146114137</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6144714471</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CDA PUERTA DE GRANADA 2821</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4337,42 +4321,38 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>07-12-1999</t>
+          <t>20-02-1987</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ALANEDU09@GMAIL.COM</t>
+          <t>SILVAOLIVASM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 16:46:37</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 11:22:59</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 16:47:42</t>
+          <t>09-02-2026 11:26:28</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4380,13 +4360,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>09-02-2026 11:25:37</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4394,14 +4382,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26200522199520001636</t>
+          <t>26200522188970001605</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4418,12 +4406,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342346</t>
+          <t>342175</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4433,17 +4421,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SOFIA VICTORIA</t>
+          <t>MARCO IVAN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">MOLINAR </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>CANTU</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4453,32 +4441,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6141631910</t>
+          <t>6141719602</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CAFETALES</t>
+          <t>ERNESTO ESPINOZA 269</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>03-01-2007</t>
+          <t>16-04-1996</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
+          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:42:44</t>
+          <t>09-02-2026 14:21:30</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4489,7 +4477,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4499,7 +4487,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:57</t>
+          <t>09-02-2026 14:25:15</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4509,7 +4497,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:26</t>
+          <t>09-02-2026 14:23:33</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4529,7 +4517,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26200522203900001653</t>
+          <t>26200522193020001613</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4541,24 +4529,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342395</t>
+          <t>342364</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4568,17 +4556,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ALISON</t>
+          <t>CLAUDIA LESLIE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4588,12 +4576,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6142511165</t>
+          <t>6143534589</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MARK TWAIN 500</t>
+          <t>CIUDAD DURANGO 31125</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4603,38 +4591,42 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>08-10-2000</t>
+          <t>19-01-2000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ALISONMONTES00@GMAIL.COM</t>
+          <t>LESLIEMILLA09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 18:32:20</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>09-02-2026 18:00:59</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 18:40:18</t>
+          <t>09-02-2026 18:08:11</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4644,7 +4636,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>09-02-2026 18:39:43</t>
+          <t>09-02-2026 18:07:44</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4664,36 +4656,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26200522207950001662</t>
+          <t>26200522205660001656</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342761</t>
+          <t>331503</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4703,17 +4695,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DOZAL</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CHACON</t>
+          <t>HERMOSILLO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4723,67 +4715,75 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6563497877</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6143556958</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>MINA LOS REYES 3722</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30-01-2003</t>
+          <t>29-01-1999</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
+          <t>X61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-02-2026 17:45:06</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-01-2026 11:17:55</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10-02-2026 17:46:42</t>
+          <t>09-02-2026 11:20:21</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>09-02-2026 11:19:32</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4791,36 +4791,44 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26200522241060001732</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26200522188810001604</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>341505</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4830,17 +4838,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARBARA </t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DOZAL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>CHACON</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4850,14 +4858,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6143682180</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>SAN JORGE 2600</t>
-        </is>
-      </c>
+          <t>6563497877</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4865,38 +4869,42 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>15-09-2006</t>
+          <t>30-01-2003</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VALERIAR150906@GMAIL.COM</t>
+          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>06-02-2026 10:10:46</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>10-02-2026 17:45:06</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 05:14:42</t>
+          <t>10-02-2026 17:46:42</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4904,21 +4912,13 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:13:41</t>
-        </is>
-      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4926,27 +4926,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26200522217020001672</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522241060001732</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4958,12 +4950,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343806</t>
+          <t>340085</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4973,17 +4965,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JESUS RUBEN</t>
+          <t>EDNA ODALYS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>BARREA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4993,63 +4985,67 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6141109571</t>
+          <t>6143185738</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DESIERTO DEL SAHARA 3706</t>
+          <t>C SALVADOR DIAZ CASAS 57</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>20-06-1989</t>
+          <t>18-05-1999</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JESUSRUBEN201989@ICLOUD.COM</t>
+          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15-02-2026 11:10:14</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>02-02-2026 12:27:34</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>15-02-2026 11:12:58</t>
+          <t>02-02-2026 12:31:44</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>15-02-2026 11:11:57</t>
+          <t>02-02-2026 12:30:57</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5059,7 +5055,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5069,36 +5065,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26200522364120001933</t>
+          <t>26200522008980001294</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342308</t>
+          <t>343806</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5108,17 +5104,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DANIEL ANTONIO</t>
+          <t>JESUS RUBEN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERRANO </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5128,12 +5124,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6271210648</t>
+          <t>6141109571</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>REPUBLICA DOMINICANA 20</t>
+          <t>DESIERTO DEL SAHARA 3706</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5143,17 +5139,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>27-03-1999</t>
+          <t>20-06-1989</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>THEHRHH@GMAIL.COM</t>
+          <t>JESUSRUBEN201989@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:12:49</t>
+          <t>15-02-2026 11:10:14</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5164,7 +5160,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5174,17 +5170,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:19:08</t>
+          <t>15-02-2026 11:12:58</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:16:19</t>
+          <t>15-02-2026 11:11:57</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5204,7 +5200,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26200522201590001646</t>
+          <t>26200522364120001933</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5228,12 +5224,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344200</t>
+          <t>344167</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5243,17 +5239,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MAGDALENA</t>
+          <t>JONATHAN MANUEL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BALDERRAMA</t>
+          <t>MARUNGO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AVELAR</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5263,79 +5259,67 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6391115826</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>COL SANTO NIÑO</t>
-        </is>
-      </c>
+          <t>6142467576</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>10-01-1971</t>
+          <t>19-06-1985</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>MAGDAURIBE10@HOTMAIL.COM</t>
+          <t>TIJUANAMHMARUNGO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16-02-2026 17:13:45</t>
+          <t>16-02-2026 16:31:02</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>18-02-2026 18:02:37</t>
+          <t>23-02-2026 16:25:12</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:01:54</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5343,7 +5327,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26200522471160002153</t>
+          <t>26200522586990002331</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5358,29 +5342,29 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342298</t>
+          <t>344164</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5390,17 +5374,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL </t>
+          <t>KAROL AMAIRANY</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOERA </t>
+          <t>SIFUENTES</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAEZ</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5410,33 +5394,33 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6144270811</t>
+          <t>6145128509</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>22-08-1977</t>
+          <t>21-01-1999</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>VLOERASAEZ@GMAIL.COM</t>
+          <t>TIJUANAMARUNGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 17:05:24</t>
+          <t>16-02-2026 16:26:56</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -5446,28 +5430,28 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-02-2026 17:07:07</t>
+          <t>23-02-2026 16:21:52</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -5478,36 +5462,44 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26200522200740001643</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26200522586800002330</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342661</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5517,17 +5509,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ALONSO </t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORDERO </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5537,32 +5529,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6143546193</t>
+          <t>6143682180</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MONTE ALTAI 4323</t>
+          <t>SAN JORGE 2600</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>20-04-1982</t>
+          <t>15-09-2006</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
+          <t>VALERIAR150906@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10-02-2026 15:13:05</t>
+          <t>06-02-2026 10:10:46</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5573,7 +5565,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5583,7 +5575,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10-02-2026 15:19:33</t>
+          <t>10-02-2026 05:14:42</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5593,7 +5585,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>10-02-2026 15:16:36</t>
+          <t>10-02-2026 05:13:41</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5613,11 +5605,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26200522234120001697</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26200522217020001672</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>499</t>
@@ -5625,24 +5625,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344674</t>
+          <t>344070</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5652,17 +5652,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ABRAHM</t>
+          <t>DORIAN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t xml:space="preserve">RESENDIZ </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5672,79 +5672,67 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6147767384</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>CALLE DOLORES PIMENTEL</t>
-        </is>
-      </c>
+          <t>3315999428</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>22-03-1999</t>
+          <t>12-10-2005</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
+          <t>DORIAN_ROMERO@JABIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17-02-2026 19:04:34</t>
+          <t>16-02-2026 13:29:06</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>17-02-2026 19:10:12</t>
+          <t>23-02-2026 13:26:14</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>17-02-2026 19:08:30</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5752,14 +5740,22 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26200522443540002095</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+          <t>26200522580570002314</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5776,12 +5772,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342319</t>
+          <t>344118</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5791,17 +5787,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>ABRIL PAOLA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVAS </t>
+          <t>GALLEGOS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>TARANGO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5811,14 +5807,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6491107772</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>REPUBLICA DOMINICANA</t>
-        </is>
-      </c>
+          <t>6147370020</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5826,60 +5818,56 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19-11-1998</t>
+          <t>23-07-2003</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>OLIVASNANCY086@GMAIL.COM</t>
+          <t>ABRILPG19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:10</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>16-02-2026 15:15:42</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:56</t>
+          <t>23-02-2026 16:28:38</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:23:32</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5887,36 +5875,44 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26200522202050001649</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>26200522587190002333</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>344200</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5926,17 +5922,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t>MAGDALENA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>BALDERRAMA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>AVELAR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5946,12 +5942,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6142443644</t>
+          <t>6391115826</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PRIV DE GONZALEZ COSSIO 6734</t>
+          <t>COL SANTO NIÑO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5961,48 +5957,52 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>08-03-1963</t>
+          <t>10-01-1971</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>LEOTO056@GMAIL.COM</t>
+          <t>MAGDAURIBE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>11-02-2026 08:12:54</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>16-02-2026 17:13:45</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>11-02-2026 08:29:30</t>
+          <t>18-02-2026 18:02:37</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>11-02-2026 08:28:18</t>
+          <t>18-02-2026 18:01:54</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6022,40 +6022,44 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26200522259660001758</t>
+          <t>26200522471160002153</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344209</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6065,17 +6069,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ELBA</t>
+          <t xml:space="preserve">RAFAEL </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t xml:space="preserve">LOERA </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SAEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6085,28 +6089,28 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6141057797</t>
+          <t>6144270811</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>01-06-1967</t>
+          <t>22-08-1977</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>MARIAHDZ67000@HOTMAIL.COM</t>
+          <t>VLOERASAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:53</t>
+          <t>09-02-2026 17:05:24</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6121,22 +6125,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:06</t>
+          <t>09-02-2026 17:07:07</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>09-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -6153,44 +6157,36 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26200522467120002145</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522200740001643</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344234</t>
+          <t>342308</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6200,17 +6196,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JONATHA IVAN</t>
+          <t>DANIEL ANTONIO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t xml:space="preserve">SERRANO </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6220,10 +6216,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6141324957</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6271210648</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>REPUBLICA DOMINICANA 20</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6231,56 +6231,60 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>27-03-1999</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
+          <t>THEHRHH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-02-2026 17:44:53</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:12:49</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-02-2026 17:46:24</t>
+          <t>09-02-2026 17:19:08</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:16:19</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6288,36 +6292,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26200522400880002009</t>
+          <t>26200522201590001646</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343805</t>
+          <t>344674</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6327,17 +6331,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA IRENE </t>
+          <t>ABRAHM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6347,35 +6351,39 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6143813334</t>
+          <t>6147767384</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>RIO META 1803</t>
+          <t>CALLE DOLORES PIMENTEL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>24-06-1984</t>
+          <t>22-03-1999</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ROSYSOTO24@ICLOUD.COM</t>
+          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>15-02-2026 10:57:33</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>17-02-2026 19:04:34</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6393,17 +6401,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>15-02-2026 11:04:14</t>
+          <t>17-02-2026 19:10:12</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>15-02-2026 11:01:26</t>
+          <t>17-02-2026 19:08:30</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6423,7 +6431,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26200522364020001931</t>
+          <t>26200522443540002095</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6447,12 +6455,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344677</t>
+          <t>342319</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6462,17 +6470,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">OLIVAS </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6482,67 +6490,75 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6144072330</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6491107772</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>REPUBLICA DOMINICANA</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15-02-2004</t>
+          <t>19-11-1998</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CG8165424@GMAIL.COM</t>
+          <t>OLIVASNANCY086@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>17-02-2026 19:12:24</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:21:10</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>17-02-2026 19:13:46</t>
+          <t>09-02-2026 17:23:56</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:23:32</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6550,157 +6566,1642 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26200522443700002096</t>
+          <t>26200522202050001649</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>345838</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>88003</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ESMERALDA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>VILLALBA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>LASCANO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6144743555</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MONTES ALPES 11914</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>22-03-1994</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>ESMERALDA_220229@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:31:03</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:57:07</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:54:58</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26200522585800002325</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>342661</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20478</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE ALONSO </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORDERO </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CHAPARRO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6143546193</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MONTE ALTAI 4323</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>20-04-1982</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:13:05</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:19:33</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:16:36</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26200522234120001697</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>345942</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>88107</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ADRIANA AURORA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MARQUEZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6143970735</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>09-02-2002</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>ADRIANA72270@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:47:34</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:48:54</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26200522592530002354</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>342901</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20718</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LETICIA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>HOLGUIN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6142443644</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PRIV DE GONZALEZ COSSIO 6734</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>08-03-1963</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>LEOTO056@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>11-02-2026 08:12:54</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>11-02-2026 08:29:30</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>11-02-2026 08:28:18</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26200522259660001758</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Flores Torres</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>345907</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>88072</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>JAIMIE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>VALVERDE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6144790343</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CHE GUEVARA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>16-08-2004</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:09:43</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:14:20</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:13:54</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26200522590120002343</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>345918</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>88083</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>JESSER URIEL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PORTILLO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6141611733</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MINA GLAMIS 1914</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>20-04-2001</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>URIELPORTILLO951@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:21:49</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:29:11</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:27:48</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26200522590980002346</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>344209</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>22026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ELBA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GUERRERO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6141057797</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>01-06-1967</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>MARIAHDZ67000@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:19:53</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:45:06</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26200522467120002145</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>343805</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21622</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROSA IRENE </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NAJERA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6143813334</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>RIO META 1803</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>24-06-1984</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>ROSYSOTO24@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>15-02-2026 10:57:33</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:04:14</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:01:26</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26200522364020001931</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>345906</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>88071</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ESLY YAZMIN</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALVERDE </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6142830714</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>CHE GUEVARA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>19-01-1997</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>YAZMINREYES566@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:09:02</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:16:35</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:16:04</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26200522590290002344</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>344234</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>22051</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>JONATHA IVAN</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOMEZ </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SUAREZ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6141324957</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>06-08-2002</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:44:53</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:46:24</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26200522400880002009</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>344116</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>21933</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>SEND CHIH</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>NANCY</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>PONCE</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>LOZOYA</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>6143978047</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>21-10-1996</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>SUGEYPONLOZ@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>16-02-2026 15:12:06</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Tarifas 2026 LE</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Sin contrato</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>CONVENIOS $549</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>18-02-2026 15:52:54</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr">
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>26200522464950002139</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>Rubi Esmeralda  Martinez Alcala</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>344677</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>22494</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CARLOS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>MORELOS</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6144072330</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>15-02-2004</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>CG8165424@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:12:24</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:13:46</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26200522443700002096</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -709,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301635</t>
+          <t>303219</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99133</t>
+          <t>718</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">YODGAR JASIEL </t>
+          <t>ADAN ENRIQUE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LOYA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,10 +744,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6146099932</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6141522107</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CUENCA DEL CONCHOS 6805</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -755,56 +759,64 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>18-06-2008</t>
+          <t>31-01-1997</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CG569407@GMAIL.COM</t>
+          <t>ADAN.RAMIREZ1@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-07-2025 19:06:32</t>
+          <t>10-07-2025 09:58:09</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>17-02-2026 19:16:14</t>
+          <t>23-02-2026 11:23:51</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23-02-2026 11:22:05</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -812,36 +824,40 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26200522443750002097</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26200522576970002310</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>278704</t>
+          <t>340080</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>76205</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -851,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ANIBAL</t>
+          <t>YARELI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GAYTAN</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -871,63 +887,67 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8129739105</t>
+          <t>6142757940</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CALLE FRANCISCO PIMENTEL 5115</t>
+          <t>C RUBEN JARAMILLO 214</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>08-12-1998</t>
+          <t>05-01-1996</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>GAYTAN.ANIBAL@GMAIL.COM</t>
+          <t>YARELI.H9628@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12-02-2025 19:17:51</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>02-02-2026 12:19:55</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>14-02-2026 09:21:50</t>
+          <t>02-02-2026 12:24:36</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>14-02-2026 09:16:25</t>
+          <t>02-02-2026 12:24:04</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -937,7 +957,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -947,18 +967,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26200522344660001916</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522008710001292</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -975,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340080</t>
+          <t>339397</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YARELI</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>LOERA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CABALLERO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,57 +1026,53 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6142757940</t>
+          <t>6143368528</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C RUBEN JARAMILLO 214</t>
+          <t>CALLE DE METER 5510</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>05-01-1996</t>
+          <t>07-12-1998</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>YARELI.H9628@GMAIL.COM</t>
+          <t>TBRBEANS98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 12:19:55</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>30-01-2026 16:37:06</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 12:24:36</t>
+          <t>02-02-2026 17:39:05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1070,7 +1082,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 12:24:04</t>
+          <t>02-02-2026 17:37:49</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1090,36 +1102,44 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26200522008710001292</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26200522019070001314</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>303219</t>
+          <t>301635</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>99133</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,17 +1149,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADAN ENRIQUE</t>
+          <t xml:space="preserve">YODGAR JASIEL </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LOYA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1149,14 +1169,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6141522107</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CUENCA DEL CONCHOS 6805</t>
-        </is>
-      </c>
+          <t>6146099932</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1164,64 +1180,56 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31-01-1997</t>
+          <t>18-06-2008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ADAN.RAMIREZ1@HOTMAIL.COM</t>
+          <t>CG569407@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10-07-2025 09:58:09</t>
+          <t>01-07-2025 19:06:32</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>23-02-2026 11:23:51</t>
+          <t>17-02-2026 19:16:14</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>23-02-2026 11:22:05</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1229,18 +1237,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200522576970002310</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522443750002097</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1257,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>339397</t>
+          <t>288404</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>85902</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1272,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>CRISTIAN ALAN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LOERA</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CABALLERO</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1292,12 +1296,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6143368528</t>
+          <t>6144545766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CALLE DE METER 5510</t>
+          <t>ALCATIFA 15115</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,17 +1311,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>07-12-1998</t>
+          <t>08-05-2008</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>TBRBEANS98@GMAIL.COM</t>
+          <t>CRISALANCASTA_1985@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30-01-2026 16:37:06</t>
+          <t>16-04-2025 13:38:48</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1338,7 +1342,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 17:39:05</t>
+          <t>02-02-2026 12:44:05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1348,7 +1352,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-02-2026 17:37:49</t>
+          <t>02-02-2026 12:41:04</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1358,7 +1362,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1368,19 +1372,15 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26200522019070001314</t>
+          <t>26200522009480001296</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>499</t>
@@ -1388,24 +1388,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>299297</t>
+          <t>341105</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>96795</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t>ELIANA JANETH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DE LA ROSA</t>
+          <t xml:space="preserve">GAYTAN </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6143701479</t>
+          <t>6146308375</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CENTAURO DEL NORTE</t>
+          <t>CALLE DELICIAS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,24 +1450,20 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26-08-2005</t>
+          <t>12-04-1992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>XIMENADELAROSA42@GMAIL.COM</t>
+          <t>ELI.GAYTTAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>19-06-2025 09:42:01</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>04-02-2026 17:21:04</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1475,7 +1471,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1485,17 +1481,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>19-02-2026 12:14:40</t>
+          <t>04-02-2026 17:24:25</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>19-02-2026 11:40:58</t>
+          <t>04-02-2026 17:23:58</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1515,19 +1511,11 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26200522492700002183</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522082280001431</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>499</t>
@@ -1535,24 +1523,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>316379</t>
+          <t>340527</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1562,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LUGO</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1582,7 +1570,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6144687095</t>
+          <t>8112983028</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1593,17 +1581,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12-04-2007</t>
+          <t>29-10-1984</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>RIVERA.LUGO.SE07@GMAIL.COM</t>
+          <t>JULIO565@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>29-09-2025 19:06:54</t>
+          <t>03-02-2026 11:45:26</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1628,12 +1616,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>09-02-2026 17:45:36</t>
+          <t>03-02-2026 11:51:04</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1650,19 +1638,11 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26200522203750001652</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>IVONNE HERNANDEZ RIVERA</t>
-        </is>
-      </c>
+          <t>26200522037480001340</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1670,24 +1650,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>288404</t>
+          <t>279168</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>85902</t>
+          <t>76669</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1697,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRISTIAN ALAN</t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1717,75 +1697,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6144545766</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ALCATIFA 15115</t>
-        </is>
-      </c>
+          <t>6142760908</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>08-05-2008</t>
+          <t>16-11-1992</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CRISALANCASTA_1985@GMAIL.COM</t>
+          <t>ARACELYTRUJILLO26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>16-04-2025 13:38:48</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>17-02-2025 15:57:01</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-02-2026 12:44:05</t>
+          <t>18-02-2026 07:29:15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-02-2026 12:41:04</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1793,40 +1765,44 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26200522009480001296</t>
+          <t>26200522456240002117</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341105</t>
+          <t>341507</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1836,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ELIANA JANETH</t>
+          <t>KARELIA EDITH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAYTAN </t>
+          <t>GANDARILLA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1856,12 +1832,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6146308375</t>
+          <t>6391727197</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CALLE DELICIAS</t>
+          <t>SAN JORGE 2600</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1871,17 +1847,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12-04-1992</t>
+          <t>02-04-2006</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ELI.GAYTTAN@GMAIL.COM</t>
+          <t>KAREEGD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:21:04</t>
+          <t>06-02-2026 10:13:27</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1902,17 +1878,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:24:25</t>
+          <t>10-02-2026 05:11:01</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>04-02-2026 17:23:58</t>
+          <t>10-02-2026 05:10:28</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1932,11 +1908,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26200522082280001431</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26200522216950001671</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>499</t>
@@ -1944,7 +1928,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1956,12 +1940,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>279168</t>
+          <t>341661</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1971,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1991,28 +1975,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6142760908</t>
+          <t>6142817080</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16-11-1992</t>
+          <t>24-11-1998</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ARACELYTRUJILLO26@GMAIL.COM</t>
+          <t>CARLOSBEL395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>17-02-2025 15:57:01</t>
+          <t>06-02-2026 18:16:57</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2027,28 +2011,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>18-02-2026 07:29:15</t>
+          <t>11-02-2026 19:03:53</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2059,7 +2043,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26200522456240002117</t>
+          <t>26200522275860001803</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2069,34 +2053,34 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340527</t>
+          <t>341663</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2106,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>NAOMI ALEJANDRA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2126,28 +2110,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8112983028</t>
+          <t>6145973271</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29-10-1984</t>
+          <t>15-05-1998</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JULIO565@GMAIL.COM</t>
+          <t>NAOMI998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-02-2026 11:45:26</t>
+          <t>06-02-2026 18:20:37</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2172,12 +2156,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 11:51:04</t>
+          <t>11-02-2026 19:04:57</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2194,11 +2178,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26200522037480001340</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26200522275940001804</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
@@ -2206,24 +2198,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341507</t>
+          <t>341037</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KARELIA EDITH</t>
+          <t>HEDER ARTURO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GANDARILLA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,63 +2245,67 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6391727197</t>
+          <t>6145315107</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SAN JORGE 2600</t>
+          <t xml:space="preserve">PASEOS DE JUAREZ </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>02-04-2006</t>
+          <t>24-07-1983</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>KAREEGD@GMAIL.COM</t>
+          <t>HEDER1930@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>06-02-2026 10:13:27</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>04-02-2026 15:22:46</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>10-02-2026 05:11:01</t>
+          <t>04-02-2026 15:26:49</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>10-02-2026 05:10:28</t>
+          <t>04-02-2026 15:26:11</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2329,44 +2325,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26200522216950001671</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522077360001418</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341661</t>
+          <t>341100</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2376,17 +2364,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2396,10 +2384,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6142817080</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6142518849</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CALLE DELCIAS</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2407,56 +2399,60 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-11-1998</t>
+          <t>25-10-1989</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CARLOSBEL395@GMAIL.COM</t>
+          <t>MANUEL654@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>06-02-2026 18:16:57</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 17:15:41</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>11-02-2026 19:03:53</t>
+          <t>04-02-2026 17:19:37</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>04-02-2026 17:19:05</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2464,22 +2460,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26200522275860001803</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522081990001429</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2496,12 +2484,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341663</t>
+          <t>278704</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>76205</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2511,17 +2499,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NAOMI ALEJANDRA</t>
+          <t>ANIBAL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GAYTAN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2531,67 +2519,75 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6145973271</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>8129739105</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CALLE FRANCISCO PIMENTEL 5115</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15-05-1998</t>
+          <t>08-12-1998</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NAOMI998@GMAIL.COM</t>
+          <t>GAYTAN.ANIBAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>06-02-2026 18:20:37</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2025 19:17:51</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11-02-2026 19:04:57</t>
+          <t>14-02-2026 09:21:50</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>14-02-2026 09:16:25</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2599,7 +2595,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26200522275940001804</t>
+          <t>26200522344660001916</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2607,14 +2603,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2631,12 +2623,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340868</t>
+          <t>299297</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>96795</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2646,17 +2638,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ADRIAN </t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>DE LA ROSA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2666,37 +2658,37 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6142166555</t>
+          <t>6143701479</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CTO TERRANOVA 2803</t>
+          <t>CENTAURO DEL NORTE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>03-11-1986</t>
+          <t>26-08-2005</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LUIS_ADRIAN@HOTMAIL.COM</t>
+          <t>XIMENADELAROSA42@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-02-2026 06:30:38</t>
+          <t>19-06-2025 09:42:01</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2706,27 +2698,27 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-02-2026 06:34:33</t>
+          <t>19-02-2026 12:14:40</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>04-02-2026 06:33:26</t>
+          <t>19-02-2026 11:40:58</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2736,7 +2728,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2746,14 +2738,22 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26200522067340001402</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26200522492700002183</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2770,12 +2770,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341037</t>
+          <t>316379</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HEDER ARTURO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>LUGO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,14 +2805,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6145315107</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PASEOS DE JUAREZ </t>
-        </is>
-      </c>
+          <t>6144687095</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2820,17 +2816,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>24-07-1983</t>
+          <t>12-04-2007</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>HEDER1930@HOTMAIL.COM</t>
+          <t>RIVERA.LUGO.SE07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 15:22:46</t>
+          <t>29-09-2025 19:06:54</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2840,44 +2836,36 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-02-2026 15:26:49</t>
+          <t>09-02-2026 17:45:36</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>04-02-2026 15:26:11</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2885,14 +2873,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26200522077360001418</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26200522203750001652</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>IVONNE HERNANDEZ RIVERA</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2909,12 +2905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>341568</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2924,17 +2920,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAYELI ADAMARI </t>
+          <t>GRECIA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>CEBALLOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2944,12 +2940,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6144630791</t>
+          <t>6142139312</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL SAENZ 14123</t>
+          <t>ERNESTO ESPINOZA 269</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2959,17 +2955,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20-07-2001</t>
+          <t>01-04-1992</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
+          <t>AVILAGRECIA8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>05-02-2026 10:04:55</t>
+          <t>06-02-2026 14:00:17</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2990,7 +2986,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-02-2026 18:35:53</t>
+          <t>09-02-2026 14:29:47</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3000,7 +2996,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:57</t>
+          <t>09-02-2026 14:29:29</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3010,7 +3006,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3020,7 +3016,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26200522207710001661</t>
+          <t>26200522193120001614</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3191,12 +3187,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341568</t>
+          <t>342260</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3206,17 +3202,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GRECIA</t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t xml:space="preserve">VILLALOBOS </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CEBALLOS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3226,32 +3222,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6142139312</t>
+          <t>6144616643</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ERNESTO ESPINOZA 269</t>
+          <t>PROLETARIOS 19</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>01-04-1992</t>
+          <t>28-02-1992</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>AVILAGRECIA8@GMAIL.COM</t>
+          <t>JOSEEDUA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>06-02-2026 14:00:17</t>
+          <t>09-02-2026 16:34:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3272,17 +3268,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 14:29:47</t>
+          <t>11-02-2026 16:44:25</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>09-02-2026 14:29:29</t>
+          <t>11-02-2026 16:43:52</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3292,7 +3288,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3302,15 +3298,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26200522193120001614</t>
+          <t>26200522269350001778</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>499</t>
@@ -3330,12 +3330,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341100</t>
+          <t>342280</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3345,17 +3345,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t>ALAN EDUARDO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>TAMEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SANTOYO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3365,14 +3365,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6142518849</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CALLE DELCIAS</t>
-        </is>
-      </c>
+          <t>6146114137</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3380,60 +3376,56 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25-10-1989</t>
+          <t>07-12-1999</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MANUEL654@GMAIL.COM</t>
+          <t>ALANEDU09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:41</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>09-02-2026 16:46:37</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>04-02-2026 17:19:37</t>
+          <t>09-02-2026 16:47:42</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>04-02-2026 17:19:05</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3441,14 +3433,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26200522081990001429</t>
+          <t>26200522199520001636</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3465,12 +3457,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342260</t>
+          <t>342346</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3480,17 +3472,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t>SOFIA VICTORIA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLALOBOS </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3500,32 +3492,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6144616643</t>
+          <t>6141631910</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PROLETARIOS 19</t>
+          <t>CAFETALES</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28-02-1992</t>
+          <t>03-01-2007</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JOSEEDUA98@GMAIL.COM</t>
+          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:00</t>
+          <t>09-02-2026 17:42:44</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3536,7 +3528,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3546,17 +3538,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>11-02-2026 16:44:25</t>
+          <t>09-02-2026 17:47:57</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>11-02-2026 16:43:52</t>
+          <t>09-02-2026 17:47:26</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3566,7 +3558,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3576,19 +3568,11 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26200522269350001778</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522203900001653</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>499</t>
@@ -3596,24 +3580,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342280</t>
+          <t>326034</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3623,17 +3607,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ALAN EDUARDO</t>
+          <t>GILBERTO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TAMEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3643,7 +3627,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6146114137</t>
+          <t>6141834791</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3654,22 +3638,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>07-12-1999</t>
+          <t>05-06-1997</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ALANEDU09@GMAIL.COM</t>
+          <t>GILGUTIERREZV013@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 16:46:37</t>
+          <t>30-11-2025 11:31:22</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>anualidad LE 300</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3679,22 +3663,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 16:47:42</t>
+          <t>10-02-2026 19:16:06</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2027 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3711,14 +3695,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26200522199520001636</t>
+          <t>26200522246270001744</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3735,12 +3719,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342346</t>
+          <t>342395</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3750,17 +3734,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SOFIA VICTORIA</t>
+          <t>ALISON</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3770,12 +3754,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6141631910</t>
+          <t>6142511165</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CAFETALES</t>
+          <t>MARK TWAIN 500</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3785,17 +3769,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>03-01-2007</t>
+          <t>08-10-2000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
+          <t>ALISONMONTES00@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 17:42:44</t>
+          <t>09-02-2026 18:32:20</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3806,7 +3790,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3816,7 +3800,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:57</t>
+          <t>09-02-2026 18:40:18</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3826,7 +3810,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:26</t>
+          <t>09-02-2026 18:39:43</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3846,7 +3830,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26200522203900001653</t>
+          <t>26200522207950001662</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3870,12 +3854,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342395</t>
+          <t>341259</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3885,17 +3869,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ALISON</t>
+          <t xml:space="preserve">NAYELI ADAMARI </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3905,12 +3889,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6142511165</t>
+          <t>6144630791</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MARK TWAIN 500</t>
+          <t>MIGUEL ANGEL SAENZ 14123</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3920,17 +3904,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>08-10-2000</t>
+          <t>20-07-2001</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ALISONMONTES00@GMAIL.COM</t>
+          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 18:32:20</t>
+          <t>05-02-2026 10:04:55</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3951,7 +3935,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 18:40:18</t>
+          <t>09-02-2026 18:35:53</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3961,7 +3945,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>09-02-2026 18:39:43</t>
+          <t>09-02-2026 18:34:57</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3971,7 +3955,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3981,10 +3965,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26200522207950001662</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+          <t>26200522207710001661</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3993,12 +3981,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4132,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>326034</t>
+          <t>331503</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4159,17 +4147,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GILBERTO</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>HERMOSILLO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4179,10 +4167,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6141834791</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6143556958</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MINA LOS REYES 3722</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4190,56 +4182,60 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>05-06-1997</t>
+          <t>29-01-1999</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>GILGUTIERREZV013@GMAIL.COM</t>
+          <t>GON.HERM.JA1534@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>30-11-2025 11:31:22</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>anualidad LE 300</t>
-        </is>
-      </c>
+          <t>02-01-2026 11:17:55</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:06</t>
+          <t>09-02-2026 11:20:21</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>10-03-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>09-02-2026 11:19:32</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4247,36 +4243,44 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26200522246270001744</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26200522188810001604</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342110</t>
+          <t>340085</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4286,17 +4290,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MARIO EDGARDO</t>
+          <t>EDNA ODALYS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>BARREA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4306,63 +4310,67 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6144714471</t>
+          <t>6143185738</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CDA PUERTA DE GRANADA 2821</t>
+          <t>C SALVADOR DIAZ CASAS 57</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20-02-1987</t>
+          <t>18-05-1999</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>SILVAOLIVASM@GMAIL.COM</t>
+          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 11:22:59</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>02-02-2026 12:27:34</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 11:26:28</t>
+          <t>02-02-2026 12:31:44</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>09-02-2026 11:25:37</t>
+          <t>02-02-2026 12:30:57</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4382,36 +4390,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26200522188970001605</t>
+          <t>26200522008980001294</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342175</t>
+          <t>342110</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4421,17 +4429,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MARCO IVAN</t>
+          <t>MARIO EDGARDO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLINAR </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CANTU</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4441,12 +4449,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6141719602</t>
+          <t>6144714471</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ERNESTO ESPINOZA 269</t>
+          <t>CDA PUERTA DE GRANADA 2821</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4456,17 +4464,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16-04-1996</t>
+          <t>20-02-1987</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
+          <t>SILVAOLIVASM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 14:21:30</t>
+          <t>09-02-2026 11:22:59</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4477,7 +4485,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4487,7 +4495,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 14:25:15</t>
+          <t>09-02-2026 11:26:28</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4497,7 +4505,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09-02-2026 14:23:33</t>
+          <t>09-02-2026 11:25:37</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4517,7 +4525,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26200522193020001613</t>
+          <t>26200522188970001605</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4529,12 +4537,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -4680,12 +4688,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>331503</t>
+          <t>340868</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4695,17 +4703,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t xml:space="preserve">LUIS ADRIAN </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HERMOSILLO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4715,12 +4723,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6143556958</t>
+          <t>6142166555</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MINA LOS REYES 3722</t>
+          <t>CTO TERRANOVA 2803</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4730,20 +4738,24 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>29-01-1999</t>
+          <t>03-11-1986</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>X61@GMAIL.COM</t>
+          <t>LUIS_ADRIANMC@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-01-2026 11:17:55</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>04-02-2026 06:30:38</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4751,27 +4763,27 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 11:20:21</t>
+          <t>04-02-2026 06:34:33</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:32</t>
+          <t>04-02-2026 06:33:26</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4791,44 +4803,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26200522188810001604</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522067340001402</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342761</t>
+          <t>344164</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4838,17 +4842,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>KAROL AMAIRANY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DOZAL</t>
+          <t>SIFUENTES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CHACON</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4858,7 +4862,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6563497877</t>
+          <t>6145128509</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4869,22 +4873,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30-01-2003</t>
+          <t>21-01-1999</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
+          <t>TIJUANAMARUNGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 17:45:06</t>
+          <t>16-02-2026 16:26:56</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4904,18 +4908,18 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 17:46:42</t>
+          <t>23-02-2026 16:21:52</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -4926,11 +4930,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26200522241060001732</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26200522586800002330</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>549</t>
@@ -4938,7 +4950,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4950,12 +4962,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>340085</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4965,17 +4977,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EDNA ODALYS</t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BARREA</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4985,12 +4997,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6143185738</t>
+          <t>6143682180</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C SALVADOR DIAZ CASAS 57</t>
+          <t>SAN JORGE 2600</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5000,52 +5012,48 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18-05-1999</t>
+          <t>15-09-2006</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
+          <t>VALERIAR150906@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>02-02-2026 12:27:34</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 10:10:46</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-02-2026 12:31:44</t>
+          <t>10-02-2026 05:14:42</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>02-02-2026 12:30:57</t>
+          <t>10-02-2026 05:13:41</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5055,7 +5063,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5065,19 +5073,27 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26200522008980001294</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26200522217020001672</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5089,12 +5105,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343806</t>
+          <t>342175</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5104,17 +5120,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JESUS RUBEN</t>
+          <t>MARCO IVAN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">MOLINAR </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>CANTU</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5124,12 +5140,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6141109571</t>
+          <t>6141719602</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>DESIERTO DEL SAHARA 3706</t>
+          <t>ERNESTO ESPINOZA 269</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5139,17 +5155,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20-06-1989</t>
+          <t>16-04-1996</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JESUSRUBEN201989@ICLOUD.COM</t>
+          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15-02-2026 11:10:14</t>
+          <t>09-02-2026 14:21:30</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5160,7 +5176,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5170,17 +5186,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>15-02-2026 11:12:58</t>
+          <t>09-02-2026 14:25:15</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>15-02-2026 11:11:57</t>
+          <t>09-02-2026 14:23:33</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5190,7 +5206,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5200,7 +5216,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26200522364120001933</t>
+          <t>26200522193020001613</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5224,12 +5240,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344167</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5239,17 +5255,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JONATHAN MANUEL</t>
+          <t xml:space="preserve">RAFAEL </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MARUNGO</t>
+          <t xml:space="preserve">LOERA </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SAEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5259,7 +5275,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6142467576</t>
+          <t>6144270811</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5270,22 +5286,22 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19-06-1985</t>
+          <t>22-08-1977</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>TIJUANAMHMARUNGO@HOTMAIL.COM</t>
+          <t>VLOERASAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16-02-2026 16:31:02</t>
+          <t>09-02-2026 17:05:24</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5295,28 +5311,28 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>23-02-2026 16:25:12</t>
+          <t>09-02-2026 17:07:07</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>09-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5327,44 +5343,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26200522586990002331</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522200740001643</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344164</t>
+          <t>343806</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5374,17 +5382,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KAROL AMAIRANY</t>
+          <t>JESUS RUBEN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SIFUENTES</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5394,67 +5402,75 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6145128509</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6141109571</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>DESIERTO DEL SAHARA 3706</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>21-01-1999</t>
+          <t>20-06-1989</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>TIJUANAMARUNGO@GMAIL.COM</t>
+          <t>JESUSRUBEN201989@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16-02-2026 16:26:56</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>15-02-2026 11:10:14</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>23-02-2026 16:21:52</t>
+          <t>15-02-2026 11:12:58</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:11:57</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5462,44 +5478,36 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26200522586800002330</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522364120001933</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>341505</t>
+          <t>344674</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5509,17 +5517,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARBARA </t>
+          <t>ABRAHM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5529,35 +5537,39 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6143682180</t>
+          <t>6147767384</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SAN JORGE 2600</t>
+          <t>CALLE DOLORES PIMENTEL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>15-09-2006</t>
+          <t>22-03-1999</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>VALERIAR150906@GMAIL.COM</t>
+          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>06-02-2026 10:10:46</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>17-02-2026 19:04:34</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5565,7 +5577,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5575,17 +5587,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10-02-2026 05:14:42</t>
+          <t>17-02-2026 19:10:12</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>10-02-2026 05:13:41</t>
+          <t>17-02-2026 19:08:30</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5605,19 +5617,11 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26200522217020001672</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522443540002095</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>499</t>
@@ -5625,24 +5629,24 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344070</t>
+          <t>342308</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5652,17 +5656,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DORIAN</t>
+          <t>DANIEL ANTONIO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t xml:space="preserve">SERRANO </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESENDIZ </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5672,67 +5676,75 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3315999428</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6271210648</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>REPUBLICA DOMINICANA 20</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>12-10-2005</t>
+          <t>27-03-1999</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>DORIAN_ROMERO@JABIL.COM</t>
+          <t>THEHRHH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 13:29:06</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:12:49</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>23-02-2026 13:26:14</t>
+          <t>09-02-2026 17:19:08</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:16:19</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5740,22 +5752,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26200522580570002314</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
-        </is>
-      </c>
+          <t>26200522201590001646</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5772,12 +5776,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344118</t>
+          <t>344070</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5787,17 +5791,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ABRIL PAOLA</t>
+          <t>DORIAN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GALLEGOS</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TARANGO</t>
+          <t xml:space="preserve">RESENDIZ </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5807,7 +5811,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6147370020</t>
+          <t>3315999428</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5818,17 +5822,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>23-07-2003</t>
+          <t>12-10-2005</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ABRILPG19@GMAIL.COM</t>
+          <t>DORIAN_ROMERO@JABIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>16-02-2026 15:15:42</t>
+          <t>16-02-2026 13:29:06</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5853,7 +5857,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>23-02-2026 16:28:38</t>
+          <t>23-02-2026 13:26:14</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5864,7 +5868,7 @@
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5875,7 +5879,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26200522587190002333</t>
+          <t>26200522580570002314</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5885,7 +5889,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5895,24 +5899,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344200</t>
+          <t>344118</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5922,17 +5926,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MAGDALENA</t>
+          <t>ABRIL PAOLA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BALDERRAMA</t>
+          <t>GALLEGOS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AVELAR</t>
+          <t>TARANGO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5942,14 +5946,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6391115826</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>COL SANTO NIÑO</t>
-        </is>
-      </c>
+          <t>6147370020</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5957,64 +5957,56 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>10-01-1971</t>
+          <t>23-07-2003</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>MAGDAURIBE10@HOTMAIL.COM</t>
+          <t>ABRILPG19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-02-2026 17:13:45</t>
+          <t>16-02-2026 15:15:42</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>18-02-2026 18:02:37</t>
+          <t>23-02-2026 16:28:38</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:01:54</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6022,7 +6014,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26200522471160002153</t>
+          <t>26200522587190002333</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -6037,29 +6029,29 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342298</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6069,17 +6061,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL </t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOERA </t>
+          <t>DOZAL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAEZ</t>
+          <t>CHACON</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6089,28 +6081,28 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6144270811</t>
+          <t>6563497877</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22-08-1977</t>
+          <t>30-01-2003</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>VLOERASAEZ@GMAIL.COM</t>
+          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>09-02-2026 17:05:24</t>
+          <t>10-02-2026 17:45:06</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6125,22 +6117,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>09-02-2026 17:07:07</t>
+          <t>10-02-2026 17:46:42</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -6157,36 +6149,36 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26200522200740001643</t>
+          <t>26200522241060001732</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342308</t>
+          <t>345838</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>88003</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6196,17 +6188,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DANIEL ANTONIO</t>
+          <t>ESMERALDA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERRANO </t>
+          <t>VILLALBA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>LASCANO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6216,35 +6208,39 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6271210648</t>
+          <t>6144743555</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>REPUBLICA DOMINICANA 20</t>
+          <t>MONTES ALPES 11914</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>27-03-1999</t>
+          <t>22-03-1994</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>THEHRHH@GMAIL.COM</t>
+          <t>ESMERALDA_220229@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>09-02-2026 17:12:49</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>23-02-2026 15:31:03</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6252,7 +6248,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6262,17 +6258,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>09-02-2026 17:19:08</t>
+          <t>23-02-2026 15:57:07</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>09-02-2026 17:16:19</t>
+          <t>23-02-2026 15:54:58</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6282,7 +6278,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6292,10 +6288,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26200522201590001646</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
+          <t>26200522585800002325</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6304,24 +6304,24 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>344674</t>
+          <t>342661</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ABRAHM</t>
+          <t xml:space="preserve">JOSE ALONSO </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t xml:space="preserve">CORDERO </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6147767384</t>
+          <t>6143546193</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CALLE DOLORES PIMENTEL</t>
+          <t>MONTE ALTAI 4323</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6366,24 +6366,20 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>22-03-1999</t>
+          <t>20-04-1982</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
+          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>17-02-2026 19:04:34</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:13:05</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6401,17 +6397,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>17-02-2026 19:10:12</t>
+          <t>10-02-2026 15:19:33</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>17-02-2026 19:08:30</t>
+          <t>10-02-2026 15:16:36</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6431,7 +6427,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26200522443540002095</t>
+          <t>26200522234120001697</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6590,12 +6586,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>345838</t>
+          <t>345907</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>88003</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6605,17 +6601,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ESMERALDA</t>
+          <t>JAIMIE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>VILLALBA</t>
+          <t>VALVERDE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LASCANO</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6625,12 +6621,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6144743555</t>
+          <t>6144790343</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MONTES ALPES 11914</t>
+          <t>CHE GUEVARA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6640,42 +6636,42 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>22-03-1994</t>
+          <t>16-08-2004</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ESMERALDA_220229@ICLOUD.COM</t>
+          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>23-02-2026 15:31:03</t>
+          <t>23-02-2026 17:09:43</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>23-02-2026 15:57:07</t>
+          <t>23-02-2026 17:14:20</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -6685,7 +6681,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:58</t>
+          <t>23-02-2026 17:13:54</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6695,7 +6691,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6705,40 +6701,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26200522585800002325</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26200522590120002343</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342661</t>
+          <t>345918</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6748,17 +6740,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ALONSO </t>
+          <t>JESSER URIEL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORDERO </t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6768,12 +6760,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6143546193</t>
+          <t>6141611733</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MONTE ALTAI 4323</t>
+          <t>MINA GLAMIS 1914</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6783,20 +6775,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20-04-1982</t>
+          <t>20-04-2001</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
+          <t>URIELPORTILLO951@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10-02-2026 15:13:05</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>23-02-2026 17:21:49</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6814,17 +6810,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10-02-2026 15:19:33</t>
+          <t>23-02-2026 17:29:11</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>10-02-2026 15:16:36</t>
+          <t>23-02-2026 17:27:48</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6834,7 +6830,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6844,7 +6840,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26200522234120001697</t>
+          <t>26200522590980002346</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6856,24 +6852,24 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>345942</t>
+          <t>342901</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>88107</t>
+          <t>20718</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6883,17 +6879,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ADRIANA AURORA</t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6903,10 +6899,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6143970735</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6142443644</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>PRIV DE GONZALEZ COSSIO 6734</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6914,56 +6914,60 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>09-02-2002</t>
+          <t>08-03-1963</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ADRIANA72270@GMAIL.COM</t>
+          <t>LEOTO056@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>23-02-2026 17:47:34</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>11-02-2026 08:12:54</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>23-02-2026 17:48:54</t>
+          <t>11-02-2026 08:29:30</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>11-02-2026 08:28:18</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6971,19 +6975,23 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26200522592530002354</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
+          <t>26200522259660001758</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6995,12 +7003,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>344209</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7010,17 +7018,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t>ELBA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7030,14 +7038,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6142443644</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>PRIV DE GONZALEZ COSSIO 6734</t>
-        </is>
-      </c>
+          <t>6141057797</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7045,60 +7049,56 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>08-03-1963</t>
+          <t>01-06-1967</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>LEOTO056@GMAIL.COM</t>
+          <t>MARIAHDZ67000@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>11-02-2026 08:12:54</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>16-02-2026 17:19:53</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>11-02-2026 08:29:30</t>
+          <t>18-02-2026 16:45:06</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>11-02-2026 08:28:18</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7106,23 +7106,27 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26200522259660001758</t>
+          <t>26200522467120002145</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7134,12 +7138,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345907</t>
+          <t>345942</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>88107</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7149,17 +7153,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JAIMIE</t>
+          <t>ADRIANA AURORA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>VALVERDE</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7169,14 +7173,10 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6144790343</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>CHE GUEVARA</t>
-        </is>
-      </c>
+          <t>6143970735</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7184,42 +7184,42 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>16-08-2004</t>
+          <t>09-02-2002</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
+          <t>ADRIANA72270@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>23-02-2026 17:09:43</t>
+          <t>23-02-2026 17:47:34</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>23-02-2026 17:14:20</t>
+          <t>23-02-2026 17:48:54</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -7227,21 +7227,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:13:54</t>
-        </is>
-      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7249,19 +7241,19 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26200522590120002343</t>
+          <t>26200522592530002354</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7273,12 +7265,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345918</t>
+          <t>344167</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7288,17 +7280,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JESSER URIEL</t>
+          <t>JONATHAN MANUEL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>MARUNGO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7308,14 +7300,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6141611733</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>MINA GLAMIS 1914</t>
-        </is>
-      </c>
+          <t>6142467576</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7323,42 +7311,42 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>20-04-2001</t>
+          <t>19-06-1985</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>URIELPORTILLO951@GMAIL.COM</t>
+          <t>TIJUANAMHMARUNGO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>23-02-2026 17:21:49</t>
+          <t>16-02-2026 16:31:02</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-02-2026 17:29:11</t>
+          <t>23-02-2026 16:25:12</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7366,21 +7354,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:27:48</t>
-        </is>
-      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7388,14 +7368,22 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26200522590980002346</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>26200522586990002331</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7412,12 +7400,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344209</t>
+          <t>344200</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7427,17 +7415,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ELBA</t>
+          <t>MAGDALENA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>BALDERRAMA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>AVELAR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7447,10 +7435,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6141057797</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6391115826</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COL SANTO NIÑO</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7458,17 +7450,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>01-06-1967</t>
+          <t>10-01-1971</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>MARIAHDZ67000@HOTMAIL.COM</t>
+          <t>MAGDAURIBE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:53</t>
+          <t>16-02-2026 17:13:45</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7478,22 +7470,22 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:06</t>
+          <t>18-02-2026 18:02:37</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -7501,13 +7493,21 @@
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:01:54</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26200522467120002145</t>
+          <t>26200522471160002153</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7530,17 +7530,17 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>345906</t>
+          <t>344234</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7697,17 +7697,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ESLY YAZMIN</t>
+          <t>JONATHA IVAN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALVERDE </t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7717,32 +7717,28 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6142830714</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>CHE GUEVARA</t>
-        </is>
-      </c>
+          <t>6141324957</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>19-01-1997</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>YAZMINREYES566@GMAIL.COM</t>
+          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>23-02-2026 17:09:02</t>
+          <t>16-02-2026 17:44:53</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7752,44 +7748,36 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>23-02-2026 17:16:35</t>
+          <t>16-02-2026 17:46:24</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:16:04</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7797,19 +7785,19 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26200522590290002344</t>
+          <t>26200522400880002009</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7821,12 +7809,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344234</t>
+          <t>344116</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7836,17 +7824,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JONATHA IVAN</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>LOZOYA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7856,28 +7844,28 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6141324957</t>
+          <t>6143978047</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>21-10-1996</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
+          <t>SUGEYPONLOZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 17:44:53</t>
+          <t>16-02-2026 15:12:06</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7902,12 +7890,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>16-02-2026 17:46:24</t>
+          <t>18-02-2026 15:52:54</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -7924,11 +7912,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26200522400880002009</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26200522464950002139</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>549</t>
@@ -7936,7 +7932,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7948,12 +7944,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344116</t>
+          <t>344677</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7963,17 +7959,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LOZOYA</t>
+          <t>MORELOS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7983,28 +7979,28 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6143978047</t>
+          <t>6144072330</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>21-10-1996</t>
+          <t>15-02-2004</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>SUGEYPONLOZ@GMAIL.COM</t>
+          <t>CG8165424@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16-02-2026 15:12:06</t>
+          <t>17-02-2026 19:12:24</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8019,28 +8015,28 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>18-02-2026 15:52:54</t>
+          <t>17-02-2026 19:13:46</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V56" t="inlineStr"/>
@@ -8051,22 +8047,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26200522464950002139</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522443700002096</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8083,12 +8071,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344677</t>
+          <t>345906</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8098,17 +8086,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>ESLY YAZMIN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">VALVERDE </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8118,28 +8106,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6144072330</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>6142830714</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CHE GUEVARA</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>15-02-2004</t>
+          <t>19-01-1997</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CG8165424@GMAIL.COM</t>
+          <t>YAZMINREYES566@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>17-02-2026 19:12:24</t>
+          <t>23-02-2026 17:09:02</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8149,36 +8141,44 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>17-02-2026 19:13:46</t>
+          <t>23-02-2026 17:16:35</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:16:04</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8186,14 +8186,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26200522443700002096</t>
+          <t>26200522590290002344</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -852,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>340080</t>
+          <t>301635</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>99133</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>YARELI</t>
+          <t xml:space="preserve">YODGAR JASIEL </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,32 +887,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6142757940</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>C RUBEN JARAMILLO 214</t>
-        </is>
-      </c>
+          <t>6146099932</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>05-01-1996</t>
+          <t>18-06-2008</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>YARELI.H9628@GMAIL.COM</t>
+          <t>CG569407@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-02-2026 12:19:55</t>
+          <t>01-07-2025 19:06:32</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -922,44 +918,36 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-02-2026 12:24:36</t>
+          <t>17-02-2026 19:16:14</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-02-2026 12:24:04</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -967,14 +955,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26200522008710001292</t>
+          <t>26200522443750002097</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -991,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>339397</t>
+          <t>288404</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>85902</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>CRISTIAN ALAN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LOERA</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CABALLERO</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,12 +1014,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6143368528</t>
+          <t>6144545766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CALLE DE METER 5510</t>
+          <t>ALCATIFA 15115</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,17 +1029,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>07-12-1998</t>
+          <t>08-05-2008</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TBRBEANS98@GMAIL.COM</t>
+          <t>CRISALANCASTA_1985@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>30-01-2026 16:37:06</t>
+          <t>16-04-2025 13:38:48</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1072,7 +1060,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 17:39:05</t>
+          <t>02-02-2026 12:44:05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1082,7 +1070,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 17:37:49</t>
+          <t>02-02-2026 12:41:04</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1092,7 +1080,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1102,19 +1090,15 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26200522019070001314</t>
+          <t>26200522009480001296</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>499</t>
@@ -1122,24 +1106,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>301635</t>
+          <t>339397</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>99133</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1149,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">YODGAR JASIEL </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LOERA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CABALLERO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1169,10 +1153,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6146099932</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6143368528</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CALLE DE METER 5510</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1180,56 +1168,60 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18-06-2008</t>
+          <t>07-12-1998</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CG569407@GMAIL.COM</t>
+          <t>TBRBEANS98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-07-2025 19:06:32</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>30-01-2026 16:37:06</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-02-2026 19:16:14</t>
+          <t>02-02-2026 17:39:05</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:37:49</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1237,36 +1229,44 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200522443750002097</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26200522019070001314</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>288404</t>
+          <t>340080</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85902</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRISTIAN ALAN</t>
+          <t>YARELI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,53 +1296,57 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6144545766</t>
+          <t>6142757940</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ALCATIFA 15115</t>
+          <t>C RUBEN JARAMILLO 214</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>08-05-2008</t>
+          <t>05-01-1996</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CRISALANCASTA_1985@GMAIL.COM</t>
+          <t>YARELI.H9628@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16-04-2025 13:38:48</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>02-02-2026 12:19:55</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 12:44:05</t>
+          <t>02-02-2026 12:24:36</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-02-2026 12:41:04</t>
+          <t>02-02-2026 12:24:04</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1362,7 +1366,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1372,18 +1376,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26200522009480001296</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26200522008710001292</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>341105</t>
+          <t>279168</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>76669</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ELIANA JANETH</t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAYTAN </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,14 +1435,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6146308375</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CALLE DELICIAS</t>
-        </is>
-      </c>
+          <t>6142760908</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1450,60 +1446,56 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>12-04-1992</t>
+          <t>16-11-1992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ELI.GAYTTAN@GMAIL.COM</t>
+          <t>ARACELYTRUJILLO26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>04-02-2026 17:21:04</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>17-02-2025 15:57:01</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-02-2026 17:24:25</t>
+          <t>18-02-2026 07:29:15</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>04-02-2026 17:23:58</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1511,14 +1503,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26200522082280001431</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26200522456240002117</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1535,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340527</t>
+          <t>278704</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>76205</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>ANIBAL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>GAYTAN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,10 +1570,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8112983028</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>8129739105</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CALLE FRANCISCO PIMENTEL 5115</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1581,56 +1585,60 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>29-10-1984</t>
+          <t>08-12-1998</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>JULIO565@GMAIL.COM</t>
+          <t>GAYTAN.ANIBAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-02-2026 11:45:26</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2025 19:17:51</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-02-2026 11:51:04</t>
+          <t>14-02-2026 09:21:50</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>14-02-2026 09:16:25</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1638,36 +1646,40 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26200522037480001340</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26200522344660001916</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>279168</t>
+          <t>299297</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>96795</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1689,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>DE LA ROSA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,10 +1709,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6142760908</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6143701479</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CENTAURO DEL NORTE</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1708,56 +1724,64 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>16-11-1992</t>
+          <t>26-08-2005</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ARACELYTRUJILLO26@GMAIL.COM</t>
+          <t>XIMENADELAROSA42@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17-02-2025 15:57:01</t>
+          <t>19-06-2025 09:42:01</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>18-02-2026 07:29:15</t>
+          <t>19-02-2026 12:14:40</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>19-02-2026 11:40:58</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1765,7 +1789,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26200522456240002117</t>
+          <t>26200522492700002183</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1780,29 +1804,29 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341507</t>
+          <t>316379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1836,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KARELIA EDITH</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GANDARILLA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>LUGO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,75 +1856,67 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6391727197</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SAN JORGE 2600</t>
-        </is>
-      </c>
+          <t>6144687095</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>02-04-2006</t>
+          <t>12-04-2007</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>KAREEGD@GMAIL.COM</t>
+          <t>RIVERA.LUGO.SE07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>06-02-2026 10:13:27</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>29-09-2025 19:06:54</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>10-02-2026 05:11:01</t>
+          <t>09-02-2026 17:45:36</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:10:28</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1908,7 +1924,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26200522216950001671</t>
+          <t>26200522203750001652</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1918,34 +1934,34 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
+          <t>IVONNE HERNANDEZ RIVERA</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341661</t>
+          <t>340527</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1971,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,7 +1991,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6142817080</t>
+          <t>8112983028</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1986,17 +2002,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>24-11-1998</t>
+          <t>29-10-1984</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CARLOSBEL395@GMAIL.COM</t>
+          <t>JULIO565@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>06-02-2026 18:16:57</t>
+          <t>03-02-2026 11:45:26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2021,12 +2037,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>11-02-2026 19:03:53</t>
+          <t>03-02-2026 11:51:04</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2043,19 +2059,11 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26200522275860001803</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522037480001340</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2063,24 +2071,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341663</t>
+          <t>326034</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NAOMI ALEJANDRA</t>
+          <t>GILBERTO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,33 +2118,33 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6145973271</t>
+          <t>6141834791</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15-05-1998</t>
+          <t>05-06-1997</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>NAOMI998@GMAIL.COM</t>
+          <t>GILGUTIERREZV013@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>06-02-2026 18:20:37</t>
+          <t>30-11-2025 11:31:22</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>anualidad LE 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2146,22 +2154,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>11-02-2026 19:04:57</t>
+          <t>10-02-2026 19:16:06</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>10-03-2027 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2178,22 +2186,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26200522275940001804</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522246270001744</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2210,12 +2210,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341037</t>
+          <t>278277</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>75778</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HEDER ARTURO</t>
+          <t xml:space="preserve">JAVIER OMAR </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6145315107</t>
+          <t>6142791568</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASEOS DE JUAREZ </t>
+          <t>GARCILAZO DE LA VEGA 15300</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2260,52 +2260,48 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>24-07-1983</t>
+          <t>28-01-1994</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>HEDER1930@HOTMAIL.COM</t>
+          <t>JOSS0194@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-02-2026 15:22:46</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2025 17:19:45</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-02-2026 15:26:49</t>
+          <t>03-02-2026 07:23:51</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>04-02-2026 15:26:11</t>
+          <t>03-02-2026 07:22:24</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2325,14 +2321,18 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26200522077360001418</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26200522031990001330</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2349,12 +2349,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341100</t>
+          <t>341037</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,17 +2364,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t>HEDER ARTURO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SANTOYO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6142518849</t>
+          <t>6145315107</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CALLE DELCIAS</t>
+          <t xml:space="preserve">PASEOS DE JUAREZ </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2399,38 +2399,42 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>25-10-1989</t>
+          <t>24-07-1983</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>MANUEL654@GMAIL.COM</t>
+          <t>HEDER1930@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:41</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>04-02-2026 15:22:46</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>04-02-2026 17:19:37</t>
+          <t>04-02-2026 15:26:49</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2440,7 +2444,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>04-02-2026 17:19:05</t>
+          <t>04-02-2026 15:26:11</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2460,14 +2464,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26200522081990001429</t>
+          <t>26200522077360001418</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2484,12 +2488,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>278704</t>
+          <t>341259</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>76205</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2499,17 +2503,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ANIBAL</t>
+          <t xml:space="preserve">NAYELI ADAMARI </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GAYTAN</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2519,32 +2523,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8129739105</t>
+          <t>6144630791</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CALLE FRANCISCO PIMENTEL 5115</t>
+          <t>MIGUEL ANGEL SAENZ 14123</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>08-12-1998</t>
+          <t>20-07-2001</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>GAYTAN.ANIBAL@GMAIL.COM</t>
+          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>12-02-2025 19:17:51</t>
+          <t>05-02-2026 10:04:55</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2555,7 +2559,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2565,17 +2569,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>14-02-2026 09:21:50</t>
+          <t>09-02-2026 18:35:53</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>14-02-2026 09:16:25</t>
+          <t>09-02-2026 18:34:57</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2595,12 +2599,12 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26200522344660001916</t>
+          <t>26200522207710001661</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE RECORRIDO</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr"/>
@@ -2623,12 +2627,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>299297</t>
+          <t>331503</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>96795</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2638,17 +2642,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DE LA ROSA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t>HERMOSILLO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2658,39 +2662,35 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6143701479</t>
+          <t>6143556958</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CENTAURO DEL NORTE</t>
+          <t>MINA LOS REYES 3722</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26-08-2005</t>
+          <t>29-01-1999</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>XIMENADELAROSA42@GMAIL.COM</t>
+          <t>GON.HERM.JA1534@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19-06-2025 09:42:01</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>02-01-2026 11:17:55</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2708,17 +2708,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>19-02-2026 12:14:40</t>
+          <t>09-02-2026 11:20:21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>19-02-2026 11:40:58</t>
+          <t>09-02-2026 11:19:32</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26200522492700002183</t>
+          <t>26200522188810001604</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2758,24 +2758,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>316379</t>
+          <t>341100</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LUGO</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,10 +2805,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6144687095</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6142518849</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CALLE DELCIAS</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2816,56 +2820,60 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12-04-2007</t>
+          <t>25-10-1989</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>RIVERA.LUGO.SE07@GMAIL.COM</t>
+          <t>MANUEL654@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>29-09-2025 19:06:54</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 17:15:41</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>09-02-2026 17:45:36</t>
+          <t>04-02-2026 17:19:37</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>04-02-2026 17:19:05</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2873,22 +2881,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26200522203750001652</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>IVONNE HERNANDEZ RIVERA</t>
-        </is>
-      </c>
+          <t>26200522081990001429</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -3044,12 +3044,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342256</t>
+          <t>340085</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3059,17 +3059,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EIMY ANAHI</t>
+          <t>EDNA ODALYS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOBARA </t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ALCANTAR</t>
+          <t>BARREA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6145118271</t>
+          <t>6143185738</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ALAMEDAS 311</t>
+          <t>C SALVADOR DIAZ CASAS 57</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3094,48 +3094,52 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30-09-1990</t>
+          <t>18-05-1999</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>EIMI09@GMAIL.COM</t>
+          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 16:30:52</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>02-02-2026 12:27:34</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>11-02-2026 16:42:43</t>
+          <t>02-02-2026 12:31:44</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>11-02-2026 16:42:01</t>
+          <t>02-02-2026 12:30:57</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3145,7 +3149,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3155,44 +3159,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26200522269260001777</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522008980001294</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342260</t>
+          <t>342110</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3202,17 +3198,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t>MARIO EDGARDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLALOBOS </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3222,12 +3218,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6144616643</t>
+          <t>6144714471</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PROLETARIOS 19</t>
+          <t>CDA PUERTA DE GRANADA 2821</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3237,17 +3233,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>28-02-1992</t>
+          <t>20-02-1987</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>JOSEEDUA98@GMAIL.COM</t>
+          <t>SILVAOLIVASM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:00</t>
+          <t>09-02-2026 11:22:59</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3258,7 +3254,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3268,17 +3264,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>11-02-2026 16:44:25</t>
+          <t>09-02-2026 11:26:28</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>11-02-2026 16:43:52</t>
+          <t>09-02-2026 11:25:37</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3288,7 +3284,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3298,19 +3294,11 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26200522269350001778</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522188970001605</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>499</t>
@@ -3318,24 +3306,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342280</t>
+          <t>342364</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3345,17 +3333,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ALAN EDUARDO</t>
+          <t>CLAUDIA LESLIE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TAMEZ</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3365,28 +3353,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6146114137</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6143534589</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CIUDAD DURANGO 31125</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>07-12-1999</t>
+          <t>19-01-2000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ALANEDU09@GMAIL.COM</t>
+          <t>LESLIEMILLA09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 16:46:37</t>
+          <t>09-02-2026 18:00:59</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3396,22 +3388,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-02-2026 16:47:42</t>
+          <t>09-02-2026 18:08:11</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3419,13 +3411,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>09-02-2026 18:07:44</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3433,14 +3433,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26200522199520001636</t>
+          <t>26200522205660001656</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3457,12 +3457,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342346</t>
+          <t>341105</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SOFIA VICTORIA</t>
+          <t>ELIANA JANETH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">GAYTAN </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6141631910</t>
+          <t>6146308375</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CAFETALES</t>
+          <t>CALLE DELICIAS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3507,17 +3507,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>03-01-2007</t>
+          <t>12-04-1992</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
+          <t>ELI.GAYTTAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 17:42:44</t>
+          <t>04-02-2026 17:21:04</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3538,17 +3538,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:57</t>
+          <t>04-02-2026 17:24:25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:26</t>
+          <t>04-02-2026 17:23:58</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26200522203900001653</t>
+          <t>26200522082280001431</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3592,12 +3592,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>326034</t>
+          <t>340868</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3607,17 +3607,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GILBERTO</t>
+          <t xml:space="preserve">LUIS ADRIAN </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3627,10 +3627,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6141834791</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6142166555</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CTO TERRANOVA 2803</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3638,56 +3642,64 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>05-06-1997</t>
+          <t>03-11-1986</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>GILGUTIERREZV013@GMAIL.COM</t>
+          <t>LUIS_ADRIANMC@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>30-11-2025 11:31:22</t>
+          <t>04-02-2026 06:30:38</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>anualidad LE 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:06</t>
+          <t>04-02-2026 06:34:33</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-03-2027 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>04-02-2026 06:33:26</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3695,36 +3707,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26200522246270001744</t>
+          <t>26200522067340001402</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342395</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3734,17 +3746,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ALISON</t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3754,12 +3766,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6142511165</t>
+          <t>6143682180</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MARK TWAIN 500</t>
+          <t>SAN JORGE 2600</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3769,17 +3781,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08-10-2000</t>
+          <t>15-09-2006</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ALISONMONTES00@GMAIL.COM</t>
+          <t>VALERIAR150906@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 18:32:20</t>
+          <t>06-02-2026 10:10:46</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3800,17 +3812,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>09-02-2026 18:40:18</t>
+          <t>10-02-2026 05:14:42</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>09-02-2026 18:39:43</t>
+          <t>10-02-2026 05:13:41</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3820,7 +3832,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3830,11 +3842,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26200522207950001662</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26200522217020001672</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>499</t>
@@ -3842,7 +3862,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3854,12 +3874,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>341507</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3869,17 +3889,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAYELI ADAMARI </t>
+          <t>KARELIA EDITH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GANDARILLA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3889,12 +3909,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6144630791</t>
+          <t>6391727197</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL SAENZ 14123</t>
+          <t>SAN JORGE 2600</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3904,17 +3924,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>20-07-2001</t>
+          <t>02-04-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
+          <t>KAREEGD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-02-2026 10:04:55</t>
+          <t>06-02-2026 10:13:27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3935,17 +3955,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 18:35:53</t>
+          <t>10-02-2026 05:11:01</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:57</t>
+          <t>10-02-2026 05:10:28</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3965,15 +3985,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26200522207710001661</t>
+          <t>26200522216950001671</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -3981,24 +4005,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>341661</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>75778</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4008,17 +4032,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAVIER OMAR </t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4028,14 +4052,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6142791568</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>GARCILAZO DE LA VEGA 15300</t>
-        </is>
-      </c>
+          <t>6142817080</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4043,60 +4063,56 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28-01-1994</t>
+          <t>24-11-1998</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>JOSS0194@HOTMAIL.COM</t>
+          <t>CARLOSBEL395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10-02-2025 17:19:45</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>06-02-2026 18:16:57</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>03-02-2026 07:23:51</t>
+          <t>11-02-2026 19:03:53</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>03-02-2026 07:22:24</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4104,7 +4120,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26200522031990001330</t>
+          <t>26200522275860001803</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4112,10 +4128,14 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4132,12 +4152,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>331503</t>
+          <t>341663</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4147,7 +4167,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>NAOMI ALEJANDRA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4157,7 +4177,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HERMOSILLO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4167,75 +4187,67 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6143556958</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>MINA LOS REYES 3722</t>
-        </is>
-      </c>
+          <t>6145973271</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>29-01-1999</t>
+          <t>15-05-1998</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>GON.HERM.JA1534@GMAIL.COM</t>
+          <t>NAOMI998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-01-2026 11:17:55</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>06-02-2026 18:20:37</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 11:20:21</t>
+          <t>11-02-2026 19:04:57</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>09-02-2026 11:19:32</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4243,7 +4255,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26200522188810001604</t>
+          <t>26200522275940001804</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4258,29 +4270,29 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>340085</t>
+          <t>342175</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4290,17 +4302,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EDNA ODALYS</t>
+          <t>MARCO IVAN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t xml:space="preserve">MOLINAR </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BARREA</t>
+          <t>CANTU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4310,67 +4322,63 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6143185738</t>
+          <t>6141719602</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C SALVADOR DIAZ CASAS 57</t>
+          <t>ERNESTO ESPINOZA 269</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18-05-1999</t>
+          <t>16-04-1996</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
+          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-02-2026 12:27:34</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:21:30</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-02-2026 12:31:44</t>
+          <t>09-02-2026 14:25:15</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-02-2026 12:30:57</t>
+          <t>09-02-2026 14:23:33</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4390,36 +4398,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26200522008980001294</t>
+          <t>26200522193020001613</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342110</t>
+          <t>342308</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4429,17 +4437,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MARIO EDGARDO</t>
+          <t>DANIEL ANTONIO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">SERRANO </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4449,12 +4457,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6144714471</t>
+          <t>6271210648</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CDA PUERTA DE GRANADA 2821</t>
+          <t>REPUBLICA DOMINICANA 20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4464,17 +4472,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20-02-1987</t>
+          <t>27-03-1999</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>SILVAOLIVASM@GMAIL.COM</t>
+          <t>THEHRHH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:22:59</t>
+          <t>09-02-2026 17:12:49</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4485,7 +4493,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4495,7 +4503,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:26:28</t>
+          <t>09-02-2026 17:19:08</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4505,7 +4513,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:25:37</t>
+          <t>09-02-2026 17:16:19</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4515,7 +4523,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4525,7 +4533,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26200522188970001605</t>
+          <t>26200522201590001646</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4537,24 +4545,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342364</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4564,17 +4572,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CLAUDIA LESLIE</t>
+          <t xml:space="preserve">RAFAEL </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t xml:space="preserve">LOERA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>SAEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4584,32 +4592,28 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6143534589</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>CIUDAD DURANGO 31125</t>
-        </is>
-      </c>
+          <t>6144270811</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19-01-2000</t>
+          <t>22-08-1977</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>LESLIEMILLA09@GMAIL.COM</t>
+          <t>VLOERASAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 18:00:59</t>
+          <t>09-02-2026 17:05:24</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4619,44 +4623,36 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 18:08:11</t>
+          <t>09-02-2026 17:07:07</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:07:44</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4664,14 +4660,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26200522205660001656</t>
+          <t>26200522200740001643</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4688,12 +4684,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>340868</t>
+          <t>344164</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4703,17 +4699,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ADRIAN </t>
+          <t>KAROL AMAIRANY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>SIFUENTES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4723,79 +4719,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6142166555</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>CTO TERRANOVA 2803</t>
-        </is>
-      </c>
+          <t>6145128509</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>03-11-1986</t>
+          <t>21-01-1999</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>LUIS_ADRIANMC@HOTMAIL.COM</t>
+          <t>TIJUANAMARUNGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>04-02-2026 06:30:38</t>
+          <t>16-02-2026 16:26:56</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>04-02-2026 06:34:33</t>
+          <t>23-02-2026 16:21:52</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>04-02-2026 06:33:26</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4803,19 +4787,27 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26200522067340001402</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26200522586800002330</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4827,12 +4819,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>344164</t>
+          <t>342661</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4842,17 +4834,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KAROL AMAIRANY</t>
+          <t xml:space="preserve">JOSE ALONSO </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SIFUENTES</t>
+          <t xml:space="preserve">CORDERO </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4862,67 +4854,75 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6145128509</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6143546193</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MONTE ALTAI 4323</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21-01-1999</t>
+          <t>20-04-1982</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>TIJUANAMARUNGO@GMAIL.COM</t>
+          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16-02-2026 16:26:56</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:13:05</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>23-02-2026 16:21:52</t>
+          <t>10-02-2026 15:19:33</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:16:36</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4930,44 +4930,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26200522586800002330</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522234120001697</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>341505</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4977,17 +4969,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARBARA </t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>DOZAL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>CHACON</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4997,14 +4989,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6143682180</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>SAN JORGE 2600</t>
-        </is>
-      </c>
+          <t>6563497877</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5012,38 +5000,42 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15-09-2006</t>
+          <t>30-01-2003</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>VALERIAR150906@GMAIL.COM</t>
+          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>06-02-2026 10:10:46</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>10-02-2026 17:45:06</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10-02-2026 05:14:42</t>
+          <t>10-02-2026 17:46:42</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5051,21 +5043,13 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:13:41</t>
-        </is>
-      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5073,27 +5057,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26200522217020001672</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522241060001732</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5105,12 +5081,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342175</t>
+          <t>343806</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5120,17 +5096,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MARCO IVAN</t>
+          <t>JESUS RUBEN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLINAR </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CANTU</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5140,12 +5116,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6141719602</t>
+          <t>6141109571</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ERNESTO ESPINOZA 269</t>
+          <t>DESIERTO DEL SAHARA 3706</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5155,17 +5131,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16-04-1996</t>
+          <t>20-06-1989</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
+          <t>JESUSRUBEN201989@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 14:21:30</t>
+          <t>15-02-2026 11:10:14</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5176,7 +5152,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5186,17 +5162,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 14:25:15</t>
+          <t>15-02-2026 11:12:58</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>09-02-2026 14:23:33</t>
+          <t>15-02-2026 11:11:57</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5206,7 +5182,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5216,7 +5192,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26200522193020001613</t>
+          <t>26200522364120001933</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5240,12 +5216,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342298</t>
+          <t>342256</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5255,17 +5231,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL </t>
+          <t>EIMY ANAHI</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOERA </t>
+          <t xml:space="preserve">TOBARA </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAEZ</t>
+          <t>ALCANTAR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5275,67 +5251,75 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6144270811</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6145118271</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ALAMEDAS 311</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22-08-1977</t>
+          <t>30-09-1990</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>VLOERASAEZ@GMAIL.COM</t>
+          <t>EIMI09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 17:05:24</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:30:52</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-02-2026 17:07:07</t>
+          <t>11-02-2026 16:42:43</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>11-02-2026 16:42:01</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5343,14 +5327,22 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26200522200740001643</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26200522269260001777</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5367,12 +5359,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343806</t>
+          <t>342260</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5382,17 +5374,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JESUS RUBEN</t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">VILLALOBOS </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5402,12 +5394,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6141109571</t>
+          <t>6144616643</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DESIERTO DEL SAHARA 3706</t>
+          <t>PROLETARIOS 19</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5417,17 +5409,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>20-06-1989</t>
+          <t>28-02-1992</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JESUSRUBEN201989@ICLOUD.COM</t>
+          <t>JOSEEDUA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>15-02-2026 11:10:14</t>
+          <t>09-02-2026 16:34:00</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5438,7 +5430,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -5448,17 +5440,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>15-02-2026 11:12:58</t>
+          <t>11-02-2026 16:44:25</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>15-02-2026 11:11:57</t>
+          <t>11-02-2026 16:43:52</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5478,11 +5470,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26200522364120001933</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26200522269350001778</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>499</t>
@@ -5502,12 +5502,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344674</t>
+          <t>342280</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ABRAHM</t>
+          <t>ALAN EDUARDO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>TAMEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5537,14 +5537,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6147767384</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>CALLE DOLORES PIMENTEL</t>
-        </is>
-      </c>
+          <t>6146114137</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5552,64 +5548,56 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>22-03-1999</t>
+          <t>07-12-1999</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
+          <t>ALANEDU09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17-02-2026 19:04:34</t>
+          <t>09-02-2026 16:46:37</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>17-02-2026 19:10:12</t>
+          <t>09-02-2026 16:47:42</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>17-02-2026 19:08:30</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5617,14 +5605,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26200522443540002095</t>
+          <t>26200522199520001636</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5641,12 +5629,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342308</t>
+          <t>342346</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5656,17 +5644,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DANIEL ANTONIO</t>
+          <t>SOFIA VICTORIA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERRANO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5676,32 +5664,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6271210648</t>
+          <t>6141631910</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>REPUBLICA DOMINICANA 20</t>
+          <t>CAFETALES</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27-03-1999</t>
+          <t>03-01-2007</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>THEHRHH@GMAIL.COM</t>
+          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>09-02-2026 17:12:49</t>
+          <t>09-02-2026 17:42:44</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5712,7 +5700,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -5722,7 +5710,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>09-02-2026 17:19:08</t>
+          <t>09-02-2026 17:47:57</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5732,7 +5720,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>09-02-2026 17:16:19</t>
+          <t>09-02-2026 17:47:26</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5742,7 +5730,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5752,7 +5740,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26200522201590001646</t>
+          <t>26200522203900001653</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5764,24 +5752,24 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344070</t>
+          <t>342319</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5791,17 +5779,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DORIAN</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t xml:space="preserve">OLIVAS </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESENDIZ </t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5811,10 +5799,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3315999428</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6491107772</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>REPUBLICA DOMINICANA</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5822,56 +5814,60 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>12-10-2005</t>
+          <t>19-11-1998</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>DORIAN_ROMERO@JABIL.COM</t>
+          <t>OLIVASNANCY086@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>16-02-2026 13:29:06</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:21:10</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>23-02-2026 13:26:14</t>
+          <t>09-02-2026 17:23:56</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:23:32</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5879,22 +5875,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26200522580570002314</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
-        </is>
-      </c>
+          <t>26200522202050001649</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5911,12 +5899,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344118</t>
+          <t>344070</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5926,17 +5914,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ABRIL PAOLA</t>
+          <t>DORIAN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GALLEGOS</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TARANGO</t>
+          <t xml:space="preserve">RESENDIZ </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5946,7 +5934,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6147370020</t>
+          <t>3315999428</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5957,17 +5945,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>23-07-2003</t>
+          <t>12-10-2005</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ABRILPG19@GMAIL.COM</t>
+          <t>DORIAN_ROMERO@JABIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-02-2026 15:15:42</t>
+          <t>16-02-2026 13:29:06</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5992,7 +5980,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>23-02-2026 16:28:38</t>
+          <t>23-02-2026 13:26:14</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -6003,7 +5991,7 @@
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
@@ -6014,7 +6002,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26200522587190002333</t>
+          <t>26200522580570002314</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -6024,7 +6012,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6034,24 +6022,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>342761</t>
+          <t>344118</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6061,17 +6049,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>ABRIL PAOLA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DOZAL</t>
+          <t>GALLEGOS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CHACON</t>
+          <t>TARANGO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6081,7 +6069,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6563497877</t>
+          <t>6147370020</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6092,22 +6080,22 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>30-01-2003</t>
+          <t>23-07-2003</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
+          <t>ABRILPG19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>10-02-2026 17:45:06</t>
+          <t>16-02-2026 15:15:42</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6127,18 +6115,18 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>10-02-2026 17:46:42</t>
+          <t>23-02-2026 16:28:38</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -6149,11 +6137,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26200522241060001732</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+          <t>26200522587190002333</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>549</t>
@@ -6173,12 +6169,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>345838</t>
+          <t>342395</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>88003</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6188,17 +6184,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ESMERALDA</t>
+          <t>ALISON</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>VILLALBA</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LASCANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6208,12 +6204,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6144743555</t>
+          <t>6142511165</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MONTES ALPES 11914</t>
+          <t>MARK TWAIN 500</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6223,24 +6219,20 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>22-03-1994</t>
+          <t>08-10-2000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ESMERALDA_220229@ICLOUD.COM</t>
+          <t>ALISONMONTES00@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>23-02-2026 15:31:03</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:32:20</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6248,7 +6240,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6258,17 +6250,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>23-02-2026 15:57:07</t>
+          <t>09-02-2026 18:40:18</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:58</t>
+          <t>09-02-2026 18:39:43</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6288,14 +6280,10 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26200522585800002325</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26200522207950001662</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6304,7 +6292,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6316,12 +6304,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>342661</t>
+          <t>342901</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>20718</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6331,17 +6319,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ALONSO </t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORDERO </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6351,32 +6339,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6143546193</t>
+          <t>6142443644</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MONTE ALTAI 4323</t>
+          <t>PRIV DE GONZALEZ COSSIO 6734</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20-04-1982</t>
+          <t>08-03-1963</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
+          <t>LEOTO056@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>10-02-2026 15:13:05</t>
+          <t>11-02-2026 08:12:54</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6397,17 +6385,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>10-02-2026 15:19:33</t>
+          <t>11-02-2026 08:29:30</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>10-02-2026 15:16:36</t>
+          <t>11-02-2026 08:28:18</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6427,10 +6415,14 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26200522234120001697</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
+          <t>26200522259660001758</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6439,24 +6431,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342319</t>
+          <t>344674</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6466,17 +6458,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>ABRAHM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVAS </t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6486,35 +6478,39 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6491107772</t>
+          <t>6147767384</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>REPUBLICA DOMINICANA</t>
+          <t>CALLE DOLORES PIMENTEL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19-11-1998</t>
+          <t>22-03-1999</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>OLIVASNANCY086@GMAIL.COM</t>
+          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:10</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>17-02-2026 19:04:34</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6522,7 +6518,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6532,17 +6528,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:56</t>
+          <t>17-02-2026 19:10:12</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:32</t>
+          <t>17-02-2026 19:08:30</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6562,7 +6558,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26200522202050001649</t>
+          <t>26200522443540002095</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6586,12 +6582,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>345907</t>
+          <t>344209</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6601,17 +6597,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JAIMIE</t>
+          <t>ELBA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>VALVERDE</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6621,14 +6617,10 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6144790343</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>CHE GUEVARA</t>
-        </is>
-      </c>
+          <t>6141057797</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6636,17 +6628,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>16-08-2004</t>
+          <t>01-06-1967</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
+          <t>MARIAHDZ67000@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>23-02-2026 17:09:43</t>
+          <t>16-02-2026 17:19:53</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6656,44 +6648,36 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>23-02-2026 17:14:20</t>
+          <t>18-02-2026 16:45:06</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:13:54</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6701,19 +6685,27 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26200522590120002343</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26200522467120002145</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6725,12 +6717,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>345918</t>
+          <t>344167</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6740,17 +6732,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JESSER URIEL</t>
+          <t>JONATHAN MANUEL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>MARUNGO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6760,14 +6752,10 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6141611733</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>MINA GLAMIS 1914</t>
-        </is>
-      </c>
+          <t>6142467576</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6775,42 +6763,42 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>20-04-2001</t>
+          <t>19-06-1985</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>URIELPORTILLO951@GMAIL.COM</t>
+          <t>TIJUANAMHMARUNGO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>23-02-2026 17:21:49</t>
+          <t>16-02-2026 16:31:02</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>23-02-2026 17:29:11</t>
+          <t>23-02-2026 16:25:12</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6818,21 +6806,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:27:48</t>
-        </is>
-      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6840,14 +6820,22 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26200522590980002346</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
+          <t>26200522586990002331</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6864,12 +6852,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>344200</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6879,17 +6867,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t>MAGDALENA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>BALDERRAMA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>AVELAR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6899,12 +6887,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6142443644</t>
+          <t>6391115826</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PRIV DE GONZALEZ COSSIO 6734</t>
+          <t>COL SANTO NIÑO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6914,48 +6902,52 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>08-03-1963</t>
+          <t>10-01-1971</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>LEOTO056@GMAIL.COM</t>
+          <t>MAGDAURIBE10@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>11-02-2026 08:12:54</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>16-02-2026 17:13:45</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>11-02-2026 08:29:30</t>
+          <t>18-02-2026 18:02:37</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>11-02-2026 08:28:18</t>
+          <t>18-02-2026 18:01:54</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6965,7 +6957,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6975,40 +6967,44 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26200522259660001758</t>
+          <t>26200522471160002153</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344209</t>
+          <t>345838</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>88003</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7018,17 +7014,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ELBA</t>
+          <t>ESMERALDA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>VILLALBA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>LASCANO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7038,10 +7034,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6141057797</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6144743555</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>MONTES ALPES 11914</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7049,56 +7049,64 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>01-06-1967</t>
+          <t>22-03-1994</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MARIAHDZ67000@HOTMAIL.COM</t>
+          <t>ESMERALDA_220229@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:53</t>
+          <t>23-02-2026 15:31:03</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:06</t>
+          <t>23-02-2026 15:57:07</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:54:58</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7106,22 +7114,18 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26200522467120002145</t>
+          <t>26200522585800002325</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7138,12 +7142,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345942</t>
+          <t>343805</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>88107</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7153,17 +7157,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ADRIANA AURORA</t>
+          <t xml:space="preserve">ROSA IRENE </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7173,10 +7177,14 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6143970735</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>6143813334</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>RIO META 1803</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7184,56 +7192,60 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>09-02-2002</t>
+          <t>24-06-1984</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ADRIANA72270@GMAIL.COM</t>
+          <t>ROSYSOTO24@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>23-02-2026 17:47:34</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>15-02-2026 10:57:33</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>23-02-2026 17:48:54</t>
+          <t>15-02-2026 11:04:14</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>15-02-2026 11:01:26</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7241,36 +7253,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26200522592530002354</t>
+          <t>26200522364020001931</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344167</t>
+          <t>344234</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7280,17 +7292,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JONATHAN MANUEL</t>
+          <t>JONATHA IVAN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MARUNGO</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7300,7 +7312,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6142467576</t>
+          <t>6141324957</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7311,22 +7323,22 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>19-06-1985</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>TIJUANAMHMARUNGO@HOTMAIL.COM</t>
+          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>16-02-2026 16:31:02</t>
+          <t>16-02-2026 17:44:53</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -7346,18 +7358,18 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-02-2026 16:25:12</t>
+          <t>16-02-2026 17:46:24</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -7368,19 +7380,11 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26200522586990002331</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522400880002009</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
           <t>549</t>
@@ -7400,12 +7404,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344200</t>
+          <t>344116</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7415,17 +7419,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MAGDALENA</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BALDERRAMA</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AVELAR</t>
+          <t>LOZOYA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7435,14 +7439,10 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6391115826</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>COL SANTO NIÑO</t>
-        </is>
-      </c>
+          <t>6143978047</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7450,17 +7450,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>10-01-1971</t>
+          <t>21-10-1996</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>MAGDAURIBE10@HOTMAIL.COM</t>
+          <t>SUGEYPONLOZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 17:13:45</t>
+          <t>16-02-2026 15:12:06</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-02-2026 18:02:37</t>
+          <t>18-02-2026 15:52:54</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -7493,21 +7493,13 @@
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>18-02-2026 18:01:54</t>
-        </is>
-      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7515,7 +7507,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26200522471160002153</t>
+          <t>26200522464950002139</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7530,29 +7522,29 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343805</t>
+          <t>344677</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7562,17 +7554,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA IRENE </t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>MORELOS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7582,75 +7574,67 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6143813334</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>RIO META 1803</t>
-        </is>
-      </c>
+          <t>6144072330</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>24-06-1984</t>
+          <t>15-02-2004</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ROSYSOTO24@ICLOUD.COM</t>
+          <t>CG8165424@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>15-02-2026 10:57:33</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>17-02-2026 19:12:24</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>15-02-2026 11:04:14</t>
+          <t>17-02-2026 19:13:46</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>15-02-2026 11:01:26</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7658,36 +7642,36 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26200522364020001931</t>
+          <t>26200522443700002096</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344234</t>
+          <t>345907</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7697,17 +7681,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JONATHA IVAN</t>
+          <t>JAIMIE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>VALVERDE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7717,28 +7701,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6141324957</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>6144790343</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>CHE GUEVARA</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>16-08-2004</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
+          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>16-02-2026 17:44:53</t>
+          <t>23-02-2026 17:09:43</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7748,36 +7736,44 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>16-02-2026 17:46:24</t>
+          <t>23-02-2026 17:14:20</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:13:54</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7785,19 +7781,19 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26200522400880002009</t>
+          <t>26200522590120002343</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7809,12 +7805,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344116</t>
+          <t>345918</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7824,17 +7820,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>JESSER URIEL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LOZOYA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7844,67 +7840,79 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6143978047</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6141611733</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>MINA GLAMIS 1914</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>21-10-1996</t>
+          <t>20-04-2001</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>SUGEYPONLOZ@GMAIL.COM</t>
+          <t>URIELPORTILLO951@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 15:12:06</t>
+          <t>23-02-2026 17:21:49</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>18-02-2026 15:52:54</t>
+          <t>23-02-2026 17:29:11</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:27:48</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7912,27 +7920,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26200522464950002139</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522590980002346</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7944,12 +7944,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344677</t>
+          <t>345906</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7959,17 +7959,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>ESLY YAZMIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">VALVERDE </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7979,28 +7979,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6144072330</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>6142830714</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CHE GUEVARA</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>15-02-2004</t>
+          <t>19-01-1997</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CG8165424@GMAIL.COM</t>
+          <t>YAZMINREYES566@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>17-02-2026 19:12:24</t>
+          <t>23-02-2026 17:09:02</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8010,36 +8014,44 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>17-02-2026 19:13:46</t>
+          <t>23-02-2026 17:16:35</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:16:04</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8047,14 +8059,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26200522443700002096</t>
+          <t>26200522590290002344</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8071,12 +8083,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>345906</t>
+          <t>345942</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>88107</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8086,17 +8098,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ESLY YAZMIN</t>
+          <t>ADRIANA AURORA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALVERDE </t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8106,14 +8118,10 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6142830714</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>CHE GUEVARA</t>
-        </is>
-      </c>
+          <t>6143970735</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8121,42 +8129,42 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>19-01-1997</t>
+          <t>09-02-2002</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>YAZMINREYES566@GMAIL.COM</t>
+          <t>ADRIANA72270@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>23-02-2026 17:09:02</t>
+          <t>23-02-2026 17:47:34</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>23-02-2026 17:16:35</t>
+          <t>23-02-2026 17:48:54</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8164,21 +8172,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:16:04</t>
-        </is>
-      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8186,19 +8186,19 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26200522590290002344</t>
+          <t>26200522592530002354</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -852,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301635</t>
+          <t>339397</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>99133</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YODGAR JASIEL </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LOERA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CABALLERO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,10 +887,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6146099932</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6143368528</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CALLE DE METER 5510</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -898,56 +902,60 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18-06-2008</t>
+          <t>07-12-1998</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CG569407@GMAIL.COM</t>
+          <t>TBRBEANS98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>01-07-2025 19:06:32</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>30-01-2026 16:37:06</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17-02-2026 19:16:14</t>
+          <t>02-02-2026 17:39:05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:37:49</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,36 +963,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26200522443750002097</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26200522019070001314</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>288404</t>
+          <t>340080</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>85902</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRISTIAN ALAN</t>
+          <t>YARELI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,53 +1030,57 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6144545766</t>
+          <t>6142757940</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ALCATIFA 15115</t>
+          <t>C RUBEN JARAMILLO 214</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>08-05-2008</t>
+          <t>05-01-1996</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CRISALANCASTA_1985@GMAIL.COM</t>
+          <t>YARELI.H9628@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16-04-2025 13:38:48</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>02-02-2026 12:19:55</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 12:44:05</t>
+          <t>02-02-2026 12:24:36</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1070,7 +1090,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 12:41:04</t>
+          <t>02-02-2026 12:24:04</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1080,7 +1100,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1090,18 +1110,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26200522009480001296</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26200522008710001292</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1118,12 +1134,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>339397</t>
+          <t>301635</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>99133</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1149,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">YODGAR JASIEL </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LOERA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CABALLERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,14 +1169,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6143368528</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CALLE DE METER 5510</t>
-        </is>
-      </c>
+          <t>6146099932</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1168,60 +1180,56 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>07-12-1998</t>
+          <t>18-06-2008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>TBRBEANS98@GMAIL.COM</t>
+          <t>CG569407@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>30-01-2026 16:37:06</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>01-07-2025 19:06:32</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 17:39:05</t>
+          <t>17-02-2026 19:16:14</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-02-2026 17:37:49</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1229,44 +1237,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200522019070001314</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522443750002097</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340080</t>
+          <t>340527</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>YARELI</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,32 +1296,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6142757940</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>C RUBEN JARAMILLO 214</t>
-        </is>
-      </c>
+          <t>8112983028</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>05-01-1996</t>
+          <t>29-10-1984</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>YARELI.H9628@GMAIL.COM</t>
+          <t>JULIO565@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 12:19:55</t>
+          <t>03-02-2026 11:45:26</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1331,44 +1327,36 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 12:24:36</t>
+          <t>03-02-2026 11:51:04</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-02-2026 12:24:04</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1376,24 +1364,24 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26200522008710001292</t>
+          <t>26200522037480001340</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1523,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>278704</t>
+          <t>341105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>76205</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1538,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ANIBAL</t>
+          <t>ELIANA JANETH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GAYTAN</t>
+          <t xml:space="preserve">GAYTAN </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,32 +1558,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8129739105</t>
+          <t>6146308375</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CALLE FRANCISCO PIMENTEL 5115</t>
+          <t>CALLE DELICIAS</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>08-12-1998</t>
+          <t>12-04-1992</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>GAYTAN.ANIBAL@GMAIL.COM</t>
+          <t>ELI.GAYTTAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12-02-2025 19:17:51</t>
+          <t>04-02-2026 17:21:04</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1606,7 +1594,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1616,17 +1604,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>14-02-2026 09:21:50</t>
+          <t>04-02-2026 17:24:25</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>14-02-2026 09:16:25</t>
+          <t>04-02-2026 17:23:58</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1646,14 +1634,10 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26200522344660001916</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522082280001431</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1662,24 +1646,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>299297</t>
+          <t>341037</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>96795</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1689,17 +1673,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>XIMENA</t>
+          <t>HEDER ARTURO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DE LA ROSA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1709,67 +1693,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6143701479</t>
+          <t>6145315107</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CENTAURO DEL NORTE</t>
+          <t xml:space="preserve">PASEOS DE JUAREZ </t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26-08-2005</t>
+          <t>24-07-1983</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>XIMENADELAROSA42@GMAIL.COM</t>
+          <t>HEDER1930@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19-06-2025 09:42:01</t>
+          <t>04-02-2026 15:22:46</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>19-02-2026 12:14:40</t>
+          <t>04-02-2026 15:26:49</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>19-02-2026 11:40:58</t>
+          <t>04-02-2026 15:26:11</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1789,22 +1773,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26200522492700002183</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522077360001418</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1821,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>316379</t>
+          <t>341507</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1836,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>KARELIA EDITH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>GANDARILLA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LUGO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1856,67 +1832,75 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6144687095</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6391727197</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SAN JORGE 2600</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12-04-2007</t>
+          <t>02-04-2006</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>RIVERA.LUGO.SE07@GMAIL.COM</t>
+          <t>KAREEGD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>29-09-2025 19:06:54</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 10:13:27</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-02-2026 17:45:36</t>
+          <t>10-02-2026 05:11:01</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:10:28</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1924,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26200522203750001652</t>
+          <t>26200522216950001671</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1934,34 +1918,34 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>IVONNE HERNANDEZ RIVERA</t>
+          <t>DIANA EDITH BARRAZA DURAN</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340527</t>
+          <t>341661</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1971,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1991,7 +1975,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8112983028</t>
+          <t>6142817080</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2002,17 +1986,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>29-10-1984</t>
+          <t>24-11-1998</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JULIO565@GMAIL.COM</t>
+          <t>CARLOSBEL395@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-02-2026 11:45:26</t>
+          <t>06-02-2026 18:16:57</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2037,12 +2021,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-02-2026 11:51:04</t>
+          <t>11-02-2026 19:03:53</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2059,11 +2043,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26200522037480001340</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26200522275860001803</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2071,24 +2063,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>326034</t>
+          <t>341663</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GILBERTO</t>
+          <t>NAOMI ALEJANDRA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,33 +2110,33 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6141834791</t>
+          <t>6145973271</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>05-06-1997</t>
+          <t>15-05-1998</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>GILGUTIERREZV013@GMAIL.COM</t>
+          <t>NAOMI998@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>30-11-2025 11:31:22</t>
+          <t>06-02-2026 18:20:37</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>anualidad LE 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2154,22 +2146,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ANUALIDAD + MES REGALO $5,999</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>461.46</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>10-02-2026 19:16:06</t>
+          <t>11-02-2026 19:04:57</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>10-03-2027 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2186,14 +2178,22 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26200522246270001744</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26200522275940001804</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2210,12 +2210,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>341568</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>75778</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAVIER OMAR </t>
+          <t>GRECIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>AVILA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CEBALLOS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6142791568</t>
+          <t>6142139312</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GARCILAZO DE LA VEGA 15300</t>
+          <t>ERNESTO ESPINOZA 269</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28-01-1994</t>
+          <t>01-04-1992</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JOSS0194@HOTMAIL.COM</t>
+          <t>AVILAGRECIA8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10-02-2025 17:19:45</t>
+          <t>06-02-2026 14:00:17</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 07:23:51</t>
+          <t>09-02-2026 14:29:47</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-02-2026 07:22:24</t>
+          <t>09-02-2026 14:29:29</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26200522031990001330</t>
+          <t>26200522193120001614</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE RECORRIDO</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr"/>
@@ -2349,12 +2349,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341037</t>
+          <t>278704</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>76205</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,17 +2364,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HEDER ARTURO</t>
+          <t>ANIBAL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>GAYTAN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6145315107</t>
+          <t>8129739105</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASEOS DE JUAREZ </t>
+          <t>CALLE FRANCISCO PIMENTEL 5115</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2399,52 +2399,48 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24-07-1983</t>
+          <t>08-12-1998</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>HEDER1930@HOTMAIL.COM</t>
+          <t>GAYTAN.ANIBAL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>04-02-2026 15:22:46</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2025 19:17:51</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>04-02-2026 15:26:49</t>
+          <t>14-02-2026 09:21:50</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>04-02-2026 15:26:11</t>
+          <t>14-02-2026 09:16:25</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2464,14 +2460,18 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26200522077360001418</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26200522344660001916</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2488,12 +2488,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>299297</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>96795</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2503,17 +2503,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAYELI ADAMARI </t>
+          <t>XIMENA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>DE LA ROSA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6144630791</t>
+          <t>6143701479</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL SAENZ 14123</t>
+          <t>CENTAURO DEL NORTE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2538,20 +2538,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20-07-2001</t>
+          <t>26-08-2005</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
+          <t>XIMENADELAROSA42@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>05-02-2026 10:04:55</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>19-06-2025 09:42:01</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2559,7 +2563,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2569,17 +2573,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 18:35:53</t>
+          <t>19-02-2026 12:14:40</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:57</t>
+          <t>19-02-2026 11:40:58</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2599,15 +2603,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26200522207710001661</t>
+          <t>26200522492700002183</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>499</t>
@@ -2627,12 +2635,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>331503</t>
+          <t>288404</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>85902</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2642,17 +2650,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JOSE ALBERTO</t>
+          <t>CRISTIAN ALAN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HERMOSILLO</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2662,12 +2670,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6143556958</t>
+          <t>6144545766</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MINA LOS REYES 3722</t>
+          <t>ALCATIFA 15115</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2677,17 +2685,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29-01-1999</t>
+          <t>08-05-2008</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>GON.HERM.JA1534@GMAIL.COM</t>
+          <t>CRISALANCASTA_1985@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-01-2026 11:17:55</t>
+          <t>16-04-2025 13:38:48</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2708,17 +2716,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 11:20:21</t>
+          <t>02-02-2026 12:44:05</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:32</t>
+          <t>02-02-2026 12:41:04</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2728,7 +2736,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2738,19 +2746,15 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26200522188810001604</t>
+          <t>26200522009480001296</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>499</t>
@@ -2758,24 +2762,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341100</t>
+          <t>326034</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2789,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR MANUEL </t>
+          <t>GILBERTO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTOYO</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,14 +2809,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6142518849</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CALLE DELCIAS</t>
-        </is>
-      </c>
+          <t>6141834791</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2820,60 +2820,56 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25-10-1989</t>
+          <t>05-06-1997</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MANUEL654@GMAIL.COM</t>
+          <t>GILGUTIERREZV013@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 17:15:41</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>30-11-2025 11:31:22</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>anualidad LE 300</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>461.46</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-02-2026 17:19:37</t>
+          <t>10-02-2026 19:16:06</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>04-02-2026 17:19:05</t>
-        </is>
-      </c>
+          <t>10-03-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2881,14 +2877,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26200522081990001429</t>
+          <t>26200522246270001744</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2905,12 +2901,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>341568</t>
+          <t>278277</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>75778</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2920,17 +2916,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GRECIA</t>
+          <t xml:space="preserve">JAVIER OMAR </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AVILA</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CEBALLOS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2940,32 +2936,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6142139312</t>
+          <t>6142791568</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ERNESTO ESPINOZA 269</t>
+          <t>GARCILAZO DE LA VEGA 15300</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>01-04-1992</t>
+          <t>28-01-1994</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>AVILAGRECIA8@GMAIL.COM</t>
+          <t>JOSS0194@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>06-02-2026 14:00:17</t>
+          <t>10-02-2025 17:19:45</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2976,7 +2972,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2986,17 +2982,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-02-2026 14:29:47</t>
+          <t>03-02-2026 07:23:51</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>09-02-2026 14:29:29</t>
+          <t>03-02-2026 07:22:24</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3006,7 +3002,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3016,12 +3012,12 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26200522193120001614</t>
+          <t>26200522031990001330</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr"/>
@@ -3044,12 +3040,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340085</t>
+          <t>342256</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3059,17 +3055,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EDNA ODALYS</t>
+          <t>EIMY ANAHI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t xml:space="preserve">TOBARA </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BARREA</t>
+          <t>ALCANTAR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3079,12 +3075,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6143185738</t>
+          <t>6145118271</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C SALVADOR DIAZ CASAS 57</t>
+          <t>ALAMEDAS 311</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3094,52 +3090,48 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18-05-1999</t>
+          <t>30-09-1990</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
+          <t>EIMI09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-02-2026 12:27:34</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:30:52</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-02-2026 12:31:44</t>
+          <t>11-02-2026 16:42:43</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-02-2026 12:30:57</t>
+          <t>11-02-2026 16:42:01</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3149,7 +3141,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3159,36 +3151,44 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26200522008980001294</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26200522269260001777</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342110</t>
+          <t>342260</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3198,17 +3198,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MARIO EDGARDO</t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">VILLALOBOS </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6144714471</t>
+          <t>6144616643</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CDA PUERTA DE GRANADA 2821</t>
+          <t>PROLETARIOS 19</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20-02-1987</t>
+          <t>28-02-1992</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>SILVAOLIVASM@GMAIL.COM</t>
+          <t>JOSEEDUA98@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 11:22:59</t>
+          <t>09-02-2026 16:34:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 11:26:28</t>
+          <t>11-02-2026 16:44:25</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>09-02-2026 11:25:37</t>
+          <t>11-02-2026 16:43:52</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3294,11 +3294,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26200522188970001605</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26200522269350001778</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>499</t>
@@ -3306,24 +3314,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342364</t>
+          <t>342280</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3333,17 +3341,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CLAUDIA LESLIE</t>
+          <t>ALAN EDUARDO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>TAMEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MILLAN</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3353,32 +3361,28 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6143534589</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CIUDAD DURANGO 31125</t>
-        </is>
-      </c>
+          <t>6146114137</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19-01-2000</t>
+          <t>07-12-1999</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>LESLIEMILLA09@GMAIL.COM</t>
+          <t>ALANEDU09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 18:00:59</t>
+          <t>09-02-2026 16:46:37</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3388,22 +3392,22 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-02-2026 18:08:11</t>
+          <t>09-02-2026 16:47:42</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3411,21 +3415,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:07:44</t>
-        </is>
-      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3433,14 +3429,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26200522205660001656</t>
+          <t>26200522199520001636</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3457,12 +3453,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>341105</t>
+          <t>342346</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3472,17 +3468,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ELIANA JANETH</t>
+          <t>SOFIA VICTORIA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAYTAN </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3492,12 +3488,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6146308375</t>
+          <t>6141631910</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CALLE DELICIAS</t>
+          <t>CAFETALES</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3507,17 +3503,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12-04-1992</t>
+          <t>03-01-2007</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ELI.GAYTTAN@GMAIL.COM</t>
+          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>04-02-2026 17:21:04</t>
+          <t>09-02-2026 17:42:44</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3528,7 +3524,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3538,17 +3534,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>04-02-2026 17:24:25</t>
+          <t>09-02-2026 17:47:57</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>04-02-2026 17:23:58</t>
+          <t>09-02-2026 17:47:26</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3558,7 +3554,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3568,7 +3564,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26200522082280001431</t>
+          <t>26200522203900001653</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3580,7 +3576,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3592,12 +3588,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>340868</t>
+          <t>342395</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3607,17 +3603,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ADRIAN </t>
+          <t>ALISON</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3627,39 +3623,35 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6142166555</t>
+          <t>6142511165</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CTO TERRANOVA 2803</t>
+          <t>MARK TWAIN 500</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>03-11-1986</t>
+          <t>08-10-2000</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>LUIS_ADRIANMC@HOTMAIL.COM</t>
+          <t>ALISONMONTES00@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-02-2026 06:30:38</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:32:20</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3667,27 +3659,27 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04-02-2026 06:34:33</t>
+          <t>09-02-2026 18:40:18</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>04-02-2026 06:33:26</t>
+          <t>09-02-2026 18:39:43</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3707,19 +3699,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26200522067340001402</t>
+          <t>26200522207950001662</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3731,12 +3723,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>341505</t>
+          <t>331503</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3746,17 +3738,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARBARA </t>
+          <t>JOSE ALBERTO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>HERMOSILLO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3766,32 +3758,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6143682180</t>
+          <t>6143556958</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SAN JORGE 2600</t>
+          <t>MINA LOS REYES 3722</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15-09-2006</t>
+          <t>29-01-1999</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>VALERIAR150906@GMAIL.COM</t>
+          <t>GON.HERM.JA1534@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>06-02-2026 10:10:46</t>
+          <t>02-01-2026 11:17:55</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3802,7 +3794,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3812,17 +3804,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 05:14:42</t>
+          <t>09-02-2026 11:20:21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-02-2026 05:13:41</t>
+          <t>09-02-2026 11:19:32</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3832,7 +3824,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3842,7 +3834,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26200522217020001672</t>
+          <t>26200522188810001604</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3852,7 +3844,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3874,12 +3866,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341507</t>
+          <t>316379</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3889,17 +3881,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KARELIA EDITH</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GANDARILLA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>LUGO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3909,75 +3901,67 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6391727197</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>SAN JORGE 2600</t>
-        </is>
-      </c>
+          <t>6144687095</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>02-04-2006</t>
+          <t>12-04-2007</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>KAREEGD@GMAIL.COM</t>
+          <t>RIVERA.LUGO.SE07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>06-02-2026 10:13:27</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>29-09-2025 19:06:54</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>10-02-2026 05:11:01</t>
+          <t>09-02-2026 17:45:36</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:10:28</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3985,7 +3969,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26200522216950001671</t>
+          <t>26200522203750001652</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3995,34 +3979,34 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
+          <t>IVONNE HERNANDEZ RIVERA</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341661</t>
+          <t>341259</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4032,17 +4016,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t xml:space="preserve">NAYELI ADAMARI </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4052,67 +4036,75 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6142817080</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6144630791</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL SAENZ 14123</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-11-1998</t>
+          <t>20-07-2001</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CARLOSBEL395@GMAIL.COM</t>
+          <t>NAYELIHDZ2001@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>06-02-2026 18:16:57</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 10:04:55</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>11-02-2026 19:03:53</t>
+          <t>09-02-2026 18:35:53</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>09-02-2026 18:34:57</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4120,22 +4112,18 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26200522275860001803</t>
+          <t>26200522207710001661</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4152,12 +4140,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>341663</t>
+          <t>340085</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4167,17 +4155,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NAOMI ALEJANDRA</t>
+          <t>EDNA ODALYS</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>BARREA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4187,10 +4175,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6145973271</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6143185738</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C SALVADOR DIAZ CASAS 57</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4198,17 +4190,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>15-05-1998</t>
+          <t>18-05-1999</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>NAOMI998@GMAIL.COM</t>
+          <t>ODALYSCHAPARRO40@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>06-02-2026 18:20:37</t>
+          <t>02-02-2026 12:27:34</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4218,36 +4210,44 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>11-02-2026 19:04:57</t>
+          <t>02-02-2026 12:31:44</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>02-02-2026 12:30:57</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4255,44 +4255,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26200522275940001804</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522008980001294</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342175</t>
+          <t>341100</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4302,17 +4294,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MARCO IVAN</t>
+          <t xml:space="preserve">VICTOR MANUEL </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOLINAR </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CANTU</t>
+          <t>SANTOYO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4322,12 +4314,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6141719602</t>
+          <t>6142518849</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ERNESTO ESPINOZA 269</t>
+          <t>CALLE DELCIAS</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4337,17 +4329,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16-04-1996</t>
+          <t>25-10-1989</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
+          <t>MANUEL654@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 14:21:30</t>
+          <t>04-02-2026 17:15:41</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4368,17 +4360,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 14:25:15</t>
+          <t>04-02-2026 17:19:37</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>09-02-2026 14:23:33</t>
+          <t>04-02-2026 17:19:05</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4388,7 +4380,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4398,7 +4390,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26200522193020001613</t>
+          <t>26200522081990001429</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4422,12 +4414,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342308</t>
+          <t>342110</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4437,17 +4429,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DANIEL ANTONIO</t>
+          <t>MARIO EDGARDO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERRANO </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4457,12 +4449,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6271210648</t>
+          <t>6144714471</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>REPUBLICA DOMINICANA 20</t>
+          <t>CDA PUERTA DE GRANADA 2821</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4472,17 +4464,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>27-03-1999</t>
+          <t>20-02-1987</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>THEHRHH@GMAIL.COM</t>
+          <t>SILVAOLIVASM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:12:49</t>
+          <t>09-02-2026 11:22:59</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4493,7 +4485,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4503,7 +4495,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:19:08</t>
+          <t>09-02-2026 11:26:28</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4513,7 +4505,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:16:19</t>
+          <t>09-02-2026 11:25:37</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4523,7 +4515,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4533,7 +4525,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26200522201590001646</t>
+          <t>26200522188970001605</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4545,24 +4537,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342298</t>
+          <t>342364</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4572,17 +4564,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL </t>
+          <t>CLAUDIA LESLIE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOERA </t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAEZ</t>
+          <t>MILLAN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4592,28 +4584,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6144270811</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6143534589</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CIUDAD DURANGO 31125</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22-08-1977</t>
+          <t>19-01-2000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>VLOERASAEZ@GMAIL.COM</t>
+          <t>LESLIEMILLA09@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 17:05:24</t>
+          <t>09-02-2026 18:00:59</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4623,36 +4619,44 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 17:07:07</t>
+          <t>09-02-2026 18:08:11</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>09-02-2026 18:07:44</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4660,14 +4664,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26200522200740001643</t>
+          <t>26200522205660001656</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4684,12 +4688,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>344164</t>
+          <t>340868</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4699,17 +4703,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KAROL AMAIRANY</t>
+          <t xml:space="preserve">LUIS ADRIAN </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SIFUENTES</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4719,67 +4723,79 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6145128509</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6142166555</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>CTO TERRANOVA 2803</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-01-1999</t>
+          <t>03-11-1986</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>TIJUANAMARUNGO@GMAIL.COM</t>
+          <t>LUIS_ADRIANMC@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>16-02-2026 16:26:56</t>
+          <t>04-02-2026 06:30:38</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>23-02-2026 16:21:52</t>
+          <t>04-02-2026 06:34:33</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>04-02-2026 06:33:26</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4787,27 +4803,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26200522586800002330</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522067340001402</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4819,12 +4827,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342661</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4834,17 +4842,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE ALONSO </t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORDERO </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CHAPARRO</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4854,32 +4862,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6143546193</t>
+          <t>6143682180</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MONTE ALTAI 4323</t>
+          <t>SAN JORGE 2600</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20-04-1982</t>
+          <t>15-09-2006</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
+          <t>VALERIAR150906@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 15:13:05</t>
+          <t>06-02-2026 10:10:46</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4890,7 +4898,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4900,7 +4908,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 15:19:33</t>
+          <t>10-02-2026 05:14:42</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4910,7 +4918,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>10-02-2026 15:16:36</t>
+          <t>10-02-2026 05:13:41</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4930,11 +4938,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26200522234120001697</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26200522217020001672</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4942,24 +4958,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342761</t>
+          <t>344164</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4969,17 +4985,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ANDREA</t>
+          <t>KAROL AMAIRANY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DOZAL</t>
+          <t>SIFUENTES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CHACON</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4989,7 +5005,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6563497877</t>
+          <t>6145128509</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5000,22 +5016,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>30-01-2003</t>
+          <t>21-01-1999</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
+          <t>TIJUANAMARUNGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-02-2026 17:45:06</t>
+          <t>16-02-2026 16:26:56</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5035,18 +5051,18 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10-02-2026 17:46:42</t>
+          <t>23-02-2026 16:21:52</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -5057,11 +5073,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26200522241060001732</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26200522586800002330</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>549</t>
@@ -5069,7 +5093,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5081,12 +5105,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343806</t>
+          <t>342308</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5096,19 +5120,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JESUS RUBEN</t>
+          <t>DANIEL ANTONIO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t xml:space="preserve">SERRANO </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>SOTO</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>NAJERA</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>52</t>
@@ -5116,12 +5140,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6141109571</t>
+          <t>6271210648</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>DESIERTO DEL SAHARA 3706</t>
+          <t>REPUBLICA DOMINICANA 20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5131,17 +5155,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20-06-1989</t>
+          <t>27-03-1999</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JESUSRUBEN201989@ICLOUD.COM</t>
+          <t>THEHRHH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15-02-2026 11:10:14</t>
+          <t>09-02-2026 17:12:49</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5152,7 +5176,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5162,17 +5186,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>15-02-2026 11:12:58</t>
+          <t>09-02-2026 17:19:08</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>15-02-2026 11:11:57</t>
+          <t>09-02-2026 17:16:19</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5192,7 +5216,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26200522364120001933</t>
+          <t>26200522201590001646</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5216,12 +5240,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342256</t>
+          <t>342175</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5231,17 +5255,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EIMY ANAHI</t>
+          <t>MARCO IVAN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOBARA </t>
+          <t xml:space="preserve">MOLINAR </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ALCANTAR</t>
+          <t>CANTU</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5251,32 +5275,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6145118271</t>
+          <t>6141719602</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ALAMEDAS 311</t>
+          <t>ERNESTO ESPINOZA 269</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>30-09-1990</t>
+          <t>16-04-1996</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>EIMI09@GMAIL.COM</t>
+          <t>MARCO.MOLINAR3.@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 16:30:52</t>
+          <t>09-02-2026 14:21:30</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5297,17 +5321,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>11-02-2026 16:42:43</t>
+          <t>09-02-2026 14:25:15</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>11-02-2026 16:42:01</t>
+          <t>09-02-2026 14:23:33</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5317,7 +5341,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5327,19 +5351,11 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26200522269260001777</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522193020001613</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
           <t>499</t>
@@ -5359,12 +5375,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342260</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5374,17 +5390,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t xml:space="preserve">RAFAEL </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLALOBOS </t>
+          <t xml:space="preserve">LOERA </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>SAEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5394,14 +5410,10 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6144616643</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>PROLETARIOS 19</t>
-        </is>
-      </c>
+          <t>6144270811</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5409,60 +5421,56 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>28-02-1992</t>
+          <t>22-08-1977</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JOSEEDUA98@GMAIL.COM</t>
+          <t>VLOERASAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 16:34:00</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>09-02-2026 17:05:24</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>11-02-2026 16:44:25</t>
+          <t>09-02-2026 17:07:07</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>11-02-2026 16:43:52</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5470,22 +5478,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26200522269350001778</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522200740001643</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5502,12 +5502,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342280</t>
+          <t>342661</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ALAN EDUARDO</t>
+          <t xml:space="preserve">JOSE ALONSO </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TAMEZ</t>
+          <t xml:space="preserve">CORDERO </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CHAPARRO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5537,10 +5537,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6146114137</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6143546193</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>MONTE ALTAI 4323</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5548,56 +5552,60 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>07-12-1999</t>
+          <t>20-04-1982</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ALANEDU09@GMAIL.COM</t>
+          <t>ALONSO.CORDERO@QUIMICAAC.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-02-2026 16:46:37</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:13:05</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>09-02-2026 16:47:42</t>
+          <t>10-02-2026 15:19:33</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:16:36</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5605,14 +5613,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26200522199520001636</t>
+          <t>26200522234120001697</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5629,12 +5637,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342346</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5644,17 +5652,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SOFIA VICTORIA</t>
+          <t>ANDREA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>DOZAL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>CHACON</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5664,14 +5672,10 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6141631910</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>CAFETALES</t>
-        </is>
-      </c>
+          <t>6563497877</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5679,60 +5683,56 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>03-01-2007</t>
+          <t>30-01-2003</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>SOFIAVICTORIAMTZ03@GMAIL.COM</t>
+          <t>05.DOZAL.ANDREA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>09-02-2026 17:42:44</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>10-02-2026 17:45:06</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>09-02-2026 17:47:57</t>
+          <t>10-02-2026 17:46:42</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:47:26</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5740,14 +5740,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26200522203900001653</t>
+          <t>26200522241060001732</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5764,12 +5764,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342319</t>
+          <t>343806</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5779,17 +5779,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>JESUS RUBEN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVAS </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6491107772</t>
+          <t>6141109571</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>REPUBLICA DOMINICANA</t>
+          <t>DESIERTO DEL SAHARA 3706</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19-11-1998</t>
+          <t>20-06-1989</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>OLIVASNANCY086@GMAIL.COM</t>
+          <t>JESUSRUBEN201989@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:10</t>
+          <t>15-02-2026 11:10:14</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:56</t>
+          <t>15-02-2026 11:12:58</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:32</t>
+          <t>15-02-2026 11:11:57</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26200522202050001649</t>
+          <t>26200522364120001933</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5899,12 +5899,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344070</t>
+          <t>342319</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5914,17 +5914,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DORIAN</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t xml:space="preserve">OLIVAS </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESENDIZ </t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5934,10 +5934,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3315999428</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6491107772</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>REPUBLICA DOMINICANA</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5945,56 +5949,60 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>12-10-2005</t>
+          <t>19-11-1998</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>DORIAN_ROMERO@JABIL.COM</t>
+          <t>OLIVASNANCY086@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-02-2026 13:29:06</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:21:10</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>23-02-2026 13:26:14</t>
+          <t>09-02-2026 17:23:56</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:23:32</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6002,22 +6010,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26200522580570002314</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
-        </is>
-      </c>
+          <t>26200522202050001649</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344118</t>
+          <t>345838</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>88003</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6049,17 +6049,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ABRIL PAOLA</t>
+          <t>ESMERALDA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GALLEGOS</t>
+          <t>VILLALBA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TARANGO</t>
+          <t>LASCANO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6069,10 +6069,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6147370020</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>6144743555</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>MONTES ALPES 11914</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6080,42 +6084,42 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23-07-2003</t>
+          <t>22-03-1994</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ABRILPG19@GMAIL.COM</t>
+          <t>ESMERALDA_220229@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>16-02-2026 15:15:42</t>
+          <t>23-02-2026 15:31:03</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>23-02-2026 16:28:38</t>
+          <t>23-02-2026 15:57:07</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -6123,13 +6127,21 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:54:58</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6137,27 +6149,23 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26200522587190002333</t>
+          <t>26200522585800002325</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6169,12 +6177,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342395</t>
+          <t>344070</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6184,17 +6192,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ALISON</t>
+          <t>DORIAN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">RESENDIZ </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6204,14 +6212,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6142511165</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>MARK TWAIN 500</t>
-        </is>
-      </c>
+          <t>3315999428</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6219,60 +6223,56 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>08-10-2000</t>
+          <t>12-10-2005</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ALISONMONTES00@GMAIL.COM</t>
+          <t>DORIAN_ROMERO@JABIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>09-02-2026 18:32:20</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>16-02-2026 13:29:06</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>09-02-2026 18:40:18</t>
+          <t>23-02-2026 13:26:14</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:39:43</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6280,36 +6280,44 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26200522207950001662</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
+          <t>26200522580570002314</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>344118</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6319,17 +6327,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t>ABRIL PAOLA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>GALLEGOS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>TARANGO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6339,14 +6347,10 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6142443644</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>PRIV DE GONZALEZ COSSIO 6734</t>
-        </is>
-      </c>
+          <t>6147370020</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6354,60 +6358,56 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>08-03-1963</t>
+          <t>23-07-2003</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>LEOTO056@GMAIL.COM</t>
+          <t>ABRILPG19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>11-02-2026 08:12:54</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>16-02-2026 15:15:42</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>11-02-2026 08:29:30</t>
+          <t>23-02-2026 16:28:38</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>11-02-2026 08:28:18</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6415,23 +6415,27 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26200522259660001758</t>
+          <t>26200522587190002333</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6443,12 +6447,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344674</t>
+          <t>342901</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>20718</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6458,17 +6462,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ABRAHM</t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6478,39 +6482,35 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6147767384</t>
+          <t>6142443644</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CALLE DOLORES PIMENTEL</t>
+          <t>PRIV DE GONZALEZ COSSIO 6734</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>22-03-1999</t>
+          <t>08-03-1963</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
+          <t>LEOTO056@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>17-02-2026 19:04:34</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 08:12:54</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6528,17 +6528,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>17-02-2026 19:10:12</t>
+          <t>11-02-2026 08:29:30</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>17-02-2026 19:08:30</t>
+          <t>11-02-2026 08:28:18</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6558,10 +6558,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26200522443540002095</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr"/>
+          <t>26200522259660001758</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
@@ -6570,12 +6574,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6999,12 +7003,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>345838</t>
+          <t>344234</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>88003</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7014,17 +7018,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ESMERALDA</t>
+          <t>JONATHA IVAN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VILLALBA</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LASCANO</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7034,79 +7038,67 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6144743555</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>MONTES ALPES 11914</t>
-        </is>
-      </c>
+          <t>6141324957</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>22-03-1994</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ESMERALDA_220229@ICLOUD.COM</t>
+          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>23-02-2026 15:31:03</t>
+          <t>16-02-2026 17:44:53</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>23-02-2026 15:57:07</t>
+          <t>16-02-2026 17:46:24</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>23-02-2026 15:54:58</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7114,18 +7106,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26200522585800002325</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26200522400880002009</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7277,12 +7265,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344234</t>
+          <t>344674</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7292,7 +7280,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JONATHA IVAN</t>
+          <t>ABRAHM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7302,7 +7290,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7312,10 +7300,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6141324957</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6147767384</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CALLE DOLORES PIMENTEL</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7323,56 +7315,64 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>22-03-1999</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
+          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>16-02-2026 17:44:53</t>
+          <t>17-02-2026 19:04:34</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>16-02-2026 17:46:24</t>
+          <t>17-02-2026 19:10:12</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:08:30</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7380,24 +7380,24 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26200522400880002009</t>
+          <t>26200522443540002095</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -7539,12 +7539,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344677</t>
+          <t>345942</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>88107</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>ADRIANA AURORA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7574,33 +7574,33 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6144072330</t>
+          <t>6143970735</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>15-02-2004</t>
+          <t>09-02-2002</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CG8165424@GMAIL.COM</t>
+          <t>ADRIANA72270@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>17-02-2026 19:12:24</t>
+          <t>23-02-2026 17:47:34</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -7610,28 +7610,28 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>17-02-2026 19:13:46</t>
+          <t>23-02-2026 17:48:54</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V53" t="inlineStr"/>
@@ -7642,19 +7642,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26200522443700002096</t>
+          <t>26200522592530002354</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7666,12 +7666,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>345907</t>
+          <t>344677</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7681,17 +7681,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>JAIMIE</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>VALVERDE</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>MORELOS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7701,32 +7701,28 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6144790343</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>CHE GUEVARA</t>
-        </is>
-      </c>
+          <t>6144072330</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>16-08-2004</t>
+          <t>15-02-2004</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
+          <t>CG8165424@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>23-02-2026 17:09:43</t>
+          <t>17-02-2026 19:12:24</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7736,44 +7732,36 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>23-02-2026 17:14:20</t>
+          <t>17-02-2026 19:13:46</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:13:54</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7781,14 +7769,14 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26200522590120002343</t>
+          <t>26200522443700002096</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
@@ -7805,12 +7793,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>345918</t>
+          <t>345906</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7820,17 +7808,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JESSER URIEL</t>
+          <t>ESLY YAZMIN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t xml:space="preserve">VALVERDE </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7840,57 +7828,57 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6141611733</t>
+          <t>6142830714</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MINA GLAMIS 1914</t>
+          <t>CHE GUEVARA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>20-04-2001</t>
+          <t>19-01-1997</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>URIELPORTILLO951@GMAIL.COM</t>
+          <t>YAZMINREYES566@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>23-02-2026 17:21:49</t>
+          <t>23-02-2026 17:09:02</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>23-02-2026 17:29:11</t>
+          <t>23-02-2026 17:16:35</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -7900,7 +7888,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>23-02-2026 17:27:48</t>
+          <t>23-02-2026 17:16:04</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7910,7 +7898,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7920,19 +7908,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26200522590980002346</t>
+          <t>26200522590290002344</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7944,12 +7932,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>345906</t>
+          <t>345907</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7959,12 +7947,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ESLY YAZMIN</t>
+          <t>JAIMIE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALVERDE </t>
+          <t>VALVERDE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7979,7 +7967,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6142830714</t>
+          <t>6144790343</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7994,17 +7982,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>19-01-1997</t>
+          <t>16-08-2004</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>YAZMINREYES566@GMAIL.COM</t>
+          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>23-02-2026 17:09:02</t>
+          <t>23-02-2026 17:09:43</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8029,7 +8017,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>23-02-2026 17:16:35</t>
+          <t>23-02-2026 17:14:20</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -8039,7 +8027,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>23-02-2026 17:16:04</t>
+          <t>23-02-2026 17:13:54</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8059,7 +8047,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26200522590290002344</t>
+          <t>26200522590120002343</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -8083,12 +8071,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>345942</t>
+          <t>345918</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>88107</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8098,17 +8086,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ADRIANA AURORA</t>
+          <t>JESSER URIEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8118,53 +8106,57 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6143970735</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>6141611733</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>MINA GLAMIS 1914</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>09-02-2002</t>
+          <t>20-04-2001</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ADRIANA72270@GMAIL.COM</t>
+          <t>URIELPORTILLO951@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>23-02-2026 17:47:34</t>
+          <t>23-02-2026 17:21:49</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>23-02-2026 17:48:54</t>
+          <t>23-02-2026 17:29:11</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8172,13 +8164,21 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:27:48</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8186,14 +8186,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26200522592530002354</t>
+          <t>26200522590980002346</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -1261,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340527</t>
+          <t>279168</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>76669</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CARO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,28 +1296,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8112983028</t>
+          <t>6142760908</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>29-10-1984</t>
+          <t>16-11-1992</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JULIO565@GMAIL.COM</t>
+          <t>ARACELYTRUJILLO26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-02-2026 11:45:26</t>
+          <t>17-02-2025 15:57:01</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1332,28 +1332,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-02-2026 11:51:04</t>
+          <t>18-02-2026 07:29:15</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1364,19 +1364,27 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26200522037480001340</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26200522456240002117</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1388,12 +1396,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>279168</t>
+          <t>340527</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1403,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>CARO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1423,28 +1431,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6142760908</t>
+          <t>8112983028</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16-11-1992</t>
+          <t>29-10-1984</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ARACELYTRUJILLO26@GMAIL.COM</t>
+          <t>JULIO565@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17-02-2025 15:57:01</t>
+          <t>03-02-2026 11:45:26</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1459,28 +1467,28 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>18-02-2026 07:29:15</t>
+          <t>03-02-2026 11:51:04</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1491,27 +1499,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26200522456240002117</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522037480001340</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4827,12 +4827,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>341505</t>
+          <t>344164</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARBARA </t>
+          <t>KAROL AMAIRANY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SIFUENTES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4862,14 +4862,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6143682180</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>SAN JORGE 2600</t>
-        </is>
-      </c>
+          <t>6145128509</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4877,60 +4873,56 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>15-09-2006</t>
+          <t>21-01-1999</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VALERIAR150906@GMAIL.COM</t>
+          <t>TIJUANAMARUNGO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>06-02-2026 10:10:46</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>16-02-2026 16:26:56</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 05:14:42</t>
+          <t>23-02-2026 16:21:52</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>10-02-2026 05:13:41</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4938,7 +4930,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26200522217020001672</t>
+          <t>26200522586800002330</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4948,17 +4940,17 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4970,12 +4962,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>344164</t>
+          <t>341505</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4985,17 +4977,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KAROL AMAIRANY</t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SIFUENTES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5005,10 +4997,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6145128509</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6143682180</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SAN JORGE 2600</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5016,56 +5012,60 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>21-01-1999</t>
+          <t>15-09-2006</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>TIJUANAMARUNGO@GMAIL.COM</t>
+          <t>VALERIAR150906@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16-02-2026 16:26:56</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>06-02-2026 10:10:46</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>23-02-2026 16:21:52</t>
+          <t>10-02-2026 05:14:42</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>10-02-2026 05:13:41</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26200522586800002330</t>
+          <t>26200522217020001672</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5083,17 +5083,17 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
+          <t>DIANA EDITH BARRAZA DURAN</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5105,12 +5105,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342308</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DANIEL ANTONIO</t>
+          <t xml:space="preserve">RAFAEL </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERRANO </t>
+          <t xml:space="preserve">LOERA </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SAEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5140,14 +5140,10 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6271210648</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>REPUBLICA DOMINICANA 20</t>
-        </is>
-      </c>
+          <t>6144270811</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5155,60 +5151,56 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>27-03-1999</t>
+          <t>22-08-1977</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>THEHRHH@GMAIL.COM</t>
+          <t>VLOERASAEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:12:49</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>09-02-2026 17:05:24</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:19:08</t>
+          <t>09-02-2026 17:07:07</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:16:19</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5216,14 +5208,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26200522201590001646</t>
+          <t>26200522200740001643</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5375,12 +5367,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342298</t>
+          <t>342308</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5390,17 +5382,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFAEL </t>
+          <t>DANIEL ANTONIO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOERA </t>
+          <t xml:space="preserve">SERRANO </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SAEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5410,10 +5402,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6144270811</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6271210648</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>REPUBLICA DOMINICANA 20</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5421,56 +5417,60 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>22-08-1977</t>
+          <t>27-03-1999</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>VLOERASAEZ@GMAIL.COM</t>
+          <t>THEHRHH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 17:05:24</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:12:49</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-02-2026 17:07:07</t>
+          <t>09-02-2026 17:19:08</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:16:19</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5478,14 +5478,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26200522200740001643</t>
+          <t>26200522201590001646</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5764,12 +5764,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343806</t>
+          <t>342319</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5779,17 +5779,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JESUS RUBEN</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">OLIVAS </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6141109571</t>
+          <t>6491107772</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DESIERTO DEL SAHARA 3706</t>
+          <t>REPUBLICA DOMINICANA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>20-06-1989</t>
+          <t>19-11-1998</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JESUSRUBEN201989@ICLOUD.COM</t>
+          <t>OLIVASNANCY086@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>15-02-2026 11:10:14</t>
+          <t>09-02-2026 17:21:10</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>15-02-2026 11:12:58</t>
+          <t>09-02-2026 17:23:56</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>15-02-2026 11:11:57</t>
+          <t>09-02-2026 17:23:32</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26200522364120001933</t>
+          <t>26200522202050001649</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5899,12 +5899,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342319</t>
+          <t>345838</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>88003</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5914,17 +5914,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>ESMERALDA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVAS </t>
+          <t>VILLALBA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>LASCANO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6491107772</t>
+          <t>6144743555</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>REPUBLICA DOMINICANA</t>
+          <t>MONTES ALPES 11914</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5949,20 +5949,24 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19-11-1998</t>
+          <t>22-03-1994</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>OLIVASNANCY086@GMAIL.COM</t>
+          <t>ESMERALDA_220229@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:21:10</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>23-02-2026 15:31:03</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5970,7 +5974,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -5980,17 +5984,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:56</t>
+          <t>23-02-2026 15:57:07</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>09-02-2026 17:23:32</t>
+          <t>23-02-2026 15:54:58</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6000,7 +6004,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6010,10 +6014,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26200522202050001649</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>26200522585800002325</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6022,24 +6030,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>345838</t>
+          <t>343806</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>88003</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6049,17 +6057,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ESMERALDA</t>
+          <t>JESUS RUBEN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VILLALBA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LASCANO</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6069,39 +6077,35 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6144743555</t>
+          <t>6141109571</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MONTES ALPES 11914</t>
+          <t>DESIERTO DEL SAHARA 3706</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22-03-1994</t>
+          <t>20-06-1989</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ESMERALDA_220229@ICLOUD.COM</t>
+          <t>JESUSRUBEN201989@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>23-02-2026 15:31:03</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 11:10:14</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6119,17 +6123,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>23-02-2026 15:57:07</t>
+          <t>15-02-2026 11:12:58</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:58</t>
+          <t>15-02-2026 11:11:57</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6139,7 +6143,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6149,14 +6153,10 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26200522585800002325</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26200522364120001933</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
@@ -6165,12 +6165,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>344209</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6462,17 +6462,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t>ELBA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HOLGUIN</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6482,14 +6482,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6142443644</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>PRIV DE GONZALEZ COSSIO 6734</t>
-        </is>
-      </c>
+          <t>6141057797</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6497,60 +6493,56 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>08-03-1963</t>
+          <t>01-06-1967</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>LEOTO056@GMAIL.COM</t>
+          <t>MARIAHDZ67000@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>11-02-2026 08:12:54</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>16-02-2026 17:19:53</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>11-02-2026 08:29:30</t>
+          <t>18-02-2026 16:45:06</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>11-02-2026 08:28:18</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6558,23 +6550,27 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26200522259660001758</t>
+          <t>26200522467120002145</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Jesus Antonio Flores Torres</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6586,12 +6582,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344209</t>
+          <t>342901</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>20718</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6601,17 +6597,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ELBA</t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>HOLGUIN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6621,10 +6617,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6141057797</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6142443644</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PRIV DE GONZALEZ COSSIO 6734</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6632,56 +6632,60 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>01-06-1967</t>
+          <t>08-03-1963</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>MARIAHDZ67000@HOTMAIL.COM</t>
+          <t>LEOTO056@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:53</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 08:12:54</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:06</t>
+          <t>11-02-2026 08:29:30</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>11-02-2026 08:28:18</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6689,27 +6693,23 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26200522467120002145</t>
+          <t>26200522259660001758</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7003,12 +7003,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344234</t>
+          <t>344674</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JONATHA IVAN</t>
+          <t>ABRAHM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7038,10 +7038,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6141324957</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6147767384</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CALLE DOLORES PIMENTEL</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7049,56 +7053,64 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>06-08-2002</t>
+          <t>22-03-1999</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
+          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 17:44:53</t>
+          <t>17-02-2026 19:04:34</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-02-2026 17:46:24</t>
+          <t>17-02-2026 19:10:12</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>17-02-2026 19:08:30</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7106,36 +7118,36 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26200522400880002009</t>
+          <t>26200522443540002095</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>343805</t>
+          <t>344234</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7145,17 +7157,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA IRENE </t>
+          <t>JONATHA IVAN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">GOMEZ </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NAJERA</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7165,75 +7177,67 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6143813334</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>RIO META 1803</t>
-        </is>
-      </c>
+          <t>6141324957</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>24-06-1984</t>
+          <t>06-08-2002</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ROSYSOTO24@ICLOUD.COM</t>
+          <t>JONATHANGOMEZ4446@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>15-02-2026 10:57:33</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>16-02-2026 17:44:53</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>15-02-2026 11:04:14</t>
+          <t>16-02-2026 17:46:24</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>15-02-2026 11:01:26</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7241,36 +7245,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26200522364020001931</t>
+          <t>26200522400880002009</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344674</t>
+          <t>343805</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7280,17 +7284,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ABRAHM</t>
+          <t xml:space="preserve">ROSA IRENE </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>NAJERA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7300,39 +7304,35 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6147767384</t>
+          <t>6143813334</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CALLE DOLORES PIMENTEL</t>
+          <t>RIO META 1803</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22-03-1999</t>
+          <t>24-06-1984</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>COKE.ABRAHMGOMEZ@GMAIL.COM</t>
+          <t>ROSYSOTO24@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>17-02-2026 19:04:34</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>15-02-2026 10:57:33</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7350,17 +7350,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>17-02-2026 19:10:12</t>
+          <t>15-02-2026 11:04:14</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>17-02-2026 19:08:30</t>
+          <t>15-02-2026 11:01:26</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26200522443540002095</t>
+          <t>26200522364020001931</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7404,12 +7404,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344116</t>
+          <t>345906</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7419,17 +7419,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>ESLY YAZMIN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t xml:space="preserve">VALVERDE </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LOZOYA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7439,10 +7439,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6143978047</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6142830714</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CHE GUEVARA</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7450,17 +7454,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>21-10-1996</t>
+          <t>19-01-1997</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>SUGEYPONLOZ@GMAIL.COM</t>
+          <t>YAZMINREYES566@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 15:12:06</t>
+          <t>23-02-2026 17:09:02</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7470,36 +7474,44 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-02-2026 15:52:54</t>
+          <t>23-02-2026 17:16:35</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:16:04</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7507,22 +7519,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26200522464950002139</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+          <t>26200522590290002344</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7539,12 +7543,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>345942</t>
+          <t>344116</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>88107</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7554,17 +7558,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ADRIANA AURORA</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>LOZOYA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7574,7 +7578,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6143970735</t>
+          <t>6143978047</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7585,22 +7589,22 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>09-02-2002</t>
+          <t>21-10-1996</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ADRIANA72270@GMAIL.COM</t>
+          <t>SUGEYPONLOZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>23-02-2026 17:47:34</t>
+          <t>16-02-2026 15:12:06</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -7620,12 +7624,12 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>23-02-2026 17:48:54</t>
+          <t>18-02-2026 15:52:54</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -7642,11 +7646,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26200522592530002354</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
+          <t>26200522464950002139</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>549</t>
@@ -7654,7 +7666,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7793,12 +7805,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>345906</t>
+          <t>345907</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7808,12 +7820,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ESLY YAZMIN</t>
+          <t>JAIMIE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALVERDE </t>
+          <t>VALVERDE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7828,7 +7840,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6142830714</t>
+          <t>6144790343</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7843,17 +7855,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>19-01-1997</t>
+          <t>16-08-2004</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>YAZMINREYES566@GMAIL.COM</t>
+          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>23-02-2026 17:09:02</t>
+          <t>23-02-2026 17:09:43</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7878,7 +7890,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>23-02-2026 17:16:35</t>
+          <t>23-02-2026 17:14:20</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -7888,7 +7900,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>23-02-2026 17:16:04</t>
+          <t>23-02-2026 17:13:54</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7908,7 +7920,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26200522590290002344</t>
+          <t>26200522590120002343</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -7932,12 +7944,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>345907</t>
+          <t>345918</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7947,17 +7959,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>JAIMIE</t>
+          <t>JESSER URIEL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>VALVERDE</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7967,57 +7979,57 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6144790343</t>
+          <t>6141611733</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CHE GUEVARA</t>
+          <t>MINA GLAMIS 1914</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>16-08-2004</t>
+          <t>20-04-2001</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>JAIMIEVALVERDE123@GMAIL.COM</t>
+          <t>URIELPORTILLO951@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>23-02-2026 17:09:43</t>
+          <t>23-02-2026 17:21:49</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>23-02-2026 17:14:20</t>
+          <t>23-02-2026 17:29:11</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -8027,7 +8039,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>23-02-2026 17:13:54</t>
+          <t>23-02-2026 17:27:48</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8037,7 +8049,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -8047,19 +8059,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26200522590120002343</t>
+          <t>26200522590980002346</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8071,12 +8083,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>345918</t>
+          <t>345942</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>88107</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8086,17 +8098,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>JESSER URIEL</t>
+          <t>ADRIANA AURORA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8106,57 +8118,53 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6141611733</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>MINA GLAMIS 1914</t>
-        </is>
-      </c>
+          <t>6143970735</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>20-04-2001</t>
+          <t>09-02-2002</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>URIELPORTILLO951@GMAIL.COM</t>
+          <t>ADRIANA72270@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>23-02-2026 17:21:49</t>
+          <t>23-02-2026 17:47:34</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>23-02-2026 17:29:11</t>
+          <t>23-02-2026 17:48:54</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8164,21 +8172,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:27:48</t>
-        </is>
-      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8186,14 +8186,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26200522590980002346</t>
+          <t>26200522592530002354</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>316183</t>
+          <t>302219</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>99717</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t>MICHEL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PIZZARRO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6143741544</t>
+          <t>6144076811</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13 ABRIL</t>
+          <t>BUTRERA AMAPULA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20-04-2000</t>
+          <t>12-08-1998</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
+          <t>MICHELRUIZ12@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>29-09-2025 11:07:46</t>
+          <t>05-07-2025 11:09:27</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -648,32 +648,32 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:46</t>
+          <t>02-03-2026 16:46:16</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:15</t>
+          <t>02-03-2026 16:45:46</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,14 +693,18 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26200522769520002618</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26200522802980002688</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -717,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>302219</t>
+          <t>197040</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99717</t>
+          <t>94547</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MICHELL</t>
+          <t xml:space="preserve">JESUS MANUEL </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,67 +756,63 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6144076811</t>
+          <t>6145933104</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BUTRERA AMAPULA</t>
+          <t>GENERAL ANGEL TRIAS SN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12-08-1998</t>
+          <t>16-01-1989</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MICHELLERUIZ12@OUTLOOK.COM</t>
+          <t>JESUSPENA160189@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>05-07-2025 11:09:27</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-09-2023 16:57:19</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:16</t>
+          <t>03-03-2026 18:07:51</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:46</t>
+          <t>03-03-2026 18:07:22</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -832,40 +832,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26200522802980002688</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522853660002790</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>302218</t>
+          <t>316183</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>99716</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TERESA</t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>PIZZARRO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,12 +891,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6143383846</t>
+          <t>6143741544</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>POTRERO DE MAPULA</t>
+          <t>13 ABRIL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -910,17 +906,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-04-1969</t>
+          <t>20-04-2000</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CASTILLOTERE992@GMAIL.COM</t>
+          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>05-07-2025 11:07:01</t>
+          <t>29-09-2025 11:07:46</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -930,32 +926,32 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:54:14</t>
+          <t>01-03-2026 13:02:46</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:53:45</t>
+          <t>01-03-2026 13:02:15</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -975,40 +971,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26200522803800002693</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522769520002618</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347792</t>
+          <t>302218</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89957</t>
+          <t>99716</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DIEGO ADRIAN</t>
+          <t>TERESA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORRAS </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VELADOR</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,53 +1030,57 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6141929720</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6143383846</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>POTRERO DE MAPULA</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14-03-2008</t>
+          <t>20-04-1969</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DIEGOPORRASVELADOR@GMAI.COM</t>
+          <t>CASTILLOTERE992@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 18:05:21</t>
+          <t>05-07-2025 11:07:01</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 18:09:41</t>
+          <t>02-03-2026 16:54:14</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1092,13 +1088,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:53:45</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1106,36 +1110,40 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26200522810460002708</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26200522803800002693</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347667</t>
+          <t>346505</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89832</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1145,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>GENESIS KATTIE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>CARDONA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1165,67 +1173,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6143421907</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6141598342</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EMILE ZOLA</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23-07-1990</t>
+          <t>26-02-1994</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>JONATHAN.INA.AGUILAR@GMAIL.COM</t>
+          <t>GENESIS26942@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 16:15:01</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>25-02-2026 15:25:51</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 16:18:16</t>
+          <t>03-03-2026 18:02:45</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:01:16</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1233,22 +1249,403 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200522801060002678</t>
+          <t>26200522853270002789</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>347667</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>89832</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JONATHAN </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PIÑA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6143421907</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>23-07-1990</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>JONATHAN.INA.AGUILAR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:15:01</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:18:16</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>26200522801060002678</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>348061</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>90226</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CRISTOFER</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SANDOVAL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6144645759</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>28-11-2008</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:26:17</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:32:17</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26200522841880002759</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>347792</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>89957</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DIEGO ADRIAN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORRAS </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VELADOR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6141929720</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>14-03-2008</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DIEGOPORRASVELADOR@GMAI.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:05:21</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:09:41</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26200522810460002708</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,24 +709,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>197040</t>
+          <t>302218</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94547</t>
+          <t>99716</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS MANUEL </t>
+          <t>TERESA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,63 +756,67 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6145933104</t>
+          <t>6143383846</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GENERAL ANGEL TRIAS SN</t>
+          <t>POTRERO DE MAPULA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-01-1989</t>
+          <t>20-04-1969</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>JESUSPENA160189@GMAIL.COM</t>
+          <t>CASTILLOTERE992@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>15-09-2023 16:57:19</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>05-07-2025 11:07:01</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 18:07:51</t>
+          <t>02-03-2026 16:54:14</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>03-03-2026 18:07:22</t>
+          <t>02-03-2026 16:53:45</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -832,36 +836,40 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26200522853660002790</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26200522803800002693</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>316183</t>
+          <t>346505</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +879,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t>GENESIS KATTIE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PIZZARRO</t>
+          <t>CARDONA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,12 +899,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6143741544</t>
+          <t>6141598342</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13 ABRIL</t>
+          <t>EMILE ZOLA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -906,24 +914,20 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-04-2000</t>
+          <t>26-02-1994</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
+          <t>GENESIS26942@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>29-09-2025 11:07:46</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>25-02-2026 15:25:51</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -931,27 +935,27 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:46</t>
+          <t>03-03-2026 18:02:45</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:15</t>
+          <t>03-03-2026 18:01:16</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -971,36 +975,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26200522769520002618</t>
+          <t>26200522853270002789</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>302218</t>
+          <t>197040</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99716</t>
+          <t>94547</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1010,17 +1014,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TERESA</t>
+          <t xml:space="preserve">JESUS MANUEL </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1030,67 +1034,63 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6143383846</t>
+          <t>6145933104</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>POTRERO DE MAPULA</t>
+          <t>GENERAL ANGEL TRIAS SN</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20-04-1969</t>
+          <t>16-01-1989</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CASTILLOTERE992@GMAIL.COM</t>
+          <t>JESUSPENA160189@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>05-07-2025 11:07:01</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-09-2023 16:57:19</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 16:54:14</t>
+          <t>03-03-2026 18:07:51</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 16:53:45</t>
+          <t>03-03-2026 18:07:22</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1110,40 +1110,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26200522803800002693</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522853660002790</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346505</t>
+          <t>316183</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88670</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1149,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GENESIS KATTIE</t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CARDONA</t>
+          <t>PIZZARRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,12 +1169,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6141598342</t>
+          <t>6143741544</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EMILE ZOLA</t>
+          <t>13 ABRIL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1188,20 +1184,24 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>26-02-1994</t>
+          <t>20-04-2000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>GENESIS26942@GMAIL.COM</t>
+          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25-02-2026 15:25:51</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>29-09-2025 11:07:46</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1209,27 +1209,27 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 18:02:45</t>
+          <t>01-03-2026 13:02:46</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 18:01:16</t>
+          <t>01-03-2026 13:02:15</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1249,14 +1249,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200522853270002789</t>
+          <t>26200522769520002618</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347667</t>
+          <t>236224</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89832</t>
+          <t>33729</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>CESAR GERARDO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6143421907</t>
+          <t>6143219720</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23-07-1990</t>
+          <t>20-01-2003</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JONATHAN.INA.AGUILAR@GMAIL.COM</t>
+          <t>CESARGERARDOVALENZUELAVARELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:15:01</t>
+          <t>25-05-2024 09:21:57</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1344,28 +1344,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:18:16</t>
+          <t>05-03-2026 16:01:33</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1376,14 +1376,22 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26200522801060002678</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26200522920070002912</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>IVONNE HERNANDEZ RIVERA</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1400,12 +1408,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348061</t>
+          <t>347792</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>89957</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRISTOFER</t>
+          <t>DIEGO ADRIAN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t xml:space="preserve">PORRAS </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VELADOR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,7 +1443,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6144645759</t>
+          <t>6141929720</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1446,17 +1454,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-11-2008</t>
+          <t>14-03-2008</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
+          <t>DIEGOPORRASVELADOR@GMAI.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 14:26:17</t>
+          <t>02-03-2026 18:05:21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1481,12 +1489,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 14:32:17</t>
+          <t>02-03-2026 18:09:41</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1503,7 +1511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26200522841880002759</t>
+          <t>26200522810460002708</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1527,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347792</t>
+          <t>347667</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89957</t>
+          <t>89832</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DIEGO ADRIAN</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORRAS </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VELADOR</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,7 +1570,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6141929720</t>
+          <t>6143421907</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1573,17 +1581,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>14-03-2008</t>
+          <t>23-07-1990</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DIEGOPORRASVELADOR@GMAI.COM</t>
+          <t>JONATHAN.INA.AGUILAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 18:05:21</t>
+          <t>02-03-2026 16:15:01</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1608,7 +1616,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 18:09:41</t>
+          <t>02-03-2026 16:18:16</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1630,7 +1638,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26200522810460002708</t>
+          <t>26200522801060002678</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1646,6 +1654,959 @@
         </is>
       </c>
       <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347738</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89903</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EDGAR ALAN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MARRUJO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6146006419</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>16-05-1990</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>INCYCLING4@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:24:16</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:18:19</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26200522893780002864</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>NIDIA GUADALUPE CORDERO CHAVEZ</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Nidia  Cordero</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348061</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90226</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CRISTOFER</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SANDOVAL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6144645759</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>28-11-2008</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:26:17</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:32:17</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26200522841880002759</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>348564</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90729</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RODOLFO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAENZ </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6141260734</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRACC MISION UNIVERSIDAD </t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>21-10-2005</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>RODOLFOSAENZ2005@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:27:31</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:32:21</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:31:41</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26200522894670002867</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348054</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90219</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PAYAN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6143538080</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>12-07-1984</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NANCYPAYAN35@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:49:55</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>05-03-2026 13:53:43</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26200522916250002899</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348055</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90220</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LESLIE JOHANA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6146109937</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>01-01-2004</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>LESLIEROMERO1025@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:52:43</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>05-03-2026 13:52:50</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26200522916170002898</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348329</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90494</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ANNI MARLENE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELTRAN </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SALDIVAR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>9704014074</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PABLO LICON 12701</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>18-08-1986</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AFRODITA_ILOVE5@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:09:24</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:22:26</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:18:31</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26200522877220002823</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348569</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90734</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LUCIA VERONICA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAVELA </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6141003902</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>COLINAS DEL SOL</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>07-05-2005</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>VERONICAFAVELA2423@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:33:34</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:32</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:02</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26200522894880002868</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>302219</t>
+          <t>197040</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99717</t>
+          <t>94547</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MICHEL</t>
+          <t xml:space="preserve">JESUS MANUEL </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,57 +613,53 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6144076811</t>
+          <t>6145933104</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BUTRERA AMAPULA</t>
+          <t>GENERAL ANGEL TRIAS SN</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12-08-1998</t>
+          <t>16-01-1989</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MICHELRUIZ12@OUTLOOK.COM</t>
+          <t>JESUSPENA160189@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>05-07-2025 11:09:27</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-09-2023 16:57:19</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:16</t>
+          <t>03-03-2026 18:07:51</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -673,7 +669,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:46</t>
+          <t>03-03-2026 18:07:22</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,40 +689,36 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26200522802980002688</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522853660002790</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>302218</t>
+          <t>316183</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99716</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TERESA</t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>PIZZARRO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,12 +748,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6143383846</t>
+          <t>6143741544</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>POTRERO DE MAPULA</t>
+          <t>13 ABRIL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -771,17 +763,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20-04-1969</t>
+          <t>20-04-2000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CASTILLOTERE992@GMAIL.COM</t>
+          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>05-07-2025 11:07:01</t>
+          <t>29-09-2025 11:07:46</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -791,32 +783,32 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:54:14</t>
+          <t>01-03-2026 13:02:46</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:53:45</t>
+          <t>01-03-2026 13:02:15</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -836,40 +828,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26200522803800002693</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522769520002618</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346505</t>
+          <t>236224</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88670</t>
+          <t>33729</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GENESIS KATTIE</t>
+          <t>CESAR GERARDO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CARDONA</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,75 +887,67 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6141598342</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>EMILE ZOLA</t>
-        </is>
-      </c>
+          <t>6143219720</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-02-1994</t>
+          <t>20-01-2003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>GENESIS26942@GMAIL.COM</t>
+          <t>CESARGERARDOVALENZUELAVARELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25-02-2026 15:25:51</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>25-05-2024 09:21:57</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 18:02:45</t>
+          <t>05-03-2026 16:01:33</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:01:16</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -975,36 +955,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26200522853270002789</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26200522920070002912</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>IVONNE HERNANDEZ RIVERA</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>197040</t>
+          <t>302218</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>94547</t>
+          <t>99716</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS MANUEL </t>
+          <t>TERESA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,63 +1022,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6145933104</t>
+          <t>6143383846</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GENERAL ANGEL TRIAS SN</t>
+          <t>POTRERO DE MAPULA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>16-01-1989</t>
+          <t>20-04-1969</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JESUSPENA160189@GMAIL.COM</t>
+          <t>CASTILLOTERE992@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>15-09-2023 16:57:19</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>05-07-2025 11:07:01</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 18:07:51</t>
+          <t>02-03-2026 16:54:14</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>03-03-2026 18:07:22</t>
+          <t>02-03-2026 16:53:45</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1110,36 +1102,40 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26200522853660002790</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26200522803800002693</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>316183</t>
+          <t>346505</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1149,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t>GENESIS KATTIE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PIZZARRO</t>
+          <t>CARDONA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1169,12 +1165,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6143741544</t>
+          <t>6141598342</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13 ABRIL</t>
+          <t>EMILE ZOLA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1184,24 +1180,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20-04-2000</t>
+          <t>26-02-1994</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
+          <t>GENESIS26942@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>29-09-2025 11:07:46</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>25-02-2026 15:25:51</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1209,27 +1201,27 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:46</t>
+          <t>03-03-2026 18:02:45</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:15</t>
+          <t>03-03-2026 18:01:16</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1249,36 +1241,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200522769520002618</t>
+          <t>26200522853270002789</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>236224</t>
+          <t>302219</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>99717</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,17 +1280,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CESAR GERARDO</t>
+          <t>MICHEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1308,28 +1300,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6143219720</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6144076811</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BUTRERA AMAPULA</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20-01-2003</t>
+          <t>12-08-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CESARGERARDOVALENZUELAVARELA@GMAIL.COM</t>
+          <t>MICHELRUIZ12@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>25-05-2024 09:21:57</t>
+          <t>05-07-2025 11:09:27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1339,36 +1335,44 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-03-2026 16:01:33</t>
+          <t>02-03-2026 16:46:16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:45:46</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1376,7 +1380,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26200522920070002912</t>
+          <t>26200522802980002688</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1384,24 +1388,20 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>IVONNE HERNANDEZ RIVERA</t>
-        </is>
-      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1797,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348061</t>
+          <t>348054</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>90219</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRISTOFER</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,28 +1832,28 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6144645759</t>
+          <t>6143538080</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-11-2008</t>
+          <t>12-07-1984</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
+          <t>NANCYPAYAN35@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 14:26:17</t>
+          <t>03-03-2026 13:49:55</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 14:32:17</t>
+          <t>05-03-2026 13:53:43</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1900,11 +1900,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26200522841880002759</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26200522916250002899</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1924,12 +1932,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348564</t>
+          <t>348055</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90729</t>
+          <t>90220</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1947,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RODOLFO</t>
+          <t>LESLIE JOHANA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAENZ </t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,79 +1967,63 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6141260734</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FRACC MISION UNIVERSIDAD </t>
-        </is>
-      </c>
+          <t>6146109937</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21-10-2005</t>
+          <t>01-01-2004</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>RODOLFOSAENZ2005@GMAIL.COM</t>
+          <t>LESLIEROMERO1025@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>04-03-2026 18:27:31</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>03-03-2026 13:52:43</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 18:32:21</t>
+          <t>05-03-2026 13:52:50</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>04-03-2026 18:31:41</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2039,36 +2031,44 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26200522894670002867</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26200522916170002898</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348054</t>
+          <t>348329</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90219</t>
+          <t>90494</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2078,30 +2078,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>ANNI MARLENE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t xml:space="preserve">BELTRAN </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>SALDIVAR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6143538080</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>9704014074</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PABLO LICON 12701</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2109,56 +2113,64 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12-07-1984</t>
+          <t>18-08-1986</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>NANCYPAYAN35@GMAIL.COM</t>
+          <t>AFRODITA_ILOVE5@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 13:49:55</t>
+          <t>04-03-2026 07:09:24</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05-03-2026 13:53:43</t>
+          <t>04-03-2026 09:22:26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:18:31</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2166,7 +2178,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26200522916250002899</t>
+          <t>26200522877220002823</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2176,17 +2188,17 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+          <t>DIANA EDITH BARRAZA DURAN</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2198,12 +2210,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348055</t>
+          <t>348569</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>90734</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2213,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LESLIE JOHANA</t>
+          <t>LUCIA VERONICA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t xml:space="preserve">FAVELA </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2233,10 +2245,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6146109937</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6141003902</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>COLINAS DEL SOL</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2244,52 +2260,64 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>01-01-2004</t>
+          <t>07-05-2005</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LESLIEROMERO1025@GMAIL.COM</t>
+          <t>VERONICAFAVELA2423@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 13:52:43</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>04-03-2026 18:33:34</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>05-03-2026 13:52:50</t>
+          <t>04-03-2026 18:36:32</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:02</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2297,22 +2325,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26200522916170002898</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
-        </is>
-      </c>
+          <t>26200522894880002868</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2329,12 +2349,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348329</t>
+          <t>348061</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90494</t>
+          <t>90226</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2344,99 +2364,87 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ANNI MARLENE</t>
+          <t>CRISTOFER</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELTRAN </t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SALDIVAR</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6144645759</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>28-11-2008</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:26:17</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:32:17</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>9704014074</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PABLO LICON 12701</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>18-08-1986</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>AFRODITA_ILOVE5@HOTMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>04-03-2026 07:09:24</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>04-03-2026 09:22:26</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>04-03-2026 09:18:31</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2444,27 +2452,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26200522877220002823</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522841880002759</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348569</t>
+          <t>348564</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90734</t>
+          <t>90729</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LUCIA VERONICA</t>
+          <t>RODOLFO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAVELA </t>
+          <t xml:space="preserve">SAENZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6141003902</t>
+          <t>6141260734</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COLINAS DEL SOL</t>
+          <t xml:space="preserve">FRACC MISION UNIVERSIDAD </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>07-05-2005</t>
+          <t>21-10-2005</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>VERONICAFAVELA2423@GMAIL.COM</t>
+          <t>RODOLFOSAENZ2005@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>04-03-2026 18:33:34</t>
+          <t>04-03-2026 18:27:31</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04-03-2026 18:36:32</t>
+          <t>04-03-2026 18:32:21</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>04-03-2026 18:36:02</t>
+          <t>04-03-2026 18:31:41</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26200522894880002868</t>
+          <t>26200522894670002867</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>197040</t>
+          <t>136484</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>94547</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS MANUEL </t>
+          <t xml:space="preserve">SERGIO IVAN </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t xml:space="preserve">ALMANZA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">RIVAS </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6145933104</t>
+          <t>6142152293</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GENERAL ANGEL TRIAS SN</t>
+          <t>MOLINO DE ZUBIETA 20509</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,60 +628,56 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16-01-1989</t>
+          <t>05-09-1991</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>JESUSPENA160189@GMAIL.COM</t>
+          <t>ALMANZA-SARAIS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>15-09-2023 16:57:19</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>28-11-2022 16:49:16</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 18:07:51</t>
+          <t>12-03-2026 16:22:06</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:07:22</t>
-        </is>
-      </c>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -689,14 +685,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26200522853660002790</t>
+          <t>26200523126160003278</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -713,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>316183</t>
+          <t>197040</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>94547</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t xml:space="preserve">JESUS MANUEL </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PIZZARRO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,39 +744,35 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6143741544</t>
+          <t>6145933104</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13 ABRIL</t>
+          <t>GENERAL ANGEL TRIAS SN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20-04-2000</t>
+          <t>16-01-1989</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
+          <t>JESUSPENA160189@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>29-09-2025 11:07:46</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-09-2023 16:57:19</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -788,27 +780,27 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:46</t>
+          <t>03-03-2026 18:07:51</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>31-03-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:15</t>
+          <t>03-03-2026 18:07:22</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -828,36 +820,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26200522769520002618</t>
+          <t>26200522853660002790</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>236224</t>
+          <t>316183</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CESAR GERARDO</t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>PIZZARRO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,28 +879,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6143219720</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6143741544</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13 ABRIL</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-01-2003</t>
+          <t>20-04-2000</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CESARGERARDOVALENZUELAVARELA@GMAIL.COM</t>
+          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25-05-2024 09:21:57</t>
+          <t>29-09-2025 11:07:46</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -918,36 +914,44 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>05-03-2026 16:01:33</t>
+          <t>01-03-2026 13:02:46</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>31-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>01-03-2026 13:02:15</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,22 +959,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26200522920070002912</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>IVONNE HERNANDEZ RIVERA</t>
-        </is>
-      </c>
+          <t>26200522769520002618</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -987,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>302218</t>
+          <t>225206</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99716</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TERESA</t>
+          <t>NALLELI JOCELYN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,14 +1018,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6143383846</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>POTRERO DE MAPULA</t>
-        </is>
-      </c>
+          <t>6145306300</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1037,64 +1029,56 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20-04-1969</t>
+          <t>06-08-2011</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CASTILLOTERE992@GMAIL.COM</t>
+          <t>NXLL0116@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>05-07-2025 11:07:01</t>
+          <t>18-03-2024 16:17:21</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 16:54:14</t>
+          <t>10-03-2026 08:14:07</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:53:45</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1102,7 +1086,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26200522803800002693</t>
+          <t>26200523044890003125</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1110,32 +1094,36 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346505</t>
+          <t>226889</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88670</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1145,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GENESIS KATTIE</t>
+          <t>EVELIN SOFIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CARDONA</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1165,12 +1153,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6141598342</t>
+          <t>6141958186</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EMILE ZOLA</t>
+          <t>1 DE MAYO 133</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1180,48 +1168,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>26-02-1994</t>
+          <t>20-12-2006</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>GENESIS26942@GMAIL.COM</t>
+          <t>SOFIARAMOS1643@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>25-02-2026 15:25:51</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>28-03-2024 17:43:29</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 18:02:45</t>
+          <t>18-03-2026 13:14:46</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 18:01:16</t>
+          <t>18-03-2026 13:14:26</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1241,19 +1233,27 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200522853270002789</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26200523290930003550</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1265,12 +1265,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>302219</t>
+          <t>283470</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>99717</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MICHEL</t>
+          <t xml:space="preserve">ITZEL DAYANA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>ARENALES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>PRIETO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6144076811</t>
+          <t>6144519786</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BUTRERA AMAPULA</t>
+          <t>ISLA SALOMON 9818</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1315,52 +1315,52 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-08-1998</t>
+          <t>23-03-2002</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MICHELRUIZ12@OUTLOOK.COM</t>
+          <t>ITZELARENALES390@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>05-07-2025 11:09:27</t>
+          <t>17-03-2025 11:01:32</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:16</t>
+          <t>09-03-2026 04:18:05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:46</t>
+          <t>09-03-2026 04:14:06</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1380,23 +1380,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26200522802980002688</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26200522988670003033</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1408,12 +1404,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347792</t>
+          <t>302218</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89957</t>
+          <t>99716</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1423,17 +1419,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DIEGO ADRIAN</t>
+          <t>TERESA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORRAS </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VELADOR</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1443,53 +1439,57 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6141929720</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6143383846</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>POTRERO DE MAPULA</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14-03-2008</t>
+          <t>20-04-1969</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>DIEGOPORRASVELADOR@GMAI.COM</t>
+          <t>CASTILLOTERE992@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:05:21</t>
+          <t>05-07-2025 11:07:01</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:09:41</t>
+          <t>02-03-2026 16:54:14</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1497,13 +1497,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:53:45</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1511,36 +1519,40 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26200522810460002708</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26200522803800002693</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347667</t>
+          <t>302219</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89832</t>
+          <t>99717</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1562,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>MICHEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,53 +1582,57 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6143421907</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6144076811</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BUTRERA AMAPULA</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23-07-1990</t>
+          <t>12-08-1998</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>JONATHAN.INA.AGUILAR@GMAIL.COM</t>
+          <t>MICHELRUIZ12@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 16:15:01</t>
+          <t>05-07-2025 11:09:27</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 16:18:16</t>
+          <t>02-03-2026 16:46:16</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1624,13 +1640,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:45:46</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1638,36 +1662,40 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26200522801060002678</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26200522802980002688</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347738</t>
+          <t>236224</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89903</t>
+          <t>33729</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1705,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EDGAR ALAN</t>
+          <t>CESAR GERARDO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MARRUJO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,7 +1725,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6146006419</t>
+          <t>6143219720</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1708,22 +1736,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>16-05-1990</t>
+          <t>20-01-2003</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>INCYCLING4@GMAIL.COM</t>
+          <t>CESARGERARDOVALENZUELAVARELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 17:24:16</t>
+          <t>25-05-2024 09:21:57</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1733,22 +1761,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-03-2026 18:18:19</t>
+          <t>05-03-2026 16:01:33</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1765,7 +1793,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26200522893780002864</t>
+          <t>26200522920070002912</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1775,34 +1803,34 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>NIDIA GUADALUPE CORDERO CHAVEZ</t>
+          <t>IVONNE HERNANDEZ RIVERA</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Nidia  Cordero</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348054</t>
+          <t>344105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90219</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1840,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t xml:space="preserve">DANIEL </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>BULGARIN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,28 +1860,28 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6143538080</t>
+          <t>6143718185</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12-07-1984</t>
+          <t>17-09-1988</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NANCYPAYAN35@GMAIL.COM</t>
+          <t>DANBULGARINI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 13:49:55</t>
+          <t>16-02-2026 14:49:32</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1878,18 +1906,18 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-03-2026 13:53:43</t>
+          <t>09-03-2026 12:01:41</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1900,7 +1928,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26200522916250002899</t>
+          <t>26200523005200003050</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1910,7 +1938,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1920,24 +1948,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348055</t>
+          <t>346505</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1947,17 +1975,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LESLIE JOHANA</t>
+          <t>GENESIS KATTIE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>CARDONA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1967,10 +1995,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6146109937</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6141598342</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>EMILE ZOLA</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1978,52 +2010,60 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>01-01-2004</t>
+          <t>26-02-1994</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>LESLIEROMERO1025@GMAIL.COM</t>
+          <t>GENESIS26942@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 13:52:43</t>
+          <t>25-02-2026 15:25:51</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>05-03-2026 13:52:50</t>
+          <t>03-03-2026 18:02:45</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:01:16</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2031,27 +2071,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26200522916170002898</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
-        </is>
-      </c>
+          <t>26200522853270002789</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2063,12 +2095,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348329</t>
+          <t>347667</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90494</t>
+          <t>89832</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2078,99 +2110,87 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ANNI MARLENE</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELTRAN </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SALDIVAR</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6143421907</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>23-07-1990</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>JONATHAN.INA.AGUILAR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:15:01</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:18:16</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>9704014074</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PABLO LICON 12701</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>18-08-1986</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>AFRODITA_ILOVE5@HOTMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>04-03-2026 07:09:24</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>04-03-2026 09:22:26</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>04-03-2026 09:18:31</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2178,44 +2198,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26200522877220002823</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522801060002678</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348569</t>
+          <t>347792</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90734</t>
+          <t>89957</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2225,17 +2237,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LUCIA VERONICA</t>
+          <t>DIEGO ADRIAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAVELA </t>
+          <t xml:space="preserve">PORRAS </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>VELADOR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2245,47 +2257,43 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6141003902</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>COLINAS DEL SOL</t>
-        </is>
-      </c>
+          <t>6141929720</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>07-05-2005</t>
+          <t>14-03-2008</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>VERONICAFAVELA2423@GMAIL.COM</t>
+          <t>DIEGOPORRASVELADOR@GMAI.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-03-2026 18:33:34</t>
+          <t>02-03-2026 18:05:21</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2295,29 +2303,21 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-03-2026 18:36:32</t>
+          <t>02-03-2026 18:09:41</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>04-03-2026 18:36:02</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26200522894880002868</t>
+          <t>26200522810460002708</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2337,24 +2337,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348061</t>
+          <t>347738</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>89903</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,17 +2364,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRISTOFER</t>
+          <t>EDGAR ALAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>MARRUJO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6144645759</t>
+          <t>6146006419</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>28-11-2008</t>
+          <t>16-05-1990</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
+          <t>INCYCLING4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 14:26:17</t>
+          <t>02-03-2026 17:24:16</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2430,18 +2430,18 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 14:32:17</t>
+          <t>04-03-2026 18:18:19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2452,11 +2452,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26200522841880002759</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26200522893780002864</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>NIDIA GUADALUPE CORDERO CHAVEZ</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>549</t>
@@ -2464,7 +2472,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Nidia  Cordero</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2476,137 +2484,1622 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>348329</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90494</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ANNI MARLENE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELTRAN </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SALDIVAR</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>9704014074</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PABLO LICON 12701</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>18-08-1986</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AFRODITA_ILOVE5@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:09:24</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:22:26</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:18:31</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26200522877220002823</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348054</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90219</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PAYAN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6143538080</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>12-07-1984</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NANCYPAYAN35@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:49:55</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>05-03-2026 13:53:43</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26200522916250002899</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348055</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90220</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LESLIE JOHANA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6146109937</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>01-01-2004</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>LESLIEROMERO1025@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:52:43</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>05-03-2026 13:52:50</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26200522916170002898</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348061</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90226</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CRISTOFER</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SANDOVAL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6144645759</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>28-11-2008</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:26:17</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>03-03-2026 14:32:17</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26200522841880002759</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>348569</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90734</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LUCIA VERONICA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAVELA </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6141003902</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COLINAS DEL SOL</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07-05-2005</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>VERONICAFAVELA2423@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:33:34</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:32</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:02</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26200522894880002868</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>348564</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>90729</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>SEND CHIH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>RODOLFO</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">SAENZ </t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>ACOSTA</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>6141260734</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">FRACC MISION UNIVERSIDAD </t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>21-10-2005</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>RODOLFOSAENZ2005@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>04-03-2026 18:27:31</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Inscripcion $150</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Forzoso</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>04-03-2026 18:32:21</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>04-03-2026 18:31:41</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>26200522894670002867</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>349546</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>91711</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DANIEL ARTURO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6145537654</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COBALTO 18507</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>11-11-2001</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DT71455376@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:25:22</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:29:12</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:28:41</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26200523017690003082</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>349535</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>91700</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CARLOS SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SALCIDO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6145044253</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>13-05-1992</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>SEBASROME13@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:12:40</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:14:22</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26200523016680003073</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>349630</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>91795</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MARIANA ITZEL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>JURADO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>QUEZADA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6143626782</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PRIV DE JJ CALVO</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>21-01-2007</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MARIANAITZELJURADO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:51:15</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:51:15</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:51:15</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26200523024410003095</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>349538</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>91703</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DENISSE LETICIA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REYES </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6143696905</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>DESIERTOS DE SONORA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>02-02-1998</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>DR5047060@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:15:41</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:23:04</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:21:50</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26200523017320003078</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>350479</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>92643</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ISAAC UBALDO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GARIBAY</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6141198094</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CALLE CRONOS 15142</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>17-11-1996</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ISAACGAR9711@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>12-03-2026 19:47:24</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>13-03-2026 18:30:14</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12-03-2026 19:50:19</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26200523161010003353</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>351563</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>93727</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>JASON</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GALINDO </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PAYAN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6144716170</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>21-06-1999</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>JASELEONEL@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:14:06</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:15:39</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26200523258130003482</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Luis Alberto Pulido Teran</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SEND CHIH.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>136484</t>
+          <t>226889</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERGIO IVAN </t>
+          <t>EVELIN SOFIA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMANZA </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIVAS </t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,71 +613,79 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6142152293</t>
+          <t>6141958186</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MOLINO DE ZUBIETA 20509</t>
+          <t>1 DE MAYO 133</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>05-09-1991</t>
+          <t>20-12-2006</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ALMANZA-SARAIS@HOTMAIL.COM</t>
+          <t>SOFIARAMOS1643@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>28-11-2022 16:49:16</t>
+          <t>28-03-2024 17:43:29</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>12-03-2026 16:22:06</t>
+          <t>18-03-2026 13:14:46</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>18-03-2026 13:14:26</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -685,36 +693,44 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26200523126160003278</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26200523290930003550</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>197040</t>
+          <t>136484</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94547</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS MANUEL </t>
+          <t xml:space="preserve">SERGIO IVAN </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑA </t>
+          <t xml:space="preserve">ALMANZA </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">RIVAS </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,12 +760,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6145933104</t>
+          <t>6142152293</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GENERAL ANGEL TRIAS SN</t>
+          <t>MOLINO DE ZUBIETA 20509</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -759,60 +775,56 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-01-1989</t>
+          <t>05-09-1991</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>JESUSPENA160189@GMAIL.COM</t>
+          <t>ALMANZA-SARAIS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>15-09-2023 16:57:19</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>28-11-2022 16:49:16</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 18:07:51</t>
+          <t>12-03-2026 16:22:06</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:07:22</t>
-        </is>
-      </c>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,36 +832,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26200522853660002790</t>
+          <t>26200523126160003278</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>316183</t>
+          <t>197040</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>94547</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ARACELY</t>
+          <t xml:space="preserve">JESUS MANUEL </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t xml:space="preserve">PEÑA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PIZZARRO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,39 +891,35 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6143741544</t>
+          <t>6145933104</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13 ABRIL</t>
+          <t>GENERAL ANGEL TRIAS SN</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-04-2000</t>
+          <t>16-01-1989</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
+          <t>JESUSPENA160189@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>29-09-2025 11:07:46</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-09-2023 16:57:19</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -919,27 +927,27 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:46</t>
+          <t>03-03-2026 18:07:51</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>31-03-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>01-03-2026 13:02:15</t>
+          <t>03-03-2026 18:07:22</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -959,24 +967,24 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26200522769520002618</t>
+          <t>26200522853660002790</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>226889</t>
+          <t>270213</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>67716</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EVELIN SOFIA</t>
+          <t>ANA NICOLE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,14 +1161,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6141958186</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1 DE MAYO 133</t>
-        </is>
-      </c>
+          <t>6361361915</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1168,64 +1172,56 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20-12-2006</t>
+          <t>27-12-2006</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SOFIARAMOS1643@GMAIL.COM</t>
+          <t>CARBAJALVEGANICOLE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>28-03-2024 17:43:29</t>
+          <t>23-12-2024 06:07:01</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>18-03-2026 13:14:46</t>
+          <t>30-03-2026 09:45:28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>18-03-2026 13:14:26</t>
-        </is>
-      </c>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1233,7 +1229,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26200523290930003550</t>
+          <t>26200523622000004103</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1241,19 +1237,15 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
-        </is>
-      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1265,12 +1257,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>283470</t>
+          <t>302219</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>99717</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1280,17 +1272,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZEL DAYANA </t>
+          <t>MICHEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ARENALES</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PRIETO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1300,12 +1292,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6144519786</t>
+          <t>6144076811</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ISLA SALOMON 9818</t>
+          <t>BUTRERA AMAPULA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1315,52 +1307,52 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23-03-2002</t>
+          <t>12-08-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ITZELARENALES390@GMAIL.COM</t>
+          <t>MICHELRUIZ12@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17-03-2025 11:01:32</t>
+          <t>05-07-2025 11:09:27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>09-03-2026 04:18:05</t>
+          <t>02-03-2026 16:46:16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>09-03-2026 04:14:06</t>
+          <t>02-03-2026 16:45:46</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1380,19 +1372,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26200522988670003033</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26200522802980002688</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Edgar Eduardo Perez Pillado</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1404,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>302218</t>
+          <t>236224</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>99716</t>
+          <t>33729</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1419,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TERESA</t>
+          <t>CESAR GERARDO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1439,32 +1435,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6143383846</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>POTRERO DE MAPULA</t>
-        </is>
-      </c>
+          <t>6143219720</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20-04-1969</t>
+          <t>20-01-2003</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CASTILLOTERE992@GMAIL.COM</t>
+          <t>CESARGERARDOVALENZUELAVARELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>05-07-2025 11:07:01</t>
+          <t>25-05-2024 09:21:57</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1474,44 +1466,36 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:54:14</t>
+          <t>05-03-2026 16:01:33</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:53:45</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1519,7 +1503,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26200522803800002693</t>
+          <t>26200522920070002912</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1527,32 +1511,36 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>IVONNE HERNANDEZ RIVERA</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>302219</t>
+          <t>279478</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>99717</t>
+          <t>76979</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1562,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MICHEL</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>DE LA PAZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1582,67 +1570,67 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6144076811</t>
+          <t>6144746949</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BUTRERA AMAPULA</t>
+          <t>MARIA MONTESSORI 612</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12-08-1998</t>
+          <t>18-08-2000</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MICHELRUIZ12@OUTLOOK.COM</t>
+          <t>DELAPAZZARAGOZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>05-07-2025 11:09:27</t>
+          <t>18-02-2025 14:33:28</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:16</t>
+          <t>24-03-2026 10:51:48</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>23-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 16:45:46</t>
+          <t>24-03-2026 10:50:10</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1662,7 +1650,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26200522802980002688</t>
+          <t>26200523463580003849</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1673,12 +1661,12 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>Jesus Antonio Flores Torres</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1690,12 +1678,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>236224</t>
+          <t>283470</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>80971</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1705,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CESAR GERARDO</t>
+          <t xml:space="preserve">ITZEL DAYANA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>ARENALES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>PRIETO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1725,67 +1713,79 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6143219720</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6144519786</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ISLA SALOMON 9818</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20-01-2003</t>
+          <t>23-03-2002</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CESARGERARDOVALENZUELAVARELA@GMAIL.COM</t>
+          <t>ITZELARENALES390@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25-05-2024 09:21:57</t>
+          <t>17-03-2025 11:01:32</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>05-03-2026 16:01:33</t>
+          <t>09-03-2026 04:18:05</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>09-03-2026 04:14:06</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1793,44 +1793,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26200522920070002912</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>IVONNE HERNANDEZ RIVERA</t>
-        </is>
-      </c>
+          <t>26200522988670003033</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>302218</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>99716</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1840,17 +1832,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIEL </t>
+          <t>TERESA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BULGARIN</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1860,67 +1852,79 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6143718185</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6143383846</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>POTRERO DE MAPULA</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>17-09-1988</t>
+          <t>20-04-1969</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>DANBULGARINI@GMAIL.COM</t>
+          <t>CASTILLOTERE992@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>16-02-2026 14:49:32</t>
+          <t>05-07-2025 11:07:01</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-03-2026 12:01:41</t>
+          <t>02-03-2026 16:54:14</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:53:45</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1928,7 +1932,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26200523005200003050</t>
+          <t>26200522803800002693</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1936,36 +1940,32 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Rubi Esmeralda  Martinez Alcala</t>
-        </is>
-      </c>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>346505</t>
+          <t>344105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88670</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GENESIS KATTIE</t>
+          <t xml:space="preserve">DANIEL </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CARDONA</t>
+          <t>BULGARIN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1995,75 +1995,67 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6141598342</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>EMILE ZOLA</t>
-        </is>
-      </c>
+          <t>6143718185</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26-02-1994</t>
+          <t>17-09-1988</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>GENESIS26942@GMAIL.COM</t>
+          <t>DANBULGARINI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>25-02-2026 15:25:51</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>16-02-2026 14:49:32</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 18:02:45</t>
+          <t>09-03-2026 12:01:41</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>03-03-2026 18:01:16</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2071,36 +2063,44 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26200522853270002789</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26200523005200003050</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Rubi Esmeralda  Martinez Alcala</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347667</t>
+          <t>316183</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89832</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JONATHAN </t>
+          <t>ARACELY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PIÑA</t>
+          <t>PIZZARRO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2130,43 +2130,47 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6143421907</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6143741544</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>13 ABRIL</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>23-07-1990</t>
+          <t>20-04-2000</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JONATHAN.INA.AGUILAR@GMAIL.COM</t>
+          <t>ARACELY_GOMEZT@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 16:15:01</t>
+          <t>29-09-2025 11:07:46</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2176,21 +2180,29 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 16:18:16</t>
+          <t>01-03-2026 13:02:46</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>31-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>01-03-2026 13:02:15</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2198,7 +2210,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26200522801060002678</t>
+          <t>26200522769520002618</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2349,12 +2361,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347738</t>
+          <t>346505</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89903</t>
+          <t>88670</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2364,17 +2376,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EDGAR ALAN</t>
+          <t>GENESIS KATTIE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MARRUJO</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>CARDONA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2384,67 +2396,75 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6146006419</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6141598342</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>EMILE ZOLA</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>16-05-1990</t>
+          <t>26-02-1994</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>INCYCLING4@GMAIL.COM</t>
+          <t>GENESIS26942@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 17:24:16</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>25-02-2026 15:25:51</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>04-03-2026 18:18:19</t>
+          <t>03-03-2026 18:02:45</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:01:16</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2452,27 +2472,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26200522893780002864</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>NIDIA GUADALUPE CORDERO CHAVEZ</t>
-        </is>
-      </c>
+          <t>26200522853270002789</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Nidia  Cordero</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2484,12 +2496,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348329</t>
+          <t>347667</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90494</t>
+          <t>89832</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2499,99 +2511,87 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ANNI MARLENE</t>
+          <t xml:space="preserve">JONATHAN </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BELTRAN </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SALDIVAR</t>
+          <t>PIÑA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6143421907</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>23-07-1990</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>JONATHAN.INA.AGUILAR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:15:01</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:18:16</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>9704014074</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PABLO LICON 12701</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>18-08-1986</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>AFRODITA_ILOVE5@HOTMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>04-03-2026 07:09:24</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>04-03-2026 09:22:26</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>04-03-2026 09:18:31</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2599,44 +2599,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26200522877220002823</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>DIANA EDITH BARRAZA DURAN</t>
-        </is>
-      </c>
+          <t>26200522801060002678</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348054</t>
+          <t>347738</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90219</t>
+          <t>89903</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2646,17 +2638,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NANCY</t>
+          <t>EDGAR ALAN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>MARRUJO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PAYAN</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2666,28 +2658,28 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6143538080</t>
+          <t>6146006419</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12-07-1984</t>
+          <t>16-05-1990</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NANCYPAYAN35@GMAIL.COM</t>
+          <t>INCYCLING4@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 13:49:55</t>
+          <t>02-03-2026 17:24:16</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2712,18 +2704,18 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>05-03-2026 13:53:43</t>
+          <t>04-03-2026 18:18:19</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2734,7 +2726,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26200522916250002899</t>
+          <t>26200522893780002864</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2744,7 +2736,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+          <t>NIDIA GUADALUPE CORDERO CHAVEZ</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2754,7 +2746,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Nidia  Cordero</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2766,12 +2758,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348055</t>
+          <t>348061</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>90226</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2781,17 +2773,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LESLIE JOHANA</t>
+          <t>CRISTOFER</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>SANDOVAL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2801,31 +2793,35 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6146109937</t>
+          <t>6144645759</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>01-01-2004</t>
+          <t>28-11-2008</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LESLIEROMERO1025@GMAIL.COM</t>
+          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 13:52:43</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>03-03-2026 14:26:17</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -2833,28 +2829,28 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>05-03-2026 13:52:50</t>
+          <t>03-03-2026 14:32:17</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2865,27 +2861,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26200522916170002898</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
-        </is>
-      </c>
+          <t>26200522841880002759</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>Edgar Eduardo Perez Pillado</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2897,12 +2885,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348061</t>
+          <t>348054</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>90219</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2912,17 +2900,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRISTOFER</t>
+          <t>NANCY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SANDOVAL</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>PAYAN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2932,28 +2920,28 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6144645759</t>
+          <t>6143538080</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>28-11-2008</t>
+          <t>12-07-1984</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CRISTOPHERSAN2811@GMAIL.COM</t>
+          <t>NANCYPAYAN35@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-03-2026 14:26:17</t>
+          <t>03-03-2026 13:49:55</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2978,12 +2966,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-03-2026 14:32:17</t>
+          <t>05-03-2026 13:53:43</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -3000,11 +2988,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26200522841880002759</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26200522916250002899</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>549</t>
@@ -3024,12 +3020,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348569</t>
+          <t>348055</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90734</t>
+          <t>90220</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3039,17 +3035,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LUCIA VERONICA</t>
+          <t>LESLIE JOHANA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAVELA </t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3059,14 +3055,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6141003902</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>COLINAS DEL SOL</t>
-        </is>
-      </c>
+          <t>6146109937</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3074,64 +3066,52 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>07-05-2005</t>
+          <t>01-01-2004</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>VERONICAFAVELA2423@GMAIL.COM</t>
+          <t>LESLIEROMERO1025@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-03-2026 18:33:34</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>03-03-2026 13:52:43</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-03-2026 18:36:32</t>
+          <t>05-03-2026 13:52:50</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>04-03-2026 18:36:02</t>
-        </is>
-      </c>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3139,14 +3119,22 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26200522894880002868</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26200522916170002898</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3163,12 +3151,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348564</t>
+          <t>349630</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90729</t>
+          <t>91795</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3178,17 +3166,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RODOLFO</t>
+          <t>MARIANA ITZEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAENZ </t>
+          <t>JURADO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>QUEZADA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3198,39 +3186,35 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6141260734</t>
+          <t>6143626782</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRACC MISION UNIVERSIDAD </t>
+          <t>PRIV DE JJ CALVO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21-10-2005</t>
+          <t>21-01-2007</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>RODOLFOSAENZ2005@GMAIL.COM</t>
+          <t>MARIANAITZELJURADO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-03-2026 18:27:31</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>09-03-2026 18:51:15</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3248,29 +3232,29 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-03-2026 18:32:21</t>
+          <t>09-03-2026 18:51:15</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>04-03-2026 18:31:41</t>
+          <t>09-03-2026 18:51:15</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3278,7 +3262,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26200522894670002867</t>
+          <t>26200523024410003095</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3441,12 +3425,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>349535</t>
+          <t>348564</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>91700</t>
+          <t>90729</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3456,17 +3440,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CARLOS SEBASTIAN</t>
+          <t>RODOLFO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t xml:space="preserve">SAENZ </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SALCIDO</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3476,10 +3460,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6145044253</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6141260734</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRACC MISION UNIVERSIDAD </t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3487,32 +3475,32 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13-05-1992</t>
+          <t>21-10-2005</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SEBASROME13@GMAIL.COM</t>
+          <t>RODOLFOSAENZ2005@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-03-2026 17:12:40</t>
+          <t>04-03-2026 18:27:31</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3522,21 +3510,29 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-03-2026 17:14:22</t>
+          <t>04-03-2026 18:32:21</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:31:41</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3544,7 +3540,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26200523016680003073</t>
+          <t>26200522894670002867</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3556,24 +3552,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>349630</t>
+          <t>349535</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>91795</t>
+          <t>91700</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3583,17 +3579,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MARIANA ITZEL</t>
+          <t>CARLOS SEBASTIAN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JURADO</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>QUEZADA</t>
+          <t>SALCIDO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3603,43 +3599,43 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6143626782</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>PRIV DE JJ CALVO</t>
-        </is>
-      </c>
+          <t>6145044253</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21-01-2007</t>
+          <t>13-05-1992</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MARIANAITZELJURADO@GMAIL.COM</t>
+          <t>SEBASROME13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-03-2026 18:51:15</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>09-03-2026 17:12:40</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3649,7 +3645,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-03-2026 18:51:15</t>
+          <t>09-03-2026 17:14:22</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3657,21 +3653,13 @@
           <t>08-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>09-03-2026 18:51:15</t>
-        </is>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3679,7 +3667,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26200523024410003095</t>
+          <t>26200523016680003073</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3691,24 +3679,24 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Ivonne Hernandez Rivera</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>349538</t>
+          <t>350479</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>91703</t>
+          <t>92643</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3718,17 +3706,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DENISSE LETICIA</t>
+          <t>ISAAC UBALDO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>GARIBAY</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CORRALES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3738,32 +3726,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6143696905</t>
+          <t>6141198094</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>DESIERTOS DE SONORA</t>
+          <t>CALLE CRONOS 15142</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>02-02-1998</t>
+          <t>17-11-1996</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>DR5047060@GMAIL.COM</t>
+          <t>ISAACGAR9711@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-03-2026 17:15:41</t>
+          <t>12-03-2026 19:47:24</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3788,17 +3776,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>09-03-2026 17:23:04</t>
+          <t>13-03-2026 18:30:14</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>09-03-2026 17:21:50</t>
+          <t>12-03-2026 19:50:19</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3818,7 +3806,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26200523017320003078</t>
+          <t>26200523161010003353</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3830,24 +3818,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Luis Alberto Pulido Teran</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>350479</t>
+          <t>349538</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>92643</t>
+          <t>91703</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3857,17 +3845,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ISAAC UBALDO</t>
+          <t>DENISSE LETICIA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GARIBAY</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CORRALES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3877,32 +3865,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6141198094</t>
+          <t>6143696905</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CALLE CRONOS 15142</t>
+          <t>DESIERTOS DE SONORA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17-11-1996</t>
+          <t>02-02-1998</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ISAACGAR9711@GMAIL.COM</t>
+          <t>DR5047060@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12-03-2026 19:47:24</t>
+          <t>09-03-2026 17:15:41</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3927,17 +3915,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>13-03-2026 18:30:14</t>
+          <t>09-03-2026 17:23:04</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12-03-2026 19:50:19</t>
+          <t>09-03-2026 17:21:50</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3957,7 +3945,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26200523161010003353</t>
+          <t>26200523017320003078</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3969,137 +3957,1841 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>348329</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90494</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ANNI MARLENE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELTRAN </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SALDIVAR</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9704014074</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PABLO LICON 12701</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>18-08-1986</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AFRODITA_ILOVE5@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:09:24</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:22:26</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>04-03-2026 09:18:31</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26200522877220002823</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>DIANA EDITH BARRAZA DURAN</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Flores Torres</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348569</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90734</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LUCIA VERONICA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAVELA </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6141003902</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>COLINAS DEL SOL</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>07-05-2005</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>VERONICAFAVELA2423@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:33:34</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:32</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:36:02</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26200522894880002868</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>351563</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>93727</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>SEND CHIH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>JASON</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>PAYAN</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>6144716170</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>21-06-1999</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>JASELEONEL@HOTMAIL.COM</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>17-03-2026 16:14:06</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Tarifas 2026 LE</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Sin contrato</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>1 MES $899</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>899</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>17-03-2026 16:15:39</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>16-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr">
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>26200523258130003482</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
         <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>Luis Alberto Pulido Teran</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>352628</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>94792</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LUCAS OMAR</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CAROLEO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OYUELA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6144050064</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>GRACIANO URRIETA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>07-01-1993</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>LUCASCAROLEO21@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>22-03-2026 20:56:47</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:46:19</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:45:25</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26200523497430003917</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Edgar Eduardo Perez Pillado</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>353227</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>95391</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>REINA LUCIA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZAVALA </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ORDUÑO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6142313038</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>RIO AROS 849</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>08-03-2000</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>LUCIASAVALAA0@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>24-03-2026 19:42:49</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>26-03-2026 11:16:38</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>26-03-2026 11:15:57</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26200523531680003983</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>IVONNE HERNANDEZ RIVERA</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>353183</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>95347</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ARIADNE ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6145120740</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>COLONIA LLORONES</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>14-10-2010</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>CLAUDIAGMSCL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>24-03-2026 18:22:20</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:49:48</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:49:23</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26200523544130004012</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>NIDIA GUADALUPE CORDERO CHAVEZ</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>354427</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>96591</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MARTIN ALFONSO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6143962703</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>INFONAVIT</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>28-06-1990</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>MARTINELPRIMO56@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:34:50</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:39:20</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:38:47</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26200523648190004147</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>354430</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>96594</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MARIA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AVILA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>RICO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6145099514</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>QUINTAS</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>28-11-1995</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>LUPIITA13@LIVE.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:38:28</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:42:19</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:41:50</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26200523648430004148</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>354089</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>96253</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RIGOBERTO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ORTEGA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CORONEL</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6144950597</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>24-05-1995</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>R_ORTEGA_C@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>30-03-2026 08:31:29</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>30-03-2026 08:33:22</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26200523620090004098</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>352576</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>94740</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OSCAR UZIEL</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SOLIS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6142210308</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ANDREA DORIA 2501</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>22-03-1997</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>MARTINEZOSCAR888@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>22-03-2026 10:41:04</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>26-03-2026 05:12:34</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>26-03-2026 05:11:07</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26200523520650003969</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Ivonne Hernandez Rivera</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>352629</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>94793</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NANCY GABRIELA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TERRAZAS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>URIBE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6141380085</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>URQUIDI</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>18-04-1986</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>LUCASCAROLEO22@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>22-03-2026 20:58:38</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:49:14</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:48:55</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26200523497510003918</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Edgar Eduardo Perez Pillado</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>353181</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>95345</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CLAUDIA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SALDAÑA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6144037467</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BOSQUE COUVET</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>22-05-1989</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CLAUIDAGMSCL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>24-03-2026 18:21:37</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:46:58</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:45:37</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26200523543920004011</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>353484</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>95648</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLOS ALBERTO </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOMINGUEZ </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLIVAS </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6142880601</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>C IRWIN WALLACE 14310</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>30-05-2002</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CARLOSDOMIGUEZ6771@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>26-03-2026 06:33:56</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>26-03-2026 06:40:28</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>26-03-2026 06:39:12</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26200523526970003974</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Flores Torres</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>
